--- a/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
+++ b/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X484"/>
+  <dimension ref="A1:X531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41122,6 +41122,3954 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS | D. ORRIT SERRANO | J. BERGENS | N. OKEKE | R. HAYES</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>5</v>
+      </c>
+      <c r="E485" t="n">
+        <v>79</v>
+      </c>
+      <c r="F485" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G485" t="n">
+        <v>0</v>
+      </c>
+      <c r="H485" t="n">
+        <v>3</v>
+      </c>
+      <c r="I485" t="n">
+        <v>1</v>
+      </c>
+      <c r="J485" t="n">
+        <v>2</v>
+      </c>
+      <c r="K485" t="n">
+        <v>0</v>
+      </c>
+      <c r="L485" t="n">
+        <v>150</v>
+      </c>
+      <c r="M485" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N485" t="n">
+        <v>0</v>
+      </c>
+      <c r="O485" t="n">
+        <v>0</v>
+      </c>
+      <c r="P485" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>0</v>
+      </c>
+      <c r="R485" t="n">
+        <v>2</v>
+      </c>
+      <c r="S485" t="n">
+        <v>0</v>
+      </c>
+      <c r="T485" t="n">
+        <v>1</v>
+      </c>
+      <c r="U485" t="n">
+        <v>1</v>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W485" t="n">
+        <v>24</v>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS | J. BERGENS | J. CERA RODRIGUEZ | N. OKEKE | R. HAYES</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>5</v>
+      </c>
+      <c r="E486" t="n">
+        <v>129</v>
+      </c>
+      <c r="F486" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G486" t="n">
+        <v>10</v>
+      </c>
+      <c r="H486" t="n">
+        <v>6</v>
+      </c>
+      <c r="I486" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J486" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="K486" t="n">
+        <v>210.08</v>
+      </c>
+      <c r="L486" t="n">
+        <v>164.84</v>
+      </c>
+      <c r="M486" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="N486" t="n">
+        <v>4</v>
+      </c>
+      <c r="O486" t="n">
+        <v>4</v>
+      </c>
+      <c r="P486" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>1</v>
+      </c>
+      <c r="R486" t="n">
+        <v>1</v>
+      </c>
+      <c r="S486" t="n">
+        <v>6</v>
+      </c>
+      <c r="T486" t="n">
+        <v>1</v>
+      </c>
+      <c r="U486" t="n">
+        <v>1</v>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W486" t="n">
+        <v>24</v>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS | J. BERGENS | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>5</v>
+      </c>
+      <c r="E487" t="n">
+        <v>22</v>
+      </c>
+      <c r="F487" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G487" t="n">
+        <v>0</v>
+      </c>
+      <c r="H487" t="n">
+        <v>0</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0</v>
+      </c>
+      <c r="J487" t="n">
+        <v>1</v>
+      </c>
+      <c r="K487" t="n">
+        <v>0</v>
+      </c>
+      <c r="L487" t="n">
+        <v>0</v>
+      </c>
+      <c r="M487" t="n">
+        <v>0</v>
+      </c>
+      <c r="N487" t="n">
+        <v>0</v>
+      </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
+      <c r="P487" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>0</v>
+      </c>
+      <c r="R487" t="n">
+        <v>0</v>
+      </c>
+      <c r="S487" t="n">
+        <v>0</v>
+      </c>
+      <c r="T487" t="n">
+        <v>1</v>
+      </c>
+      <c r="U487" t="n">
+        <v>0</v>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W487" t="n">
+        <v>24</v>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>D. ORRIT SERRANO | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>5</v>
+      </c>
+      <c r="E488" t="n">
+        <v>10</v>
+      </c>
+      <c r="F488" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G488" t="n">
+        <v>0</v>
+      </c>
+      <c r="H488" t="n">
+        <v>0</v>
+      </c>
+      <c r="I488" t="n">
+        <v>0</v>
+      </c>
+      <c r="J488" t="n">
+        <v>1</v>
+      </c>
+      <c r="K488" t="n">
+        <v>0</v>
+      </c>
+      <c r="L488" t="n">
+        <v>0</v>
+      </c>
+      <c r="M488" t="n">
+        <v>0</v>
+      </c>
+      <c r="N488" t="n">
+        <v>0</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="P488" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>0</v>
+      </c>
+      <c r="R488" t="n">
+        <v>2</v>
+      </c>
+      <c r="S488" t="n">
+        <v>0</v>
+      </c>
+      <c r="T488" t="n">
+        <v>0</v>
+      </c>
+      <c r="U488" t="n">
+        <v>1</v>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W488" t="n">
+        <v>24</v>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>J. BERGENS | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>5</v>
+      </c>
+      <c r="E489" t="n">
+        <v>332</v>
+      </c>
+      <c r="F489" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G489" t="n">
+        <v>8</v>
+      </c>
+      <c r="H489" t="n">
+        <v>8</v>
+      </c>
+      <c r="I489" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="J489" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K489" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="L489" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="M489" t="n">
+        <v>-30.39</v>
+      </c>
+      <c r="N489" t="n">
+        <v>10</v>
+      </c>
+      <c r="O489" t="n">
+        <v>2</v>
+      </c>
+      <c r="P489" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>2</v>
+      </c>
+      <c r="R489" t="n">
+        <v>6</v>
+      </c>
+      <c r="S489" t="n">
+        <v>6</v>
+      </c>
+      <c r="T489" t="n">
+        <v>1</v>
+      </c>
+      <c r="U489" t="n">
+        <v>3</v>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W489" t="n">
+        <v>24</v>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>4</v>
+      </c>
+      <c r="E490" t="n">
+        <v>27</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G490" t="n">
+        <v>1</v>
+      </c>
+      <c r="H490" t="n">
+        <v>0</v>
+      </c>
+      <c r="I490" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J490" t="n">
+        <v>1</v>
+      </c>
+      <c r="K490" t="n">
+        <v>0</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" t="n">
+        <v>0</v>
+      </c>
+      <c r="N490" t="n">
+        <v>0</v>
+      </c>
+      <c r="O490" t="n">
+        <v>2</v>
+      </c>
+      <c r="P490" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>1</v>
+      </c>
+      <c r="R490" t="n">
+        <v>1</v>
+      </c>
+      <c r="S490" t="n">
+        <v>0</v>
+      </c>
+      <c r="T490" t="n">
+        <v>0</v>
+      </c>
+      <c r="U490" t="n">
+        <v>0</v>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W490" t="n">
+        <v>24</v>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK | A. INFANTE GUTIERREZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>5</v>
+      </c>
+      <c r="E491" t="n">
+        <v>31</v>
+      </c>
+      <c r="F491" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G491" t="n">
+        <v>2</v>
+      </c>
+      <c r="H491" t="n">
+        <v>0</v>
+      </c>
+      <c r="I491" t="n">
+        <v>1</v>
+      </c>
+      <c r="J491" t="n">
+        <v>0</v>
+      </c>
+      <c r="K491" t="n">
+        <v>200</v>
+      </c>
+      <c r="L491" t="n">
+        <v>0</v>
+      </c>
+      <c r="M491" t="n">
+        <v>0</v>
+      </c>
+      <c r="N491" t="n">
+        <v>1</v>
+      </c>
+      <c r="O491" t="n">
+        <v>0</v>
+      </c>
+      <c r="P491" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>0</v>
+      </c>
+      <c r="R491" t="n">
+        <v>0</v>
+      </c>
+      <c r="S491" t="n">
+        <v>0</v>
+      </c>
+      <c r="T491" t="n">
+        <v>0</v>
+      </c>
+      <c r="U491" t="n">
+        <v>0</v>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W491" t="n">
+        <v>24</v>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>5</v>
+      </c>
+      <c r="E492" t="n">
+        <v>27</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G492" t="n">
+        <v>0</v>
+      </c>
+      <c r="H492" t="n">
+        <v>2</v>
+      </c>
+      <c r="I492" t="n">
+        <v>1</v>
+      </c>
+      <c r="J492" t="n">
+        <v>1</v>
+      </c>
+      <c r="K492" t="n">
+        <v>0</v>
+      </c>
+      <c r="L492" t="n">
+        <v>200</v>
+      </c>
+      <c r="M492" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N492" t="n">
+        <v>1</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
+      <c r="P492" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>0</v>
+      </c>
+      <c r="R492" t="n">
+        <v>1</v>
+      </c>
+      <c r="S492" t="n">
+        <v>0</v>
+      </c>
+      <c r="T492" t="n">
+        <v>0</v>
+      </c>
+      <c r="U492" t="n">
+        <v>0</v>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W492" t="n">
+        <v>24</v>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>5</v>
+      </c>
+      <c r="E493" t="n">
+        <v>50</v>
+      </c>
+      <c r="F493" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G493" t="n">
+        <v>0</v>
+      </c>
+      <c r="H493" t="n">
+        <v>2</v>
+      </c>
+      <c r="I493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J493" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0</v>
+      </c>
+      <c r="L493" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M493" t="n">
+        <v>0</v>
+      </c>
+      <c r="N493" t="n">
+        <v>1</v>
+      </c>
+      <c r="O493" t="n">
+        <v>0</v>
+      </c>
+      <c r="P493" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>1</v>
+      </c>
+      <c r="R493" t="n">
+        <v>1</v>
+      </c>
+      <c r="S493" t="n">
+        <v>2</v>
+      </c>
+      <c r="T493" t="n">
+        <v>0</v>
+      </c>
+      <c r="U493" t="n">
+        <v>0</v>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W493" t="n">
+        <v>24</v>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | L. OBAJO BELTRAN | P. SALL</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>5</v>
+      </c>
+      <c r="E494" t="n">
+        <v>85</v>
+      </c>
+      <c r="F494" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G494" t="n">
+        <v>3</v>
+      </c>
+      <c r="H494" t="n">
+        <v>4</v>
+      </c>
+      <c r="I494" t="n">
+        <v>2</v>
+      </c>
+      <c r="J494" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K494" t="n">
+        <v>150</v>
+      </c>
+      <c r="L494" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="M494" t="n">
+        <v>-62.77</v>
+      </c>
+      <c r="N494" t="n">
+        <v>1</v>
+      </c>
+      <c r="O494" t="n">
+        <v>0</v>
+      </c>
+      <c r="P494" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>0</v>
+      </c>
+      <c r="R494" t="n">
+        <v>1</v>
+      </c>
+      <c r="S494" t="n">
+        <v>2</v>
+      </c>
+      <c r="T494" t="n">
+        <v>0</v>
+      </c>
+      <c r="U494" t="n">
+        <v>0</v>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W494" t="n">
+        <v>24</v>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>5</v>
+      </c>
+      <c r="E495" t="n">
+        <v>123</v>
+      </c>
+      <c r="F495" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G495" t="n">
+        <v>6</v>
+      </c>
+      <c r="H495" t="n">
+        <v>6</v>
+      </c>
+      <c r="I495" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J495" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K495" t="n">
+        <v>164.84</v>
+      </c>
+      <c r="L495" t="n">
+        <v>154.64</v>
+      </c>
+      <c r="M495" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N495" t="n">
+        <v>2</v>
+      </c>
+      <c r="O495" t="n">
+        <v>6</v>
+      </c>
+      <c r="P495" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>2</v>
+      </c>
+      <c r="R495" t="n">
+        <v>3</v>
+      </c>
+      <c r="S495" t="n">
+        <v>2</v>
+      </c>
+      <c r="T495" t="n">
+        <v>1</v>
+      </c>
+      <c r="U495" t="n">
+        <v>1</v>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W495" t="n">
+        <v>24</v>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>5</v>
+      </c>
+      <c r="E496" t="n">
+        <v>91</v>
+      </c>
+      <c r="F496" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G496" t="n">
+        <v>4</v>
+      </c>
+      <c r="H496" t="n">
+        <v>3</v>
+      </c>
+      <c r="I496" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J496" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K496" t="n">
+        <v>144.93</v>
+      </c>
+      <c r="L496" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="M496" t="n">
+        <v>-14.65</v>
+      </c>
+      <c r="N496" t="n">
+        <v>2</v>
+      </c>
+      <c r="O496" t="n">
+        <v>4</v>
+      </c>
+      <c r="P496" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>1</v>
+      </c>
+      <c r="R496" t="n">
+        <v>2</v>
+      </c>
+      <c r="S496" t="n">
+        <v>2</v>
+      </c>
+      <c r="T496" t="n">
+        <v>0</v>
+      </c>
+      <c r="U496" t="n">
+        <v>1</v>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W496" t="n">
+        <v>24</v>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>5</v>
+      </c>
+      <c r="E497" t="n">
+        <v>10</v>
+      </c>
+      <c r="F497" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G497" t="n">
+        <v>0</v>
+      </c>
+      <c r="H497" t="n">
+        <v>0</v>
+      </c>
+      <c r="I497" t="n">
+        <v>1</v>
+      </c>
+      <c r="J497" t="n">
+        <v>0</v>
+      </c>
+      <c r="K497" t="n">
+        <v>0</v>
+      </c>
+      <c r="L497" t="n">
+        <v>0</v>
+      </c>
+      <c r="M497" t="n">
+        <v>0</v>
+      </c>
+      <c r="N497" t="n">
+        <v>2</v>
+      </c>
+      <c r="O497" t="n">
+        <v>0</v>
+      </c>
+      <c r="P497" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>1</v>
+      </c>
+      <c r="R497" t="n">
+        <v>0</v>
+      </c>
+      <c r="S497" t="n">
+        <v>0</v>
+      </c>
+      <c r="T497" t="n">
+        <v>0</v>
+      </c>
+      <c r="U497" t="n">
+        <v>0</v>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W497" t="n">
+        <v>24</v>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>5</v>
+      </c>
+      <c r="E498" t="n">
+        <v>182</v>
+      </c>
+      <c r="F498" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G498" t="n">
+        <v>2</v>
+      </c>
+      <c r="H498" t="n">
+        <v>2</v>
+      </c>
+      <c r="I498" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J498" t="n">
+        <v>4</v>
+      </c>
+      <c r="K498" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="L498" t="n">
+        <v>50</v>
+      </c>
+      <c r="M498" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N498" t="n">
+        <v>2</v>
+      </c>
+      <c r="O498" t="n">
+        <v>2</v>
+      </c>
+      <c r="P498" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>1</v>
+      </c>
+      <c r="R498" t="n">
+        <v>6</v>
+      </c>
+      <c r="S498" t="n">
+        <v>0</v>
+      </c>
+      <c r="T498" t="n">
+        <v>0</v>
+      </c>
+      <c r="U498" t="n">
+        <v>2</v>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W498" t="n">
+        <v>24</v>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>A. CALVO TORRES | C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | J. LACUNZA ABECIA</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>5</v>
+      </c>
+      <c r="E499" t="n">
+        <v>9</v>
+      </c>
+      <c r="F499" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G499" t="n">
+        <v>0</v>
+      </c>
+      <c r="H499" t="n">
+        <v>2</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0</v>
+      </c>
+      <c r="J499" t="n">
+        <v>1</v>
+      </c>
+      <c r="K499" t="n">
+        <v>0</v>
+      </c>
+      <c r="L499" t="n">
+        <v>200</v>
+      </c>
+      <c r="M499" t="n">
+        <v>0</v>
+      </c>
+      <c r="N499" t="n">
+        <v>0</v>
+      </c>
+      <c r="O499" t="n">
+        <v>0</v>
+      </c>
+      <c r="P499" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>0</v>
+      </c>
+      <c r="R499" t="n">
+        <v>1</v>
+      </c>
+      <c r="S499" t="n">
+        <v>0</v>
+      </c>
+      <c r="T499" t="n">
+        <v>0</v>
+      </c>
+      <c r="U499" t="n">
+        <v>0</v>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W499" t="n">
+        <v>24</v>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>A. CALVO TORRES | C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | P. YARNOZ LUMBRERAS</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>5</v>
+      </c>
+      <c r="E500" t="n">
+        <v>33</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G500" t="n">
+        <v>3</v>
+      </c>
+      <c r="H500" t="n">
+        <v>0</v>
+      </c>
+      <c r="I500" t="n">
+        <v>2</v>
+      </c>
+      <c r="J500" t="n">
+        <v>0</v>
+      </c>
+      <c r="K500" t="n">
+        <v>150</v>
+      </c>
+      <c r="L500" t="n">
+        <v>0</v>
+      </c>
+      <c r="M500" t="n">
+        <v>0</v>
+      </c>
+      <c r="N500" t="n">
+        <v>2</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
+      <c r="P500" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>0</v>
+      </c>
+      <c r="R500" t="n">
+        <v>0</v>
+      </c>
+      <c r="S500" t="n">
+        <v>0</v>
+      </c>
+      <c r="T500" t="n">
+        <v>0</v>
+      </c>
+      <c r="U500" t="n">
+        <v>0</v>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W500" t="n">
+        <v>24</v>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | J. LACUNZA ABECIA | P. YARNOZ LUMBRERAS</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>5</v>
+      </c>
+      <c r="E501" t="n">
+        <v>248</v>
+      </c>
+      <c r="F501" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="G501" t="n">
+        <v>13</v>
+      </c>
+      <c r="H501" t="n">
+        <v>14</v>
+      </c>
+      <c r="I501" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="J501" t="n">
+        <v>8</v>
+      </c>
+      <c r="K501" t="n">
+        <v>195.78</v>
+      </c>
+      <c r="L501" t="n">
+        <v>175</v>
+      </c>
+      <c r="M501" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="N501" t="n">
+        <v>7</v>
+      </c>
+      <c r="O501" t="n">
+        <v>6</v>
+      </c>
+      <c r="P501" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>3</v>
+      </c>
+      <c r="R501" t="n">
+        <v>9</v>
+      </c>
+      <c r="S501" t="n">
+        <v>0</v>
+      </c>
+      <c r="T501" t="n">
+        <v>0</v>
+      </c>
+      <c r="U501" t="n">
+        <v>1</v>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W501" t="n">
+        <v>24</v>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. BARROS GARCIA</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>5</v>
+      </c>
+      <c r="E502" t="n">
+        <v>9</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G502" t="n">
+        <v>2</v>
+      </c>
+      <c r="H502" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" t="n">
+        <v>1</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0</v>
+      </c>
+      <c r="K502" t="n">
+        <v>200</v>
+      </c>
+      <c r="L502" t="n">
+        <v>0</v>
+      </c>
+      <c r="M502" t="n">
+        <v>0</v>
+      </c>
+      <c r="N502" t="n">
+        <v>1</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>0</v>
+      </c>
+      <c r="R502" t="n">
+        <v>0</v>
+      </c>
+      <c r="S502" t="n">
+        <v>0</v>
+      </c>
+      <c r="T502" t="n">
+        <v>0</v>
+      </c>
+      <c r="U502" t="n">
+        <v>0</v>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W502" t="n">
+        <v>24</v>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>5</v>
+      </c>
+      <c r="E503" t="n">
+        <v>124</v>
+      </c>
+      <c r="F503" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G503" t="n">
+        <v>7</v>
+      </c>
+      <c r="H503" t="n">
+        <v>5</v>
+      </c>
+      <c r="I503" t="n">
+        <v>4</v>
+      </c>
+      <c r="J503" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K503" t="n">
+        <v>175</v>
+      </c>
+      <c r="L503" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M503" t="n">
+        <v>-52.27</v>
+      </c>
+      <c r="N503" t="n">
+        <v>5</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
+      <c r="P503" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>1</v>
+      </c>
+      <c r="R503" t="n">
+        <v>2</v>
+      </c>
+      <c r="S503" t="n">
+        <v>5</v>
+      </c>
+      <c r="T503" t="n">
+        <v>0</v>
+      </c>
+      <c r="U503" t="n">
+        <v>2</v>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W503" t="n">
+        <v>24</v>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | J. MENENDEZ GARCIA | M. OKAFOR AUGUSTIN | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>5</v>
+      </c>
+      <c r="E504" t="n">
+        <v>24</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G504" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" t="n">
+        <v>3</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K504" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M504" t="n">
+        <v>0</v>
+      </c>
+      <c r="N504" t="n">
+        <v>0</v>
+      </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>0</v>
+      </c>
+      <c r="R504" t="n">
+        <v>1</v>
+      </c>
+      <c r="S504" t="n">
+        <v>1</v>
+      </c>
+      <c r="T504" t="n">
+        <v>0</v>
+      </c>
+      <c r="U504" t="n">
+        <v>0</v>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W504" t="n">
+        <v>24</v>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. BARROS GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>5</v>
+      </c>
+      <c r="E505" t="n">
+        <v>24</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G505" t="n">
+        <v>0</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>1</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" t="n">
+        <v>0</v>
+      </c>
+      <c r="M505" t="n">
+        <v>0</v>
+      </c>
+      <c r="N505" t="n">
+        <v>0</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>0</v>
+      </c>
+      <c r="R505" t="n">
+        <v>1</v>
+      </c>
+      <c r="S505" t="n">
+        <v>0</v>
+      </c>
+      <c r="T505" t="n">
+        <v>0</v>
+      </c>
+      <c r="U505" t="n">
+        <v>0</v>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W505" t="n">
+        <v>24</v>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | I. DUKE TOUSSAINT | S. BARROS GARCIA | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>5</v>
+      </c>
+      <c r="E506" t="n">
+        <v>11</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G506" t="n">
+        <v>2</v>
+      </c>
+      <c r="H506" t="n">
+        <v>2</v>
+      </c>
+      <c r="I506" t="n">
+        <v>1</v>
+      </c>
+      <c r="J506" t="n">
+        <v>1</v>
+      </c>
+      <c r="K506" t="n">
+        <v>200</v>
+      </c>
+      <c r="L506" t="n">
+        <v>200</v>
+      </c>
+      <c r="M506" t="n">
+        <v>0</v>
+      </c>
+      <c r="N506" t="n">
+        <v>1</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
+      <c r="P506" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>0</v>
+      </c>
+      <c r="R506" t="n">
+        <v>1</v>
+      </c>
+      <c r="S506" t="n">
+        <v>0</v>
+      </c>
+      <c r="T506" t="n">
+        <v>0</v>
+      </c>
+      <c r="U506" t="n">
+        <v>0</v>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W506" t="n">
+        <v>24</v>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>5</v>
+      </c>
+      <c r="E507" t="n">
+        <v>9</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0</v>
+      </c>
+      <c r="H507" t="n">
+        <v>3</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="n">
+        <v>1</v>
+      </c>
+      <c r="K507" t="n">
+        <v>0</v>
+      </c>
+      <c r="L507" t="n">
+        <v>300</v>
+      </c>
+      <c r="M507" t="n">
+        <v>0</v>
+      </c>
+      <c r="N507" t="n">
+        <v>0</v>
+      </c>
+      <c r="O507" t="n">
+        <v>0</v>
+      </c>
+      <c r="P507" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>0</v>
+      </c>
+      <c r="R507" t="n">
+        <v>1</v>
+      </c>
+      <c r="S507" t="n">
+        <v>0</v>
+      </c>
+      <c r="T507" t="n">
+        <v>0</v>
+      </c>
+      <c r="U507" t="n">
+        <v>0</v>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W507" t="n">
+        <v>24</v>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>G. ARCOS GONZALEZ | J. MENENDEZ GARCIA | M. OKAFOR AUGUSTIN | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>5</v>
+      </c>
+      <c r="E508" t="n">
+        <v>89</v>
+      </c>
+      <c r="F508" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G508" t="n">
+        <v>5</v>
+      </c>
+      <c r="H508" t="n">
+        <v>3</v>
+      </c>
+      <c r="I508" t="n">
+        <v>3</v>
+      </c>
+      <c r="J508" t="n">
+        <v>2</v>
+      </c>
+      <c r="K508" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L508" t="n">
+        <v>150</v>
+      </c>
+      <c r="M508" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="N508" t="n">
+        <v>3</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>0</v>
+      </c>
+      <c r="R508" t="n">
+        <v>3</v>
+      </c>
+      <c r="S508" t="n">
+        <v>0</v>
+      </c>
+      <c r="T508" t="n">
+        <v>0</v>
+      </c>
+      <c r="U508" t="n">
+        <v>1</v>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W508" t="n">
+        <v>24</v>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. KOCIC | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>5</v>
+      </c>
+      <c r="E509" t="n">
+        <v>84</v>
+      </c>
+      <c r="F509" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G509" t="n">
+        <v>2</v>
+      </c>
+      <c r="H509" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" t="n">
+        <v>1</v>
+      </c>
+      <c r="J509" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K509" t="n">
+        <v>200</v>
+      </c>
+      <c r="L509" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M509" t="n">
+        <v>130.56</v>
+      </c>
+      <c r="N509" t="n">
+        <v>2</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0</v>
+      </c>
+      <c r="P509" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>1</v>
+      </c>
+      <c r="R509" t="n">
+        <v>2</v>
+      </c>
+      <c r="S509" t="n">
+        <v>2</v>
+      </c>
+      <c r="T509" t="n">
+        <v>0</v>
+      </c>
+      <c r="U509" t="n">
+        <v>0</v>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W509" t="n">
+        <v>24</v>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>5</v>
+      </c>
+      <c r="E510" t="n">
+        <v>3</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0</v>
+      </c>
+      <c r="H510" t="n">
+        <v>1</v>
+      </c>
+      <c r="I510" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J510" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M510" t="n">
+        <v>0</v>
+      </c>
+      <c r="N510" t="n">
+        <v>0</v>
+      </c>
+      <c r="O510" t="n">
+        <v>0</v>
+      </c>
+      <c r="P510" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>1</v>
+      </c>
+      <c r="R510" t="n">
+        <v>1</v>
+      </c>
+      <c r="S510" t="n">
+        <v>2</v>
+      </c>
+      <c r="T510" t="n">
+        <v>0</v>
+      </c>
+      <c r="U510" t="n">
+        <v>1</v>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W510" t="n">
+        <v>24</v>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. KOCIC | V. MORENO MARTIN | V. STEVANIC</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>5</v>
+      </c>
+      <c r="E511" t="n">
+        <v>40</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G511" t="n">
+        <v>4</v>
+      </c>
+      <c r="H511" t="n">
+        <v>0</v>
+      </c>
+      <c r="I511" t="n">
+        <v>2</v>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="n">
+        <v>200</v>
+      </c>
+      <c r="L511" t="n">
+        <v>0</v>
+      </c>
+      <c r="M511" t="n">
+        <v>200</v>
+      </c>
+      <c r="N511" t="n">
+        <v>2</v>
+      </c>
+      <c r="O511" t="n">
+        <v>0</v>
+      </c>
+      <c r="P511" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>0</v>
+      </c>
+      <c r="R511" t="n">
+        <v>1</v>
+      </c>
+      <c r="S511" t="n">
+        <v>0</v>
+      </c>
+      <c r="T511" t="n">
+        <v>0</v>
+      </c>
+      <c r="U511" t="n">
+        <v>0</v>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W511" t="n">
+        <v>24</v>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>C. JACOBS | E. A NONGO BERTHOLD | H. ARBOSA ROLDAN | J. PARDINA MOLINA | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>5</v>
+      </c>
+      <c r="E512" t="n">
+        <v>3</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G512" t="n">
+        <v>1</v>
+      </c>
+      <c r="H512" t="n">
+        <v>0</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J512" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K512" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L512" t="n">
+        <v>0</v>
+      </c>
+      <c r="M512" t="n">
+        <v>0</v>
+      </c>
+      <c r="N512" t="n">
+        <v>1</v>
+      </c>
+      <c r="O512" t="n">
+        <v>2</v>
+      </c>
+      <c r="P512" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>1</v>
+      </c>
+      <c r="R512" t="n">
+        <v>0</v>
+      </c>
+      <c r="S512" t="n">
+        <v>0</v>
+      </c>
+      <c r="T512" t="n">
+        <v>0</v>
+      </c>
+      <c r="U512" t="n">
+        <v>1</v>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W512" t="n">
+        <v>24</v>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>C. JACOBS | E. A NONGO BERTHOLD | H. ARBOSA ROLDAN | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>5</v>
+      </c>
+      <c r="E513" t="n">
+        <v>19</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G513" t="n">
+        <v>0</v>
+      </c>
+      <c r="H513" t="n">
+        <v>2</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0</v>
+      </c>
+      <c r="J513" t="n">
+        <v>1</v>
+      </c>
+      <c r="K513" t="n">
+        <v>0</v>
+      </c>
+      <c r="L513" t="n">
+        <v>200</v>
+      </c>
+      <c r="M513" t="n">
+        <v>0</v>
+      </c>
+      <c r="N513" t="n">
+        <v>0</v>
+      </c>
+      <c r="O513" t="n">
+        <v>0</v>
+      </c>
+      <c r="P513" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>0</v>
+      </c>
+      <c r="R513" t="n">
+        <v>1</v>
+      </c>
+      <c r="S513" t="n">
+        <v>0</v>
+      </c>
+      <c r="T513" t="n">
+        <v>0</v>
+      </c>
+      <c r="U513" t="n">
+        <v>0</v>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W513" t="n">
+        <v>24</v>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>C. JACOBS | H. ARBOSA ROLDAN | J. PARDINA MOLINA | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>5</v>
+      </c>
+      <c r="E514" t="n">
+        <v>34</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" t="n">
+        <v>1</v>
+      </c>
+      <c r="J514" t="n">
+        <v>0</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" t="n">
+        <v>0</v>
+      </c>
+      <c r="M514" t="n">
+        <v>0</v>
+      </c>
+      <c r="N514" t="n">
+        <v>1</v>
+      </c>
+      <c r="O514" t="n">
+        <v>0</v>
+      </c>
+      <c r="P514" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>0</v>
+      </c>
+      <c r="R514" t="n">
+        <v>1</v>
+      </c>
+      <c r="S514" t="n">
+        <v>0</v>
+      </c>
+      <c r="T514" t="n">
+        <v>0</v>
+      </c>
+      <c r="U514" t="n">
+        <v>1</v>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W514" t="n">
+        <v>24</v>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>C. JACOBS | H. ARBOSA ROLDAN | K. TORRES CUEVAS | P. DIENE | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>5</v>
+      </c>
+      <c r="E515" t="n">
+        <v>50</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G515" t="n">
+        <v>2</v>
+      </c>
+      <c r="H515" t="n">
+        <v>2</v>
+      </c>
+      <c r="I515" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J515" t="n">
+        <v>1</v>
+      </c>
+      <c r="K515" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L515" t="n">
+        <v>200</v>
+      </c>
+      <c r="M515" t="n">
+        <v>-93.62</v>
+      </c>
+      <c r="N515" t="n">
+        <v>1</v>
+      </c>
+      <c r="O515" t="n">
+        <v>2</v>
+      </c>
+      <c r="P515" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>0</v>
+      </c>
+      <c r="R515" t="n">
+        <v>1</v>
+      </c>
+      <c r="S515" t="n">
+        <v>0</v>
+      </c>
+      <c r="T515" t="n">
+        <v>0</v>
+      </c>
+      <c r="U515" t="n">
+        <v>0</v>
+      </c>
+      <c r="V515" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W515" t="n">
+        <v>24</v>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>C. JACOBS | H. ARBOSA ROLDAN | M. DE PABLO DEL CASTILLO | P. DIENE | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>5</v>
+      </c>
+      <c r="E516" t="n">
+        <v>21</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G516" t="n">
+        <v>0</v>
+      </c>
+      <c r="H516" t="n">
+        <v>2</v>
+      </c>
+      <c r="I516" t="n">
+        <v>1</v>
+      </c>
+      <c r="J516" t="n">
+        <v>1</v>
+      </c>
+      <c r="K516" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" t="n">
+        <v>200</v>
+      </c>
+      <c r="M516" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N516" t="n">
+        <v>1</v>
+      </c>
+      <c r="O516" t="n">
+        <v>0</v>
+      </c>
+      <c r="P516" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>0</v>
+      </c>
+      <c r="R516" t="n">
+        <v>1</v>
+      </c>
+      <c r="S516" t="n">
+        <v>0</v>
+      </c>
+      <c r="T516" t="n">
+        <v>0</v>
+      </c>
+      <c r="U516" t="n">
+        <v>0</v>
+      </c>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W516" t="n">
+        <v>24</v>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | G. VERGARA HARBOE | J. MARTINEZ MEGIAS | L. FAIAL</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>5</v>
+      </c>
+      <c r="E517" t="n">
+        <v>9</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G517" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I517" t="n">
+        <v>1</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0</v>
+      </c>
+      <c r="K517" t="n">
+        <v>0</v>
+      </c>
+      <c r="L517" t="n">
+        <v>0</v>
+      </c>
+      <c r="M517" t="n">
+        <v>0</v>
+      </c>
+      <c r="N517" t="n">
+        <v>0</v>
+      </c>
+      <c r="O517" t="n">
+        <v>0</v>
+      </c>
+      <c r="P517" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>0</v>
+      </c>
+      <c r="R517" t="n">
+        <v>0</v>
+      </c>
+      <c r="S517" t="n">
+        <v>0</v>
+      </c>
+      <c r="T517" t="n">
+        <v>0</v>
+      </c>
+      <c r="U517" t="n">
+        <v>0</v>
+      </c>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W517" t="n">
+        <v>24</v>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | L. FAIAL</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>5</v>
+      </c>
+      <c r="E518" t="n">
+        <v>120</v>
+      </c>
+      <c r="F518" t="n">
+        <v>2</v>
+      </c>
+      <c r="G518" t="n">
+        <v>4</v>
+      </c>
+      <c r="H518" t="n">
+        <v>6</v>
+      </c>
+      <c r="I518" t="n">
+        <v>3</v>
+      </c>
+      <c r="J518" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K518" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L518" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M518" t="n">
+        <v>-93.94</v>
+      </c>
+      <c r="N518" t="n">
+        <v>3</v>
+      </c>
+      <c r="O518" t="n">
+        <v>0</v>
+      </c>
+      <c r="P518" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>0</v>
+      </c>
+      <c r="R518" t="n">
+        <v>2</v>
+      </c>
+      <c r="S518" t="n">
+        <v>6</v>
+      </c>
+      <c r="T518" t="n">
+        <v>0</v>
+      </c>
+      <c r="U518" t="n">
+        <v>2</v>
+      </c>
+      <c r="V518" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W518" t="n">
+        <v>24</v>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. VERGARA HARBOE | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | L. FAIAL</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>5</v>
+      </c>
+      <c r="E519" t="n">
+        <v>91</v>
+      </c>
+      <c r="F519" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G519" t="n">
+        <v>2</v>
+      </c>
+      <c r="H519" t="n">
+        <v>3</v>
+      </c>
+      <c r="I519" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J519" t="n">
+        <v>3</v>
+      </c>
+      <c r="K519" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L519" t="n">
+        <v>100</v>
+      </c>
+      <c r="M519" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="N519" t="n">
+        <v>4</v>
+      </c>
+      <c r="O519" t="n">
+        <v>2</v>
+      </c>
+      <c r="P519" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q519" t="n">
+        <v>3</v>
+      </c>
+      <c r="R519" t="n">
+        <v>2</v>
+      </c>
+      <c r="S519" t="n">
+        <v>0</v>
+      </c>
+      <c r="T519" t="n">
+        <v>1</v>
+      </c>
+      <c r="U519" t="n">
+        <v>0</v>
+      </c>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W519" t="n">
+        <v>24</v>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>I. HANEY | I. ORDOÑEZ OCHOA | J. GARCIA-ABRIL GUERRERO | M. OCHI | P. ISERN MAZA</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>5</v>
+      </c>
+      <c r="E520" t="n">
+        <v>65</v>
+      </c>
+      <c r="F520" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G520" t="n">
+        <v>3</v>
+      </c>
+      <c r="H520" t="n">
+        <v>0</v>
+      </c>
+      <c r="I520" t="n">
+        <v>2</v>
+      </c>
+      <c r="J520" t="n">
+        <v>2</v>
+      </c>
+      <c r="K520" t="n">
+        <v>150</v>
+      </c>
+      <c r="L520" t="n">
+        <v>0</v>
+      </c>
+      <c r="M520" t="n">
+        <v>150</v>
+      </c>
+      <c r="N520" t="n">
+        <v>1</v>
+      </c>
+      <c r="O520" t="n">
+        <v>0</v>
+      </c>
+      <c r="P520" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>0</v>
+      </c>
+      <c r="R520" t="n">
+        <v>3</v>
+      </c>
+      <c r="S520" t="n">
+        <v>0</v>
+      </c>
+      <c r="T520" t="n">
+        <v>0</v>
+      </c>
+      <c r="U520" t="n">
+        <v>1</v>
+      </c>
+      <c r="V520" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W520" t="n">
+        <v>24</v>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>I. HANEY | I. ORDOÑEZ OCHOA | J. GARCIA-ABRIL GUERRERO | M. OCHI | P. MARIN FONTAN</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>5</v>
+      </c>
+      <c r="E521" t="n">
+        <v>146</v>
+      </c>
+      <c r="F521" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G521" t="n">
+        <v>6</v>
+      </c>
+      <c r="H521" t="n">
+        <v>6</v>
+      </c>
+      <c r="I521" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J521" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K521" t="n">
+        <v>164.84</v>
+      </c>
+      <c r="L521" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M521" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="N521" t="n">
+        <v>3</v>
+      </c>
+      <c r="O521" t="n">
+        <v>6</v>
+      </c>
+      <c r="P521" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q521" t="n">
+        <v>2</v>
+      </c>
+      <c r="R521" t="n">
+        <v>4</v>
+      </c>
+      <c r="S521" t="n">
+        <v>2</v>
+      </c>
+      <c r="T521" t="n">
+        <v>0</v>
+      </c>
+      <c r="U521" t="n">
+        <v>2</v>
+      </c>
+      <c r="V521" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W521" t="n">
+        <v>24</v>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>I. HANEY | I. ORDOÑEZ OCHOA | M. OCHI | P. ISERN MAZA | P. MARIN FONTAN</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>5</v>
+      </c>
+      <c r="E522" t="n">
+        <v>9</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" t="n">
+        <v>1</v>
+      </c>
+      <c r="K522" t="n">
+        <v>0</v>
+      </c>
+      <c r="L522" t="n">
+        <v>0</v>
+      </c>
+      <c r="M522" t="n">
+        <v>0</v>
+      </c>
+      <c r="N522" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" t="n">
+        <v>0</v>
+      </c>
+      <c r="P522" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>0</v>
+      </c>
+      <c r="R522" t="n">
+        <v>0</v>
+      </c>
+      <c r="S522" t="n">
+        <v>0</v>
+      </c>
+      <c r="T522" t="n">
+        <v>1</v>
+      </c>
+      <c r="U522" t="n">
+        <v>0</v>
+      </c>
+      <c r="V522" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W522" t="n">
+        <v>24</v>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>I. AIZPITARTE ARANZA | J. CEBOLLA HERRERA | M. OLAIZOLA GARIN | N. WILLIAMS | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>5</v>
+      </c>
+      <c r="E523" t="n">
+        <v>33</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" t="n">
+        <v>5</v>
+      </c>
+      <c r="I523" t="n">
+        <v>1</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" t="n">
+        <v>568.1799999999999</v>
+      </c>
+      <c r="M523" t="n">
+        <v>-568.1799999999999</v>
+      </c>
+      <c r="N523" t="n">
+        <v>1</v>
+      </c>
+      <c r="O523" t="n">
+        <v>0</v>
+      </c>
+      <c r="P523" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>0</v>
+      </c>
+      <c r="R523" t="n">
+        <v>1</v>
+      </c>
+      <c r="S523" t="n">
+        <v>2</v>
+      </c>
+      <c r="T523" t="n">
+        <v>0</v>
+      </c>
+      <c r="U523" t="n">
+        <v>1</v>
+      </c>
+      <c r="V523" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W523" t="n">
+        <v>24</v>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>I. AIZPITARTE ARANZA | M. NIANG NDONGO | N. WILLIAMS | O. INDA HERNANDEZ | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>5</v>
+      </c>
+      <c r="E524" t="n">
+        <v>228</v>
+      </c>
+      <c r="F524" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G524" t="n">
+        <v>11</v>
+      </c>
+      <c r="H524" t="n">
+        <v>5</v>
+      </c>
+      <c r="I524" t="n">
+        <v>4</v>
+      </c>
+      <c r="J524" t="n">
+        <v>4</v>
+      </c>
+      <c r="K524" t="n">
+        <v>275</v>
+      </c>
+      <c r="L524" t="n">
+        <v>125</v>
+      </c>
+      <c r="M524" t="n">
+        <v>150</v>
+      </c>
+      <c r="N524" t="n">
+        <v>6</v>
+      </c>
+      <c r="O524" t="n">
+        <v>0</v>
+      </c>
+      <c r="P524" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>2</v>
+      </c>
+      <c r="R524" t="n">
+        <v>5</v>
+      </c>
+      <c r="S524" t="n">
+        <v>0</v>
+      </c>
+      <c r="T524" t="n">
+        <v>0</v>
+      </c>
+      <c r="U524" t="n">
+        <v>1</v>
+      </c>
+      <c r="V524" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W524" t="n">
+        <v>24</v>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>I. MIRANDA GARCIA | M. NIANG NDONGO | N. WILLIAMS | O. INDA HERNANDEZ | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>5</v>
+      </c>
+      <c r="E525" t="n">
+        <v>9</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G525" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" t="n">
+        <v>0</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" t="n">
+        <v>1</v>
+      </c>
+      <c r="K525" t="n">
+        <v>0</v>
+      </c>
+      <c r="L525" t="n">
+        <v>0</v>
+      </c>
+      <c r="M525" t="n">
+        <v>0</v>
+      </c>
+      <c r="N525" t="n">
+        <v>0</v>
+      </c>
+      <c r="O525" t="n">
+        <v>0</v>
+      </c>
+      <c r="P525" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>0</v>
+      </c>
+      <c r="R525" t="n">
+        <v>1</v>
+      </c>
+      <c r="S525" t="n">
+        <v>0</v>
+      </c>
+      <c r="T525" t="n">
+        <v>0</v>
+      </c>
+      <c r="U525" t="n">
+        <v>0</v>
+      </c>
+      <c r="V525" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W525" t="n">
+        <v>24</v>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>J. CEBOLLA HERRERA | M. OLAIZOLA GARIN | N. WILLIAMS | O. ARDANZA BERNAOLA | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>5</v>
+      </c>
+      <c r="E526" t="n">
+        <v>7</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G526" t="n">
+        <v>0</v>
+      </c>
+      <c r="H526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" t="n">
+        <v>1</v>
+      </c>
+      <c r="J526" t="n">
+        <v>0</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" t="n">
+        <v>0</v>
+      </c>
+      <c r="M526" t="n">
+        <v>0</v>
+      </c>
+      <c r="N526" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" t="n">
+        <v>0</v>
+      </c>
+      <c r="P526" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q526" t="n">
+        <v>0</v>
+      </c>
+      <c r="R526" t="n">
+        <v>1</v>
+      </c>
+      <c r="S526" t="n">
+        <v>0</v>
+      </c>
+      <c r="T526" t="n">
+        <v>0</v>
+      </c>
+      <c r="U526" t="n">
+        <v>1</v>
+      </c>
+      <c r="V526" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W526" t="n">
+        <v>24</v>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>5</v>
+      </c>
+      <c r="E527" t="n">
+        <v>7</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G527" t="n">
+        <v>0</v>
+      </c>
+      <c r="H527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="n">
+        <v>1</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0</v>
+      </c>
+      <c r="L527" t="n">
+        <v>0</v>
+      </c>
+      <c r="M527" t="n">
+        <v>0</v>
+      </c>
+      <c r="N527" t="n">
+        <v>1</v>
+      </c>
+      <c r="O527" t="n">
+        <v>0</v>
+      </c>
+      <c r="P527" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q527" t="n">
+        <v>1</v>
+      </c>
+      <c r="R527" t="n">
+        <v>0</v>
+      </c>
+      <c r="S527" t="n">
+        <v>0</v>
+      </c>
+      <c r="T527" t="n">
+        <v>1</v>
+      </c>
+      <c r="U527" t="n">
+        <v>0</v>
+      </c>
+      <c r="V527" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W527" t="n">
+        <v>24</v>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>5</v>
+      </c>
+      <c r="E528" t="n">
+        <v>33</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G528" t="n">
+        <v>5</v>
+      </c>
+      <c r="H528" t="n">
+        <v>0</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J528" t="n">
+        <v>1</v>
+      </c>
+      <c r="K528" t="n">
+        <v>568.1799999999999</v>
+      </c>
+      <c r="L528" t="n">
+        <v>0</v>
+      </c>
+      <c r="M528" t="n">
+        <v>568.1799999999999</v>
+      </c>
+      <c r="N528" t="n">
+        <v>1</v>
+      </c>
+      <c r="O528" t="n">
+        <v>2</v>
+      </c>
+      <c r="P528" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q528" t="n">
+        <v>1</v>
+      </c>
+      <c r="R528" t="n">
+        <v>1</v>
+      </c>
+      <c r="S528" t="n">
+        <v>0</v>
+      </c>
+      <c r="T528" t="n">
+        <v>0</v>
+      </c>
+      <c r="U528" t="n">
+        <v>0</v>
+      </c>
+      <c r="V528" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W528" t="n">
+        <v>24</v>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>5</v>
+      </c>
+      <c r="E529" t="n">
+        <v>27</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G529" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" t="n">
+        <v>2</v>
+      </c>
+      <c r="I529" t="n">
+        <v>1</v>
+      </c>
+      <c r="J529" t="n">
+        <v>1</v>
+      </c>
+      <c r="K529" t="n">
+        <v>0</v>
+      </c>
+      <c r="L529" t="n">
+        <v>200</v>
+      </c>
+      <c r="M529" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N529" t="n">
+        <v>1</v>
+      </c>
+      <c r="O529" t="n">
+        <v>0</v>
+      </c>
+      <c r="P529" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q529" t="n">
+        <v>0</v>
+      </c>
+      <c r="R529" t="n">
+        <v>1</v>
+      </c>
+      <c r="S529" t="n">
+        <v>0</v>
+      </c>
+      <c r="T529" t="n">
+        <v>0</v>
+      </c>
+      <c r="U529" t="n">
+        <v>0</v>
+      </c>
+      <c r="V529" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W529" t="n">
+        <v>24</v>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>5</v>
+      </c>
+      <c r="E530" t="n">
+        <v>48</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G530" t="n">
+        <v>0</v>
+      </c>
+      <c r="H530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" t="n">
+        <v>1</v>
+      </c>
+      <c r="J530" t="n">
+        <v>0</v>
+      </c>
+      <c r="K530" t="n">
+        <v>0</v>
+      </c>
+      <c r="L530" t="n">
+        <v>0</v>
+      </c>
+      <c r="M530" t="n">
+        <v>0</v>
+      </c>
+      <c r="N530" t="n">
+        <v>1</v>
+      </c>
+      <c r="O530" t="n">
+        <v>0</v>
+      </c>
+      <c r="P530" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q530" t="n">
+        <v>0</v>
+      </c>
+      <c r="R530" t="n">
+        <v>0</v>
+      </c>
+      <c r="S530" t="n">
+        <v>0</v>
+      </c>
+      <c r="T530" t="n">
+        <v>0</v>
+      </c>
+      <c r="U530" t="n">
+        <v>0</v>
+      </c>
+      <c r="V530" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W530" t="n">
+        <v>24</v>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>5</v>
+      </c>
+      <c r="E531" t="n">
+        <v>162</v>
+      </c>
+      <c r="F531" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G531" t="n">
+        <v>5</v>
+      </c>
+      <c r="H531" t="n">
+        <v>9</v>
+      </c>
+      <c r="I531" t="n">
+        <v>3</v>
+      </c>
+      <c r="J531" t="n">
+        <v>3</v>
+      </c>
+      <c r="K531" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L531" t="n">
+        <v>300</v>
+      </c>
+      <c r="M531" t="n">
+        <v>-133.33</v>
+      </c>
+      <c r="N531" t="n">
+        <v>4</v>
+      </c>
+      <c r="O531" t="n">
+        <v>0</v>
+      </c>
+      <c r="P531" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q531" t="n">
+        <v>1</v>
+      </c>
+      <c r="R531" t="n">
+        <v>5</v>
+      </c>
+      <c r="S531" t="n">
+        <v>0</v>
+      </c>
+      <c r="T531" t="n">
+        <v>0</v>
+      </c>
+      <c r="U531" t="n">
+        <v>2</v>
+      </c>
+      <c r="V531" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W531" t="n">
+        <v>24</v>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
+++ b/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X484"/>
+  <dimension ref="A1:X549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41122,6 +41122,5466 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS | D. ORRIT SERRANO | J. BERGENS | N. OKEKE | R. HAYES</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>5</v>
+      </c>
+      <c r="E485" t="n">
+        <v>79</v>
+      </c>
+      <c r="F485" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G485" t="n">
+        <v>0</v>
+      </c>
+      <c r="H485" t="n">
+        <v>3</v>
+      </c>
+      <c r="I485" t="n">
+        <v>1</v>
+      </c>
+      <c r="J485" t="n">
+        <v>2</v>
+      </c>
+      <c r="K485" t="n">
+        <v>0</v>
+      </c>
+      <c r="L485" t="n">
+        <v>150</v>
+      </c>
+      <c r="M485" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N485" t="n">
+        <v>0</v>
+      </c>
+      <c r="O485" t="n">
+        <v>0</v>
+      </c>
+      <c r="P485" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>0</v>
+      </c>
+      <c r="R485" t="n">
+        <v>2</v>
+      </c>
+      <c r="S485" t="n">
+        <v>0</v>
+      </c>
+      <c r="T485" t="n">
+        <v>1</v>
+      </c>
+      <c r="U485" t="n">
+        <v>1</v>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W485" t="n">
+        <v>24</v>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS | J. BERGENS | J. CERA RODRIGUEZ | N. OKEKE | R. HAYES</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>5</v>
+      </c>
+      <c r="E486" t="n">
+        <v>129</v>
+      </c>
+      <c r="F486" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G486" t="n">
+        <v>10</v>
+      </c>
+      <c r="H486" t="n">
+        <v>6</v>
+      </c>
+      <c r="I486" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J486" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="K486" t="n">
+        <v>210.08</v>
+      </c>
+      <c r="L486" t="n">
+        <v>164.84</v>
+      </c>
+      <c r="M486" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="N486" t="n">
+        <v>4</v>
+      </c>
+      <c r="O486" t="n">
+        <v>4</v>
+      </c>
+      <c r="P486" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>1</v>
+      </c>
+      <c r="R486" t="n">
+        <v>1</v>
+      </c>
+      <c r="S486" t="n">
+        <v>6</v>
+      </c>
+      <c r="T486" t="n">
+        <v>1</v>
+      </c>
+      <c r="U486" t="n">
+        <v>1</v>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W486" t="n">
+        <v>24</v>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS | J. BERGENS | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>5</v>
+      </c>
+      <c r="E487" t="n">
+        <v>22</v>
+      </c>
+      <c r="F487" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G487" t="n">
+        <v>0</v>
+      </c>
+      <c r="H487" t="n">
+        <v>0</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0</v>
+      </c>
+      <c r="J487" t="n">
+        <v>1</v>
+      </c>
+      <c r="K487" t="n">
+        <v>0</v>
+      </c>
+      <c r="L487" t="n">
+        <v>0</v>
+      </c>
+      <c r="M487" t="n">
+        <v>0</v>
+      </c>
+      <c r="N487" t="n">
+        <v>0</v>
+      </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
+      <c r="P487" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>0</v>
+      </c>
+      <c r="R487" t="n">
+        <v>0</v>
+      </c>
+      <c r="S487" t="n">
+        <v>0</v>
+      </c>
+      <c r="T487" t="n">
+        <v>1</v>
+      </c>
+      <c r="U487" t="n">
+        <v>0</v>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W487" t="n">
+        <v>24</v>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>D. ORRIT SERRANO | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>5</v>
+      </c>
+      <c r="E488" t="n">
+        <v>10</v>
+      </c>
+      <c r="F488" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G488" t="n">
+        <v>0</v>
+      </c>
+      <c r="H488" t="n">
+        <v>0</v>
+      </c>
+      <c r="I488" t="n">
+        <v>0</v>
+      </c>
+      <c r="J488" t="n">
+        <v>1</v>
+      </c>
+      <c r="K488" t="n">
+        <v>0</v>
+      </c>
+      <c r="L488" t="n">
+        <v>0</v>
+      </c>
+      <c r="M488" t="n">
+        <v>0</v>
+      </c>
+      <c r="N488" t="n">
+        <v>0</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="P488" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>0</v>
+      </c>
+      <c r="R488" t="n">
+        <v>2</v>
+      </c>
+      <c r="S488" t="n">
+        <v>0</v>
+      </c>
+      <c r="T488" t="n">
+        <v>0</v>
+      </c>
+      <c r="U488" t="n">
+        <v>1</v>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W488" t="n">
+        <v>24</v>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>J. BERGENS | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>5</v>
+      </c>
+      <c r="E489" t="n">
+        <v>332</v>
+      </c>
+      <c r="F489" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G489" t="n">
+        <v>8</v>
+      </c>
+      <c r="H489" t="n">
+        <v>8</v>
+      </c>
+      <c r="I489" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="J489" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K489" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="L489" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="M489" t="n">
+        <v>-30.39</v>
+      </c>
+      <c r="N489" t="n">
+        <v>10</v>
+      </c>
+      <c r="O489" t="n">
+        <v>2</v>
+      </c>
+      <c r="P489" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>2</v>
+      </c>
+      <c r="R489" t="n">
+        <v>6</v>
+      </c>
+      <c r="S489" t="n">
+        <v>6</v>
+      </c>
+      <c r="T489" t="n">
+        <v>1</v>
+      </c>
+      <c r="U489" t="n">
+        <v>3</v>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W489" t="n">
+        <v>24</v>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>4</v>
+      </c>
+      <c r="E490" t="n">
+        <v>27</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G490" t="n">
+        <v>1</v>
+      </c>
+      <c r="H490" t="n">
+        <v>0</v>
+      </c>
+      <c r="I490" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J490" t="n">
+        <v>1</v>
+      </c>
+      <c r="K490" t="n">
+        <v>0</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" t="n">
+        <v>0</v>
+      </c>
+      <c r="N490" t="n">
+        <v>0</v>
+      </c>
+      <c r="O490" t="n">
+        <v>2</v>
+      </c>
+      <c r="P490" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>1</v>
+      </c>
+      <c r="R490" t="n">
+        <v>1</v>
+      </c>
+      <c r="S490" t="n">
+        <v>0</v>
+      </c>
+      <c r="T490" t="n">
+        <v>0</v>
+      </c>
+      <c r="U490" t="n">
+        <v>0</v>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W490" t="n">
+        <v>24</v>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK | A. INFANTE GUTIERREZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>5</v>
+      </c>
+      <c r="E491" t="n">
+        <v>31</v>
+      </c>
+      <c r="F491" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G491" t="n">
+        <v>2</v>
+      </c>
+      <c r="H491" t="n">
+        <v>0</v>
+      </c>
+      <c r="I491" t="n">
+        <v>1</v>
+      </c>
+      <c r="J491" t="n">
+        <v>0</v>
+      </c>
+      <c r="K491" t="n">
+        <v>200</v>
+      </c>
+      <c r="L491" t="n">
+        <v>0</v>
+      </c>
+      <c r="M491" t="n">
+        <v>0</v>
+      </c>
+      <c r="N491" t="n">
+        <v>1</v>
+      </c>
+      <c r="O491" t="n">
+        <v>0</v>
+      </c>
+      <c r="P491" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>0</v>
+      </c>
+      <c r="R491" t="n">
+        <v>0</v>
+      </c>
+      <c r="S491" t="n">
+        <v>0</v>
+      </c>
+      <c r="T491" t="n">
+        <v>0</v>
+      </c>
+      <c r="U491" t="n">
+        <v>0</v>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W491" t="n">
+        <v>24</v>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>5</v>
+      </c>
+      <c r="E492" t="n">
+        <v>27</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G492" t="n">
+        <v>0</v>
+      </c>
+      <c r="H492" t="n">
+        <v>2</v>
+      </c>
+      <c r="I492" t="n">
+        <v>1</v>
+      </c>
+      <c r="J492" t="n">
+        <v>1</v>
+      </c>
+      <c r="K492" t="n">
+        <v>0</v>
+      </c>
+      <c r="L492" t="n">
+        <v>200</v>
+      </c>
+      <c r="M492" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N492" t="n">
+        <v>1</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
+      <c r="P492" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>0</v>
+      </c>
+      <c r="R492" t="n">
+        <v>1</v>
+      </c>
+      <c r="S492" t="n">
+        <v>0</v>
+      </c>
+      <c r="T492" t="n">
+        <v>0</v>
+      </c>
+      <c r="U492" t="n">
+        <v>0</v>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W492" t="n">
+        <v>24</v>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>5</v>
+      </c>
+      <c r="E493" t="n">
+        <v>50</v>
+      </c>
+      <c r="F493" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G493" t="n">
+        <v>0</v>
+      </c>
+      <c r="H493" t="n">
+        <v>2</v>
+      </c>
+      <c r="I493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J493" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0</v>
+      </c>
+      <c r="L493" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M493" t="n">
+        <v>0</v>
+      </c>
+      <c r="N493" t="n">
+        <v>1</v>
+      </c>
+      <c r="O493" t="n">
+        <v>0</v>
+      </c>
+      <c r="P493" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>1</v>
+      </c>
+      <c r="R493" t="n">
+        <v>1</v>
+      </c>
+      <c r="S493" t="n">
+        <v>2</v>
+      </c>
+      <c r="T493" t="n">
+        <v>0</v>
+      </c>
+      <c r="U493" t="n">
+        <v>0</v>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W493" t="n">
+        <v>24</v>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | L. OBAJO BELTRAN | P. SALL</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>5</v>
+      </c>
+      <c r="E494" t="n">
+        <v>85</v>
+      </c>
+      <c r="F494" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G494" t="n">
+        <v>3</v>
+      </c>
+      <c r="H494" t="n">
+        <v>4</v>
+      </c>
+      <c r="I494" t="n">
+        <v>2</v>
+      </c>
+      <c r="J494" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K494" t="n">
+        <v>150</v>
+      </c>
+      <c r="L494" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="M494" t="n">
+        <v>-62.77</v>
+      </c>
+      <c r="N494" t="n">
+        <v>1</v>
+      </c>
+      <c r="O494" t="n">
+        <v>0</v>
+      </c>
+      <c r="P494" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>0</v>
+      </c>
+      <c r="R494" t="n">
+        <v>1</v>
+      </c>
+      <c r="S494" t="n">
+        <v>2</v>
+      </c>
+      <c r="T494" t="n">
+        <v>0</v>
+      </c>
+      <c r="U494" t="n">
+        <v>0</v>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W494" t="n">
+        <v>24</v>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>5</v>
+      </c>
+      <c r="E495" t="n">
+        <v>123</v>
+      </c>
+      <c r="F495" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G495" t="n">
+        <v>6</v>
+      </c>
+      <c r="H495" t="n">
+        <v>6</v>
+      </c>
+      <c r="I495" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J495" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K495" t="n">
+        <v>164.84</v>
+      </c>
+      <c r="L495" t="n">
+        <v>154.64</v>
+      </c>
+      <c r="M495" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N495" t="n">
+        <v>2</v>
+      </c>
+      <c r="O495" t="n">
+        <v>6</v>
+      </c>
+      <c r="P495" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>2</v>
+      </c>
+      <c r="R495" t="n">
+        <v>3</v>
+      </c>
+      <c r="S495" t="n">
+        <v>2</v>
+      </c>
+      <c r="T495" t="n">
+        <v>1</v>
+      </c>
+      <c r="U495" t="n">
+        <v>1</v>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W495" t="n">
+        <v>24</v>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>5</v>
+      </c>
+      <c r="E496" t="n">
+        <v>91</v>
+      </c>
+      <c r="F496" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G496" t="n">
+        <v>4</v>
+      </c>
+      <c r="H496" t="n">
+        <v>3</v>
+      </c>
+      <c r="I496" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J496" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K496" t="n">
+        <v>144.93</v>
+      </c>
+      <c r="L496" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="M496" t="n">
+        <v>-14.65</v>
+      </c>
+      <c r="N496" t="n">
+        <v>2</v>
+      </c>
+      <c r="O496" t="n">
+        <v>4</v>
+      </c>
+      <c r="P496" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>1</v>
+      </c>
+      <c r="R496" t="n">
+        <v>2</v>
+      </c>
+      <c r="S496" t="n">
+        <v>2</v>
+      </c>
+      <c r="T496" t="n">
+        <v>0</v>
+      </c>
+      <c r="U496" t="n">
+        <v>1</v>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W496" t="n">
+        <v>24</v>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>5</v>
+      </c>
+      <c r="E497" t="n">
+        <v>10</v>
+      </c>
+      <c r="F497" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G497" t="n">
+        <v>0</v>
+      </c>
+      <c r="H497" t="n">
+        <v>0</v>
+      </c>
+      <c r="I497" t="n">
+        <v>1</v>
+      </c>
+      <c r="J497" t="n">
+        <v>0</v>
+      </c>
+      <c r="K497" t="n">
+        <v>0</v>
+      </c>
+      <c r="L497" t="n">
+        <v>0</v>
+      </c>
+      <c r="M497" t="n">
+        <v>0</v>
+      </c>
+      <c r="N497" t="n">
+        <v>2</v>
+      </c>
+      <c r="O497" t="n">
+        <v>0</v>
+      </c>
+      <c r="P497" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>1</v>
+      </c>
+      <c r="R497" t="n">
+        <v>0</v>
+      </c>
+      <c r="S497" t="n">
+        <v>0</v>
+      </c>
+      <c r="T497" t="n">
+        <v>0</v>
+      </c>
+      <c r="U497" t="n">
+        <v>0</v>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W497" t="n">
+        <v>24</v>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>5</v>
+      </c>
+      <c r="E498" t="n">
+        <v>182</v>
+      </c>
+      <c r="F498" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G498" t="n">
+        <v>2</v>
+      </c>
+      <c r="H498" t="n">
+        <v>2</v>
+      </c>
+      <c r="I498" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J498" t="n">
+        <v>4</v>
+      </c>
+      <c r="K498" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="L498" t="n">
+        <v>50</v>
+      </c>
+      <c r="M498" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N498" t="n">
+        <v>2</v>
+      </c>
+      <c r="O498" t="n">
+        <v>2</v>
+      </c>
+      <c r="P498" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>1</v>
+      </c>
+      <c r="R498" t="n">
+        <v>6</v>
+      </c>
+      <c r="S498" t="n">
+        <v>0</v>
+      </c>
+      <c r="T498" t="n">
+        <v>0</v>
+      </c>
+      <c r="U498" t="n">
+        <v>2</v>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W498" t="n">
+        <v>24</v>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>A. CALVO TORRES | C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | J. LACUNZA ABECIA</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>5</v>
+      </c>
+      <c r="E499" t="n">
+        <v>9</v>
+      </c>
+      <c r="F499" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G499" t="n">
+        <v>0</v>
+      </c>
+      <c r="H499" t="n">
+        <v>2</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0</v>
+      </c>
+      <c r="J499" t="n">
+        <v>1</v>
+      </c>
+      <c r="K499" t="n">
+        <v>0</v>
+      </c>
+      <c r="L499" t="n">
+        <v>200</v>
+      </c>
+      <c r="M499" t="n">
+        <v>0</v>
+      </c>
+      <c r="N499" t="n">
+        <v>0</v>
+      </c>
+      <c r="O499" t="n">
+        <v>0</v>
+      </c>
+      <c r="P499" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>0</v>
+      </c>
+      <c r="R499" t="n">
+        <v>1</v>
+      </c>
+      <c r="S499" t="n">
+        <v>0</v>
+      </c>
+      <c r="T499" t="n">
+        <v>0</v>
+      </c>
+      <c r="U499" t="n">
+        <v>0</v>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W499" t="n">
+        <v>24</v>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>A. CALVO TORRES | C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | P. YARNOZ LUMBRERAS</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>5</v>
+      </c>
+      <c r="E500" t="n">
+        <v>33</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G500" t="n">
+        <v>3</v>
+      </c>
+      <c r="H500" t="n">
+        <v>0</v>
+      </c>
+      <c r="I500" t="n">
+        <v>2</v>
+      </c>
+      <c r="J500" t="n">
+        <v>0</v>
+      </c>
+      <c r="K500" t="n">
+        <v>150</v>
+      </c>
+      <c r="L500" t="n">
+        <v>0</v>
+      </c>
+      <c r="M500" t="n">
+        <v>0</v>
+      </c>
+      <c r="N500" t="n">
+        <v>2</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
+      <c r="P500" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>0</v>
+      </c>
+      <c r="R500" t="n">
+        <v>0</v>
+      </c>
+      <c r="S500" t="n">
+        <v>0</v>
+      </c>
+      <c r="T500" t="n">
+        <v>0</v>
+      </c>
+      <c r="U500" t="n">
+        <v>0</v>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W500" t="n">
+        <v>24</v>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | J. LACUNZA ABECIA | P. YARNOZ LUMBRERAS</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>5</v>
+      </c>
+      <c r="E501" t="n">
+        <v>248</v>
+      </c>
+      <c r="F501" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="G501" t="n">
+        <v>13</v>
+      </c>
+      <c r="H501" t="n">
+        <v>14</v>
+      </c>
+      <c r="I501" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="J501" t="n">
+        <v>8</v>
+      </c>
+      <c r="K501" t="n">
+        <v>195.78</v>
+      </c>
+      <c r="L501" t="n">
+        <v>175</v>
+      </c>
+      <c r="M501" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="N501" t="n">
+        <v>7</v>
+      </c>
+      <c r="O501" t="n">
+        <v>6</v>
+      </c>
+      <c r="P501" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>3</v>
+      </c>
+      <c r="R501" t="n">
+        <v>9</v>
+      </c>
+      <c r="S501" t="n">
+        <v>0</v>
+      </c>
+      <c r="T501" t="n">
+        <v>0</v>
+      </c>
+      <c r="U501" t="n">
+        <v>1</v>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W501" t="n">
+        <v>24</v>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. BARROS GARCIA</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>5</v>
+      </c>
+      <c r="E502" t="n">
+        <v>9</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G502" t="n">
+        <v>2</v>
+      </c>
+      <c r="H502" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" t="n">
+        <v>1</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0</v>
+      </c>
+      <c r="K502" t="n">
+        <v>200</v>
+      </c>
+      <c r="L502" t="n">
+        <v>0</v>
+      </c>
+      <c r="M502" t="n">
+        <v>0</v>
+      </c>
+      <c r="N502" t="n">
+        <v>1</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>0</v>
+      </c>
+      <c r="R502" t="n">
+        <v>0</v>
+      </c>
+      <c r="S502" t="n">
+        <v>0</v>
+      </c>
+      <c r="T502" t="n">
+        <v>0</v>
+      </c>
+      <c r="U502" t="n">
+        <v>0</v>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W502" t="n">
+        <v>24</v>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>5</v>
+      </c>
+      <c r="E503" t="n">
+        <v>124</v>
+      </c>
+      <c r="F503" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G503" t="n">
+        <v>7</v>
+      </c>
+      <c r="H503" t="n">
+        <v>5</v>
+      </c>
+      <c r="I503" t="n">
+        <v>4</v>
+      </c>
+      <c r="J503" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K503" t="n">
+        <v>175</v>
+      </c>
+      <c r="L503" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M503" t="n">
+        <v>-52.27</v>
+      </c>
+      <c r="N503" t="n">
+        <v>5</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
+      <c r="P503" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>1</v>
+      </c>
+      <c r="R503" t="n">
+        <v>2</v>
+      </c>
+      <c r="S503" t="n">
+        <v>5</v>
+      </c>
+      <c r="T503" t="n">
+        <v>0</v>
+      </c>
+      <c r="U503" t="n">
+        <v>2</v>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W503" t="n">
+        <v>24</v>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | J. MENENDEZ GARCIA | M. OKAFOR AUGUSTIN | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>5</v>
+      </c>
+      <c r="E504" t="n">
+        <v>24</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G504" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" t="n">
+        <v>3</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K504" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M504" t="n">
+        <v>0</v>
+      </c>
+      <c r="N504" t="n">
+        <v>0</v>
+      </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>0</v>
+      </c>
+      <c r="R504" t="n">
+        <v>1</v>
+      </c>
+      <c r="S504" t="n">
+        <v>1</v>
+      </c>
+      <c r="T504" t="n">
+        <v>0</v>
+      </c>
+      <c r="U504" t="n">
+        <v>0</v>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W504" t="n">
+        <v>24</v>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. BARROS GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>5</v>
+      </c>
+      <c r="E505" t="n">
+        <v>24</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G505" t="n">
+        <v>0</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>1</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" t="n">
+        <v>0</v>
+      </c>
+      <c r="M505" t="n">
+        <v>0</v>
+      </c>
+      <c r="N505" t="n">
+        <v>0</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>0</v>
+      </c>
+      <c r="R505" t="n">
+        <v>1</v>
+      </c>
+      <c r="S505" t="n">
+        <v>0</v>
+      </c>
+      <c r="T505" t="n">
+        <v>0</v>
+      </c>
+      <c r="U505" t="n">
+        <v>0</v>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W505" t="n">
+        <v>24</v>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | I. DUKE TOUSSAINT | S. BARROS GARCIA | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>5</v>
+      </c>
+      <c r="E506" t="n">
+        <v>11</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G506" t="n">
+        <v>2</v>
+      </c>
+      <c r="H506" t="n">
+        <v>2</v>
+      </c>
+      <c r="I506" t="n">
+        <v>1</v>
+      </c>
+      <c r="J506" t="n">
+        <v>1</v>
+      </c>
+      <c r="K506" t="n">
+        <v>200</v>
+      </c>
+      <c r="L506" t="n">
+        <v>200</v>
+      </c>
+      <c r="M506" t="n">
+        <v>0</v>
+      </c>
+      <c r="N506" t="n">
+        <v>1</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
+      <c r="P506" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>0</v>
+      </c>
+      <c r="R506" t="n">
+        <v>1</v>
+      </c>
+      <c r="S506" t="n">
+        <v>0</v>
+      </c>
+      <c r="T506" t="n">
+        <v>0</v>
+      </c>
+      <c r="U506" t="n">
+        <v>0</v>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W506" t="n">
+        <v>24</v>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>5</v>
+      </c>
+      <c r="E507" t="n">
+        <v>9</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0</v>
+      </c>
+      <c r="H507" t="n">
+        <v>3</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="n">
+        <v>1</v>
+      </c>
+      <c r="K507" t="n">
+        <v>0</v>
+      </c>
+      <c r="L507" t="n">
+        <v>300</v>
+      </c>
+      <c r="M507" t="n">
+        <v>0</v>
+      </c>
+      <c r="N507" t="n">
+        <v>0</v>
+      </c>
+      <c r="O507" t="n">
+        <v>0</v>
+      </c>
+      <c r="P507" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>0</v>
+      </c>
+      <c r="R507" t="n">
+        <v>1</v>
+      </c>
+      <c r="S507" t="n">
+        <v>0</v>
+      </c>
+      <c r="T507" t="n">
+        <v>0</v>
+      </c>
+      <c r="U507" t="n">
+        <v>0</v>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W507" t="n">
+        <v>24</v>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>G. ARCOS GONZALEZ | J. MENENDEZ GARCIA | M. OKAFOR AUGUSTIN | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>5</v>
+      </c>
+      <c r="E508" t="n">
+        <v>89</v>
+      </c>
+      <c r="F508" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G508" t="n">
+        <v>5</v>
+      </c>
+      <c r="H508" t="n">
+        <v>3</v>
+      </c>
+      <c r="I508" t="n">
+        <v>3</v>
+      </c>
+      <c r="J508" t="n">
+        <v>2</v>
+      </c>
+      <c r="K508" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L508" t="n">
+        <v>150</v>
+      </c>
+      <c r="M508" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="N508" t="n">
+        <v>3</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>0</v>
+      </c>
+      <c r="R508" t="n">
+        <v>3</v>
+      </c>
+      <c r="S508" t="n">
+        <v>0</v>
+      </c>
+      <c r="T508" t="n">
+        <v>0</v>
+      </c>
+      <c r="U508" t="n">
+        <v>1</v>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W508" t="n">
+        <v>24</v>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. KOCIC | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>5</v>
+      </c>
+      <c r="E509" t="n">
+        <v>84</v>
+      </c>
+      <c r="F509" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G509" t="n">
+        <v>2</v>
+      </c>
+      <c r="H509" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" t="n">
+        <v>1</v>
+      </c>
+      <c r="J509" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K509" t="n">
+        <v>200</v>
+      </c>
+      <c r="L509" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M509" t="n">
+        <v>130.56</v>
+      </c>
+      <c r="N509" t="n">
+        <v>2</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0</v>
+      </c>
+      <c r="P509" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>1</v>
+      </c>
+      <c r="R509" t="n">
+        <v>2</v>
+      </c>
+      <c r="S509" t="n">
+        <v>2</v>
+      </c>
+      <c r="T509" t="n">
+        <v>0</v>
+      </c>
+      <c r="U509" t="n">
+        <v>0</v>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W509" t="n">
+        <v>24</v>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>5</v>
+      </c>
+      <c r="E510" t="n">
+        <v>3</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0</v>
+      </c>
+      <c r="H510" t="n">
+        <v>1</v>
+      </c>
+      <c r="I510" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J510" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M510" t="n">
+        <v>0</v>
+      </c>
+      <c r="N510" t="n">
+        <v>0</v>
+      </c>
+      <c r="O510" t="n">
+        <v>0</v>
+      </c>
+      <c r="P510" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>1</v>
+      </c>
+      <c r="R510" t="n">
+        <v>1</v>
+      </c>
+      <c r="S510" t="n">
+        <v>2</v>
+      </c>
+      <c r="T510" t="n">
+        <v>0</v>
+      </c>
+      <c r="U510" t="n">
+        <v>1</v>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W510" t="n">
+        <v>24</v>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. KOCIC | V. MORENO MARTIN | V. STEVANIC</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>5</v>
+      </c>
+      <c r="E511" t="n">
+        <v>40</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G511" t="n">
+        <v>4</v>
+      </c>
+      <c r="H511" t="n">
+        <v>0</v>
+      </c>
+      <c r="I511" t="n">
+        <v>2</v>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="n">
+        <v>200</v>
+      </c>
+      <c r="L511" t="n">
+        <v>0</v>
+      </c>
+      <c r="M511" t="n">
+        <v>200</v>
+      </c>
+      <c r="N511" t="n">
+        <v>2</v>
+      </c>
+      <c r="O511" t="n">
+        <v>0</v>
+      </c>
+      <c r="P511" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>0</v>
+      </c>
+      <c r="R511" t="n">
+        <v>1</v>
+      </c>
+      <c r="S511" t="n">
+        <v>0</v>
+      </c>
+      <c r="T511" t="n">
+        <v>0</v>
+      </c>
+      <c r="U511" t="n">
+        <v>0</v>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W511" t="n">
+        <v>24</v>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>C. JACOBS | E. A NONGO BERTHOLD | H. ARBOSA ROLDAN | J. PARDINA MOLINA | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>5</v>
+      </c>
+      <c r="E512" t="n">
+        <v>3</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G512" t="n">
+        <v>1</v>
+      </c>
+      <c r="H512" t="n">
+        <v>0</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J512" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K512" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L512" t="n">
+        <v>0</v>
+      </c>
+      <c r="M512" t="n">
+        <v>0</v>
+      </c>
+      <c r="N512" t="n">
+        <v>1</v>
+      </c>
+      <c r="O512" t="n">
+        <v>2</v>
+      </c>
+      <c r="P512" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>1</v>
+      </c>
+      <c r="R512" t="n">
+        <v>0</v>
+      </c>
+      <c r="S512" t="n">
+        <v>0</v>
+      </c>
+      <c r="T512" t="n">
+        <v>0</v>
+      </c>
+      <c r="U512" t="n">
+        <v>1</v>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W512" t="n">
+        <v>24</v>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>C. JACOBS | E. A NONGO BERTHOLD | H. ARBOSA ROLDAN | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>5</v>
+      </c>
+      <c r="E513" t="n">
+        <v>19</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G513" t="n">
+        <v>0</v>
+      </c>
+      <c r="H513" t="n">
+        <v>2</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0</v>
+      </c>
+      <c r="J513" t="n">
+        <v>1</v>
+      </c>
+      <c r="K513" t="n">
+        <v>0</v>
+      </c>
+      <c r="L513" t="n">
+        <v>200</v>
+      </c>
+      <c r="M513" t="n">
+        <v>0</v>
+      </c>
+      <c r="N513" t="n">
+        <v>0</v>
+      </c>
+      <c r="O513" t="n">
+        <v>0</v>
+      </c>
+      <c r="P513" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>0</v>
+      </c>
+      <c r="R513" t="n">
+        <v>1</v>
+      </c>
+      <c r="S513" t="n">
+        <v>0</v>
+      </c>
+      <c r="T513" t="n">
+        <v>0</v>
+      </c>
+      <c r="U513" t="n">
+        <v>0</v>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W513" t="n">
+        <v>24</v>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>C. JACOBS | H. ARBOSA ROLDAN | J. PARDINA MOLINA | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>5</v>
+      </c>
+      <c r="E514" t="n">
+        <v>34</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" t="n">
+        <v>1</v>
+      </c>
+      <c r="J514" t="n">
+        <v>0</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" t="n">
+        <v>0</v>
+      </c>
+      <c r="M514" t="n">
+        <v>0</v>
+      </c>
+      <c r="N514" t="n">
+        <v>1</v>
+      </c>
+      <c r="O514" t="n">
+        <v>0</v>
+      </c>
+      <c r="P514" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>0</v>
+      </c>
+      <c r="R514" t="n">
+        <v>1</v>
+      </c>
+      <c r="S514" t="n">
+        <v>0</v>
+      </c>
+      <c r="T514" t="n">
+        <v>0</v>
+      </c>
+      <c r="U514" t="n">
+        <v>1</v>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W514" t="n">
+        <v>24</v>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>C. JACOBS | H. ARBOSA ROLDAN | K. TORRES CUEVAS | P. DIENE | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>5</v>
+      </c>
+      <c r="E515" t="n">
+        <v>50</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G515" t="n">
+        <v>2</v>
+      </c>
+      <c r="H515" t="n">
+        <v>2</v>
+      </c>
+      <c r="I515" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J515" t="n">
+        <v>1</v>
+      </c>
+      <c r="K515" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L515" t="n">
+        <v>200</v>
+      </c>
+      <c r="M515" t="n">
+        <v>-93.62</v>
+      </c>
+      <c r="N515" t="n">
+        <v>1</v>
+      </c>
+      <c r="O515" t="n">
+        <v>2</v>
+      </c>
+      <c r="P515" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>0</v>
+      </c>
+      <c r="R515" t="n">
+        <v>1</v>
+      </c>
+      <c r="S515" t="n">
+        <v>0</v>
+      </c>
+      <c r="T515" t="n">
+        <v>0</v>
+      </c>
+      <c r="U515" t="n">
+        <v>0</v>
+      </c>
+      <c r="V515" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W515" t="n">
+        <v>24</v>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>C. JACOBS | H. ARBOSA ROLDAN | M. DE PABLO DEL CASTILLO | P. DIENE | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>5</v>
+      </c>
+      <c r="E516" t="n">
+        <v>21</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G516" t="n">
+        <v>0</v>
+      </c>
+      <c r="H516" t="n">
+        <v>2</v>
+      </c>
+      <c r="I516" t="n">
+        <v>1</v>
+      </c>
+      <c r="J516" t="n">
+        <v>1</v>
+      </c>
+      <c r="K516" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" t="n">
+        <v>200</v>
+      </c>
+      <c r="M516" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N516" t="n">
+        <v>1</v>
+      </c>
+      <c r="O516" t="n">
+        <v>0</v>
+      </c>
+      <c r="P516" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>0</v>
+      </c>
+      <c r="R516" t="n">
+        <v>1</v>
+      </c>
+      <c r="S516" t="n">
+        <v>0</v>
+      </c>
+      <c r="T516" t="n">
+        <v>0</v>
+      </c>
+      <c r="U516" t="n">
+        <v>0</v>
+      </c>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W516" t="n">
+        <v>24</v>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | G. VERGARA HARBOE | J. MARTINEZ MEGIAS | L. FAIAL</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>5</v>
+      </c>
+      <c r="E517" t="n">
+        <v>9</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G517" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I517" t="n">
+        <v>1</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0</v>
+      </c>
+      <c r="K517" t="n">
+        <v>0</v>
+      </c>
+      <c r="L517" t="n">
+        <v>0</v>
+      </c>
+      <c r="M517" t="n">
+        <v>0</v>
+      </c>
+      <c r="N517" t="n">
+        <v>0</v>
+      </c>
+      <c r="O517" t="n">
+        <v>0</v>
+      </c>
+      <c r="P517" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>0</v>
+      </c>
+      <c r="R517" t="n">
+        <v>0</v>
+      </c>
+      <c r="S517" t="n">
+        <v>0</v>
+      </c>
+      <c r="T517" t="n">
+        <v>0</v>
+      </c>
+      <c r="U517" t="n">
+        <v>0</v>
+      </c>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W517" t="n">
+        <v>24</v>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | L. FAIAL</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>5</v>
+      </c>
+      <c r="E518" t="n">
+        <v>120</v>
+      </c>
+      <c r="F518" t="n">
+        <v>2</v>
+      </c>
+      <c r="G518" t="n">
+        <v>4</v>
+      </c>
+      <c r="H518" t="n">
+        <v>6</v>
+      </c>
+      <c r="I518" t="n">
+        <v>3</v>
+      </c>
+      <c r="J518" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K518" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L518" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M518" t="n">
+        <v>-93.94</v>
+      </c>
+      <c r="N518" t="n">
+        <v>3</v>
+      </c>
+      <c r="O518" t="n">
+        <v>0</v>
+      </c>
+      <c r="P518" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>0</v>
+      </c>
+      <c r="R518" t="n">
+        <v>2</v>
+      </c>
+      <c r="S518" t="n">
+        <v>6</v>
+      </c>
+      <c r="T518" t="n">
+        <v>0</v>
+      </c>
+      <c r="U518" t="n">
+        <v>2</v>
+      </c>
+      <c r="V518" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W518" t="n">
+        <v>24</v>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. VERGARA HARBOE | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | L. FAIAL</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>5</v>
+      </c>
+      <c r="E519" t="n">
+        <v>91</v>
+      </c>
+      <c r="F519" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G519" t="n">
+        <v>2</v>
+      </c>
+      <c r="H519" t="n">
+        <v>3</v>
+      </c>
+      <c r="I519" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J519" t="n">
+        <v>3</v>
+      </c>
+      <c r="K519" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L519" t="n">
+        <v>100</v>
+      </c>
+      <c r="M519" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="N519" t="n">
+        <v>4</v>
+      </c>
+      <c r="O519" t="n">
+        <v>2</v>
+      </c>
+      <c r="P519" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q519" t="n">
+        <v>3</v>
+      </c>
+      <c r="R519" t="n">
+        <v>2</v>
+      </c>
+      <c r="S519" t="n">
+        <v>0</v>
+      </c>
+      <c r="T519" t="n">
+        <v>1</v>
+      </c>
+      <c r="U519" t="n">
+        <v>0</v>
+      </c>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W519" t="n">
+        <v>24</v>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>I. HANEY | I. ORDOÑEZ OCHOA | J. GARCIA-ABRIL GUERRERO | M. OCHI | P. ISERN MAZA</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>5</v>
+      </c>
+      <c r="E520" t="n">
+        <v>65</v>
+      </c>
+      <c r="F520" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G520" t="n">
+        <v>3</v>
+      </c>
+      <c r="H520" t="n">
+        <v>0</v>
+      </c>
+      <c r="I520" t="n">
+        <v>2</v>
+      </c>
+      <c r="J520" t="n">
+        <v>2</v>
+      </c>
+      <c r="K520" t="n">
+        <v>150</v>
+      </c>
+      <c r="L520" t="n">
+        <v>0</v>
+      </c>
+      <c r="M520" t="n">
+        <v>150</v>
+      </c>
+      <c r="N520" t="n">
+        <v>1</v>
+      </c>
+      <c r="O520" t="n">
+        <v>0</v>
+      </c>
+      <c r="P520" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>0</v>
+      </c>
+      <c r="R520" t="n">
+        <v>3</v>
+      </c>
+      <c r="S520" t="n">
+        <v>0</v>
+      </c>
+      <c r="T520" t="n">
+        <v>0</v>
+      </c>
+      <c r="U520" t="n">
+        <v>1</v>
+      </c>
+      <c r="V520" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W520" t="n">
+        <v>24</v>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>I. HANEY | I. ORDOÑEZ OCHOA | J. GARCIA-ABRIL GUERRERO | M. OCHI | P. MARIN FONTAN</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>5</v>
+      </c>
+      <c r="E521" t="n">
+        <v>146</v>
+      </c>
+      <c r="F521" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G521" t="n">
+        <v>6</v>
+      </c>
+      <c r="H521" t="n">
+        <v>6</v>
+      </c>
+      <c r="I521" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J521" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K521" t="n">
+        <v>164.84</v>
+      </c>
+      <c r="L521" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M521" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="N521" t="n">
+        <v>3</v>
+      </c>
+      <c r="O521" t="n">
+        <v>6</v>
+      </c>
+      <c r="P521" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q521" t="n">
+        <v>2</v>
+      </c>
+      <c r="R521" t="n">
+        <v>4</v>
+      </c>
+      <c r="S521" t="n">
+        <v>2</v>
+      </c>
+      <c r="T521" t="n">
+        <v>0</v>
+      </c>
+      <c r="U521" t="n">
+        <v>2</v>
+      </c>
+      <c r="V521" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W521" t="n">
+        <v>24</v>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>I. HANEY | I. ORDOÑEZ OCHOA | M. OCHI | P. ISERN MAZA | P. MARIN FONTAN</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>5</v>
+      </c>
+      <c r="E522" t="n">
+        <v>9</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" t="n">
+        <v>1</v>
+      </c>
+      <c r="K522" t="n">
+        <v>0</v>
+      </c>
+      <c r="L522" t="n">
+        <v>0</v>
+      </c>
+      <c r="M522" t="n">
+        <v>0</v>
+      </c>
+      <c r="N522" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" t="n">
+        <v>0</v>
+      </c>
+      <c r="P522" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>0</v>
+      </c>
+      <c r="R522" t="n">
+        <v>0</v>
+      </c>
+      <c r="S522" t="n">
+        <v>0</v>
+      </c>
+      <c r="T522" t="n">
+        <v>1</v>
+      </c>
+      <c r="U522" t="n">
+        <v>0</v>
+      </c>
+      <c r="V522" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W522" t="n">
+        <v>24</v>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>I. AIZPITARTE ARANZA | J. CEBOLLA HERRERA | M. OLAIZOLA GARIN | N. WILLIAMS | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>5</v>
+      </c>
+      <c r="E523" t="n">
+        <v>33</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" t="n">
+        <v>5</v>
+      </c>
+      <c r="I523" t="n">
+        <v>1</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" t="n">
+        <v>568.1799999999999</v>
+      </c>
+      <c r="M523" t="n">
+        <v>-568.1799999999999</v>
+      </c>
+      <c r="N523" t="n">
+        <v>1</v>
+      </c>
+      <c r="O523" t="n">
+        <v>0</v>
+      </c>
+      <c r="P523" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>0</v>
+      </c>
+      <c r="R523" t="n">
+        <v>1</v>
+      </c>
+      <c r="S523" t="n">
+        <v>2</v>
+      </c>
+      <c r="T523" t="n">
+        <v>0</v>
+      </c>
+      <c r="U523" t="n">
+        <v>1</v>
+      </c>
+      <c r="V523" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W523" t="n">
+        <v>24</v>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>I. AIZPITARTE ARANZA | M. NIANG NDONGO | N. WILLIAMS | O. INDA HERNANDEZ | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>5</v>
+      </c>
+      <c r="E524" t="n">
+        <v>228</v>
+      </c>
+      <c r="F524" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G524" t="n">
+        <v>11</v>
+      </c>
+      <c r="H524" t="n">
+        <v>5</v>
+      </c>
+      <c r="I524" t="n">
+        <v>4</v>
+      </c>
+      <c r="J524" t="n">
+        <v>4</v>
+      </c>
+      <c r="K524" t="n">
+        <v>275</v>
+      </c>
+      <c r="L524" t="n">
+        <v>125</v>
+      </c>
+      <c r="M524" t="n">
+        <v>150</v>
+      </c>
+      <c r="N524" t="n">
+        <v>6</v>
+      </c>
+      <c r="O524" t="n">
+        <v>0</v>
+      </c>
+      <c r="P524" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>2</v>
+      </c>
+      <c r="R524" t="n">
+        <v>5</v>
+      </c>
+      <c r="S524" t="n">
+        <v>0</v>
+      </c>
+      <c r="T524" t="n">
+        <v>0</v>
+      </c>
+      <c r="U524" t="n">
+        <v>1</v>
+      </c>
+      <c r="V524" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W524" t="n">
+        <v>24</v>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>I. MIRANDA GARCIA | M. NIANG NDONGO | N. WILLIAMS | O. INDA HERNANDEZ | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>5</v>
+      </c>
+      <c r="E525" t="n">
+        <v>9</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G525" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" t="n">
+        <v>0</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" t="n">
+        <v>1</v>
+      </c>
+      <c r="K525" t="n">
+        <v>0</v>
+      </c>
+      <c r="L525" t="n">
+        <v>0</v>
+      </c>
+      <c r="M525" t="n">
+        <v>0</v>
+      </c>
+      <c r="N525" t="n">
+        <v>0</v>
+      </c>
+      <c r="O525" t="n">
+        <v>0</v>
+      </c>
+      <c r="P525" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>0</v>
+      </c>
+      <c r="R525" t="n">
+        <v>1</v>
+      </c>
+      <c r="S525" t="n">
+        <v>0</v>
+      </c>
+      <c r="T525" t="n">
+        <v>0</v>
+      </c>
+      <c r="U525" t="n">
+        <v>0</v>
+      </c>
+      <c r="V525" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W525" t="n">
+        <v>24</v>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>J. CEBOLLA HERRERA | M. OLAIZOLA GARIN | N. WILLIAMS | O. ARDANZA BERNAOLA | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>5</v>
+      </c>
+      <c r="E526" t="n">
+        <v>7</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G526" t="n">
+        <v>0</v>
+      </c>
+      <c r="H526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" t="n">
+        <v>1</v>
+      </c>
+      <c r="J526" t="n">
+        <v>0</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" t="n">
+        <v>0</v>
+      </c>
+      <c r="M526" t="n">
+        <v>0</v>
+      </c>
+      <c r="N526" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" t="n">
+        <v>0</v>
+      </c>
+      <c r="P526" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q526" t="n">
+        <v>0</v>
+      </c>
+      <c r="R526" t="n">
+        <v>1</v>
+      </c>
+      <c r="S526" t="n">
+        <v>0</v>
+      </c>
+      <c r="T526" t="n">
+        <v>0</v>
+      </c>
+      <c r="U526" t="n">
+        <v>1</v>
+      </c>
+      <c r="V526" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W526" t="n">
+        <v>24</v>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>5</v>
+      </c>
+      <c r="E527" t="n">
+        <v>7</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G527" t="n">
+        <v>0</v>
+      </c>
+      <c r="H527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="n">
+        <v>1</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0</v>
+      </c>
+      <c r="L527" t="n">
+        <v>0</v>
+      </c>
+      <c r="M527" t="n">
+        <v>0</v>
+      </c>
+      <c r="N527" t="n">
+        <v>1</v>
+      </c>
+      <c r="O527" t="n">
+        <v>0</v>
+      </c>
+      <c r="P527" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q527" t="n">
+        <v>1</v>
+      </c>
+      <c r="R527" t="n">
+        <v>0</v>
+      </c>
+      <c r="S527" t="n">
+        <v>0</v>
+      </c>
+      <c r="T527" t="n">
+        <v>1</v>
+      </c>
+      <c r="U527" t="n">
+        <v>0</v>
+      </c>
+      <c r="V527" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W527" t="n">
+        <v>24</v>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>5</v>
+      </c>
+      <c r="E528" t="n">
+        <v>33</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G528" t="n">
+        <v>5</v>
+      </c>
+      <c r="H528" t="n">
+        <v>0</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J528" t="n">
+        <v>1</v>
+      </c>
+      <c r="K528" t="n">
+        <v>568.1799999999999</v>
+      </c>
+      <c r="L528" t="n">
+        <v>0</v>
+      </c>
+      <c r="M528" t="n">
+        <v>568.1799999999999</v>
+      </c>
+      <c r="N528" t="n">
+        <v>1</v>
+      </c>
+      <c r="O528" t="n">
+        <v>2</v>
+      </c>
+      <c r="P528" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q528" t="n">
+        <v>1</v>
+      </c>
+      <c r="R528" t="n">
+        <v>1</v>
+      </c>
+      <c r="S528" t="n">
+        <v>0</v>
+      </c>
+      <c r="T528" t="n">
+        <v>0</v>
+      </c>
+      <c r="U528" t="n">
+        <v>0</v>
+      </c>
+      <c r="V528" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W528" t="n">
+        <v>24</v>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>5</v>
+      </c>
+      <c r="E529" t="n">
+        <v>27</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G529" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" t="n">
+        <v>2</v>
+      </c>
+      <c r="I529" t="n">
+        <v>1</v>
+      </c>
+      <c r="J529" t="n">
+        <v>1</v>
+      </c>
+      <c r="K529" t="n">
+        <v>0</v>
+      </c>
+      <c r="L529" t="n">
+        <v>200</v>
+      </c>
+      <c r="M529" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N529" t="n">
+        <v>1</v>
+      </c>
+      <c r="O529" t="n">
+        <v>0</v>
+      </c>
+      <c r="P529" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q529" t="n">
+        <v>0</v>
+      </c>
+      <c r="R529" t="n">
+        <v>1</v>
+      </c>
+      <c r="S529" t="n">
+        <v>0</v>
+      </c>
+      <c r="T529" t="n">
+        <v>0</v>
+      </c>
+      <c r="U529" t="n">
+        <v>0</v>
+      </c>
+      <c r="V529" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W529" t="n">
+        <v>24</v>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>5</v>
+      </c>
+      <c r="E530" t="n">
+        <v>48</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G530" t="n">
+        <v>0</v>
+      </c>
+      <c r="H530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" t="n">
+        <v>1</v>
+      </c>
+      <c r="J530" t="n">
+        <v>0</v>
+      </c>
+      <c r="K530" t="n">
+        <v>0</v>
+      </c>
+      <c r="L530" t="n">
+        <v>0</v>
+      </c>
+      <c r="M530" t="n">
+        <v>0</v>
+      </c>
+      <c r="N530" t="n">
+        <v>1</v>
+      </c>
+      <c r="O530" t="n">
+        <v>0</v>
+      </c>
+      <c r="P530" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q530" t="n">
+        <v>0</v>
+      </c>
+      <c r="R530" t="n">
+        <v>0</v>
+      </c>
+      <c r="S530" t="n">
+        <v>0</v>
+      </c>
+      <c r="T530" t="n">
+        <v>0</v>
+      </c>
+      <c r="U530" t="n">
+        <v>0</v>
+      </c>
+      <c r="V530" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W530" t="n">
+        <v>24</v>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>5</v>
+      </c>
+      <c r="E531" t="n">
+        <v>162</v>
+      </c>
+      <c r="F531" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G531" t="n">
+        <v>5</v>
+      </c>
+      <c r="H531" t="n">
+        <v>9</v>
+      </c>
+      <c r="I531" t="n">
+        <v>3</v>
+      </c>
+      <c r="J531" t="n">
+        <v>3</v>
+      </c>
+      <c r="K531" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L531" t="n">
+        <v>300</v>
+      </c>
+      <c r="M531" t="n">
+        <v>-133.33</v>
+      </c>
+      <c r="N531" t="n">
+        <v>4</v>
+      </c>
+      <c r="O531" t="n">
+        <v>0</v>
+      </c>
+      <c r="P531" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q531" t="n">
+        <v>1</v>
+      </c>
+      <c r="R531" t="n">
+        <v>5</v>
+      </c>
+      <c r="S531" t="n">
+        <v>0</v>
+      </c>
+      <c r="T531" t="n">
+        <v>0</v>
+      </c>
+      <c r="U531" t="n">
+        <v>2</v>
+      </c>
+      <c r="V531" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W531" t="n">
+        <v>24</v>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2487927</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>A. LAFUENTE SISO | A. PALAZUELOS PEREZ | E. KALINICENKO | W. LEVEQUE</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>4</v>
+      </c>
+      <c r="E532" t="n">
+        <v>74</v>
+      </c>
+      <c r="F532" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G532" t="n">
+        <v>2</v>
+      </c>
+      <c r="H532" t="n">
+        <v>1</v>
+      </c>
+      <c r="I532" t="n">
+        <v>2</v>
+      </c>
+      <c r="J532" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K532" t="n">
+        <v>100</v>
+      </c>
+      <c r="L532" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M532" t="n">
+        <v>-13.64</v>
+      </c>
+      <c r="N532" t="n">
+        <v>2</v>
+      </c>
+      <c r="O532" t="n">
+        <v>0</v>
+      </c>
+      <c r="P532" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q532" t="n">
+        <v>0</v>
+      </c>
+      <c r="R532" t="n">
+        <v>0</v>
+      </c>
+      <c r="S532" t="n">
+        <v>2</v>
+      </c>
+      <c r="T532" t="n">
+        <v>1</v>
+      </c>
+      <c r="U532" t="n">
+        <v>1</v>
+      </c>
+      <c r="V532" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W532" t="n">
+        <v>25</v>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2487927</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>E. ARQUES LOPEZ | I. HANEY | J. HANNA | M. OCHI | P. ISERN MAZA</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>5</v>
+      </c>
+      <c r="E533" t="n">
+        <v>74</v>
+      </c>
+      <c r="F533" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G533" t="n">
+        <v>1</v>
+      </c>
+      <c r="H533" t="n">
+        <v>2</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J533" t="n">
+        <v>2</v>
+      </c>
+      <c r="K533" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L533" t="n">
+        <v>100</v>
+      </c>
+      <c r="M533" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="N533" t="n">
+        <v>0</v>
+      </c>
+      <c r="O533" t="n">
+        <v>2</v>
+      </c>
+      <c r="P533" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q533" t="n">
+        <v>1</v>
+      </c>
+      <c r="R533" t="n">
+        <v>2</v>
+      </c>
+      <c r="S533" t="n">
+        <v>0</v>
+      </c>
+      <c r="T533" t="n">
+        <v>0</v>
+      </c>
+      <c r="U533" t="n">
+        <v>0</v>
+      </c>
+      <c r="V533" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W533" t="n">
+        <v>25</v>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | S. KOCIC | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>5</v>
+      </c>
+      <c r="E534" t="n">
+        <v>231</v>
+      </c>
+      <c r="F534" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G534" t="n">
+        <v>6</v>
+      </c>
+      <c r="H534" t="n">
+        <v>5</v>
+      </c>
+      <c r="I534" t="n">
+        <v>9</v>
+      </c>
+      <c r="J534" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="K534" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="L534" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="M534" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="N534" t="n">
+        <v>7</v>
+      </c>
+      <c r="O534" t="n">
+        <v>0</v>
+      </c>
+      <c r="P534" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q534" t="n">
+        <v>0</v>
+      </c>
+      <c r="R534" t="n">
+        <v>5</v>
+      </c>
+      <c r="S534" t="n">
+        <v>7</v>
+      </c>
+      <c r="T534" t="n">
+        <v>1</v>
+      </c>
+      <c r="U534" t="n">
+        <v>2</v>
+      </c>
+      <c r="V534" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W534" t="n">
+        <v>25</v>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | S. KOCIC | S. MENDIOLA DIEZ | T. TEIXEIRA DO VALE DIAS | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>5</v>
+      </c>
+      <c r="E535" t="n">
+        <v>14</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G535" t="n">
+        <v>1</v>
+      </c>
+      <c r="H535" t="n">
+        <v>2</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J535" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K535" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L535" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M535" t="n">
+        <v>-113.64</v>
+      </c>
+      <c r="N535" t="n">
+        <v>0</v>
+      </c>
+      <c r="O535" t="n">
+        <v>2</v>
+      </c>
+      <c r="P535" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>0</v>
+      </c>
+      <c r="R535" t="n">
+        <v>1</v>
+      </c>
+      <c r="S535" t="n">
+        <v>2</v>
+      </c>
+      <c r="T535" t="n">
+        <v>0</v>
+      </c>
+      <c r="U535" t="n">
+        <v>1</v>
+      </c>
+      <c r="V535" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W535" t="n">
+        <v>25</v>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>A. RODRIGUEZ AGUILAR | D. ROLLINS | F. BELLO MOURE | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>5</v>
+      </c>
+      <c r="E536" t="n">
+        <v>69</v>
+      </c>
+      <c r="F536" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G536" t="n">
+        <v>2</v>
+      </c>
+      <c r="H536" t="n">
+        <v>0</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J536" t="n">
+        <v>2</v>
+      </c>
+      <c r="K536" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L536" t="n">
+        <v>0</v>
+      </c>
+      <c r="M536" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="N536" t="n">
+        <v>0</v>
+      </c>
+      <c r="O536" t="n">
+        <v>2</v>
+      </c>
+      <c r="P536" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q536" t="n">
+        <v>0</v>
+      </c>
+      <c r="R536" t="n">
+        <v>1</v>
+      </c>
+      <c r="S536" t="n">
+        <v>0</v>
+      </c>
+      <c r="T536" t="n">
+        <v>1</v>
+      </c>
+      <c r="U536" t="n">
+        <v>0</v>
+      </c>
+      <c r="V536" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W536" t="n">
+        <v>25</v>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>A. RODRIGUEZ AGUILAR | D. ROLLINS | J. SIENCHE GUEMETA | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>5</v>
+      </c>
+      <c r="E537" t="n">
+        <v>23</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G537" t="n">
+        <v>1</v>
+      </c>
+      <c r="H537" t="n">
+        <v>0</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J537" t="n">
+        <v>1</v>
+      </c>
+      <c r="K537" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L537" t="n">
+        <v>0</v>
+      </c>
+      <c r="M537" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N537" t="n">
+        <v>0</v>
+      </c>
+      <c r="O537" t="n">
+        <v>2</v>
+      </c>
+      <c r="P537" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>0</v>
+      </c>
+      <c r="R537" t="n">
+        <v>1</v>
+      </c>
+      <c r="S537" t="n">
+        <v>0</v>
+      </c>
+      <c r="T537" t="n">
+        <v>0</v>
+      </c>
+      <c r="U537" t="n">
+        <v>0</v>
+      </c>
+      <c r="V537" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W537" t="n">
+        <v>25</v>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>A. RODRIGUEZ AGUILAR | F. BELLO MOURE | J. SIENCHE GUEMETA | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>5</v>
+      </c>
+      <c r="E538" t="n">
+        <v>14</v>
+      </c>
+      <c r="F538" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G538" t="n">
+        <v>2</v>
+      </c>
+      <c r="H538" t="n">
+        <v>1</v>
+      </c>
+      <c r="I538" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J538" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K538" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L538" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M538" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N538" t="n">
+        <v>1</v>
+      </c>
+      <c r="O538" t="n">
+        <v>2</v>
+      </c>
+      <c r="P538" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q538" t="n">
+        <v>1</v>
+      </c>
+      <c r="R538" t="n">
+        <v>0</v>
+      </c>
+      <c r="S538" t="n">
+        <v>2</v>
+      </c>
+      <c r="T538" t="n">
+        <v>0</v>
+      </c>
+      <c r="U538" t="n">
+        <v>0</v>
+      </c>
+      <c r="V538" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W538" t="n">
+        <v>25</v>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>D. ROLLINS | J. SIENCHE GUEMETA | K. SCHUTTE | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>5</v>
+      </c>
+      <c r="E539" t="n">
+        <v>40</v>
+      </c>
+      <c r="F539" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G539" t="n">
+        <v>0</v>
+      </c>
+      <c r="H539" t="n">
+        <v>3</v>
+      </c>
+      <c r="I539" t="n">
+        <v>2</v>
+      </c>
+      <c r="J539" t="n">
+        <v>2</v>
+      </c>
+      <c r="K539" t="n">
+        <v>0</v>
+      </c>
+      <c r="L539" t="n">
+        <v>150</v>
+      </c>
+      <c r="M539" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N539" t="n">
+        <v>2</v>
+      </c>
+      <c r="O539" t="n">
+        <v>0</v>
+      </c>
+      <c r="P539" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q539" t="n">
+        <v>0</v>
+      </c>
+      <c r="R539" t="n">
+        <v>2</v>
+      </c>
+      <c r="S539" t="n">
+        <v>0</v>
+      </c>
+      <c r="T539" t="n">
+        <v>0</v>
+      </c>
+      <c r="U539" t="n">
+        <v>0</v>
+      </c>
+      <c r="V539" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W539" t="n">
+        <v>25</v>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>F. BELLO MOURE | J. SIENCHE GUEMETA | K. SCHUTTE | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>5</v>
+      </c>
+      <c r="E540" t="n">
+        <v>99</v>
+      </c>
+      <c r="F540" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G540" t="n">
+        <v>2</v>
+      </c>
+      <c r="H540" t="n">
+        <v>3</v>
+      </c>
+      <c r="I540" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J540" t="n">
+        <v>4</v>
+      </c>
+      <c r="K540" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="L540" t="n">
+        <v>75</v>
+      </c>
+      <c r="M540" t="n">
+        <v>-14.76</v>
+      </c>
+      <c r="N540" t="n">
+        <v>3</v>
+      </c>
+      <c r="O540" t="n">
+        <v>3</v>
+      </c>
+      <c r="P540" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q540" t="n">
+        <v>2</v>
+      </c>
+      <c r="R540" t="n">
+        <v>3</v>
+      </c>
+      <c r="S540" t="n">
+        <v>0</v>
+      </c>
+      <c r="T540" t="n">
+        <v>1</v>
+      </c>
+      <c r="U540" t="n">
+        <v>0</v>
+      </c>
+      <c r="V540" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W540" t="n">
+        <v>25</v>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | G. CLARKE | J. FRANCH DE PABLO | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>5</v>
+      </c>
+      <c r="E541" t="n">
+        <v>76</v>
+      </c>
+      <c r="F541" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G541" t="n">
+        <v>0</v>
+      </c>
+      <c r="H541" t="n">
+        <v>0</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" t="n">
+        <v>2</v>
+      </c>
+      <c r="K541" t="n">
+        <v>0</v>
+      </c>
+      <c r="L541" t="n">
+        <v>0</v>
+      </c>
+      <c r="M541" t="n">
+        <v>0</v>
+      </c>
+      <c r="N541" t="n">
+        <v>0</v>
+      </c>
+      <c r="O541" t="n">
+        <v>0</v>
+      </c>
+      <c r="P541" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>0</v>
+      </c>
+      <c r="R541" t="n">
+        <v>1</v>
+      </c>
+      <c r="S541" t="n">
+        <v>0</v>
+      </c>
+      <c r="T541" t="n">
+        <v>1</v>
+      </c>
+      <c r="U541" t="n">
+        <v>0</v>
+      </c>
+      <c r="V541" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W541" t="n">
+        <v>25</v>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | J. FRANCH DE PABLO | N. DEDOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>5</v>
+      </c>
+      <c r="E542" t="n">
+        <v>16</v>
+      </c>
+      <c r="F542" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G542" t="n">
+        <v>2</v>
+      </c>
+      <c r="H542" t="n">
+        <v>0</v>
+      </c>
+      <c r="I542" t="n">
+        <v>1</v>
+      </c>
+      <c r="J542" t="n">
+        <v>0</v>
+      </c>
+      <c r="K542" t="n">
+        <v>200</v>
+      </c>
+      <c r="L542" t="n">
+        <v>0</v>
+      </c>
+      <c r="M542" t="n">
+        <v>0</v>
+      </c>
+      <c r="N542" t="n">
+        <v>1</v>
+      </c>
+      <c r="O542" t="n">
+        <v>0</v>
+      </c>
+      <c r="P542" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>0</v>
+      </c>
+      <c r="R542" t="n">
+        <v>0</v>
+      </c>
+      <c r="S542" t="n">
+        <v>0</v>
+      </c>
+      <c r="T542" t="n">
+        <v>0</v>
+      </c>
+      <c r="U542" t="n">
+        <v>0</v>
+      </c>
+      <c r="V542" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W542" t="n">
+        <v>25</v>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>A. MOODY | G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>5</v>
+      </c>
+      <c r="E543" t="n">
+        <v>108</v>
+      </c>
+      <c r="F543" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G543" t="n">
+        <v>0</v>
+      </c>
+      <c r="H543" t="n">
+        <v>0</v>
+      </c>
+      <c r="I543" t="n">
+        <v>1</v>
+      </c>
+      <c r="J543" t="n">
+        <v>2</v>
+      </c>
+      <c r="K543" t="n">
+        <v>0</v>
+      </c>
+      <c r="L543" t="n">
+        <v>0</v>
+      </c>
+      <c r="M543" t="n">
+        <v>0</v>
+      </c>
+      <c r="N543" t="n">
+        <v>1</v>
+      </c>
+      <c r="O543" t="n">
+        <v>0</v>
+      </c>
+      <c r="P543" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>1</v>
+      </c>
+      <c r="R543" t="n">
+        <v>2</v>
+      </c>
+      <c r="S543" t="n">
+        <v>0</v>
+      </c>
+      <c r="T543" t="n">
+        <v>0</v>
+      </c>
+      <c r="U543" t="n">
+        <v>0</v>
+      </c>
+      <c r="V543" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W543" t="n">
+        <v>25</v>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>5</v>
+      </c>
+      <c r="E544" t="n">
+        <v>72</v>
+      </c>
+      <c r="F544" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G544" t="n">
+        <v>2</v>
+      </c>
+      <c r="H544" t="n">
+        <v>0</v>
+      </c>
+      <c r="I544" t="n">
+        <v>2</v>
+      </c>
+      <c r="J544" t="n">
+        <v>2</v>
+      </c>
+      <c r="K544" t="n">
+        <v>100</v>
+      </c>
+      <c r="L544" t="n">
+        <v>0</v>
+      </c>
+      <c r="M544" t="n">
+        <v>100</v>
+      </c>
+      <c r="N544" t="n">
+        <v>3</v>
+      </c>
+      <c r="O544" t="n">
+        <v>0</v>
+      </c>
+      <c r="P544" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>1</v>
+      </c>
+      <c r="R544" t="n">
+        <v>2</v>
+      </c>
+      <c r="S544" t="n">
+        <v>0</v>
+      </c>
+      <c r="T544" t="n">
+        <v>0</v>
+      </c>
+      <c r="U544" t="n">
+        <v>0</v>
+      </c>
+      <c r="V544" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W544" t="n">
+        <v>25</v>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>5</v>
+      </c>
+      <c r="E545" t="n">
+        <v>25</v>
+      </c>
+      <c r="F545" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G545" t="n">
+        <v>2</v>
+      </c>
+      <c r="H545" t="n">
+        <v>3</v>
+      </c>
+      <c r="I545" t="n">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
+        <v>1</v>
+      </c>
+      <c r="K545" t="n">
+        <v>200</v>
+      </c>
+      <c r="L545" t="n">
+        <v>300</v>
+      </c>
+      <c r="M545" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N545" t="n">
+        <v>1</v>
+      </c>
+      <c r="O545" t="n">
+        <v>0</v>
+      </c>
+      <c r="P545" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>0</v>
+      </c>
+      <c r="R545" t="n">
+        <v>1</v>
+      </c>
+      <c r="S545" t="n">
+        <v>0</v>
+      </c>
+      <c r="T545" t="n">
+        <v>0</v>
+      </c>
+      <c r="U545" t="n">
+        <v>0</v>
+      </c>
+      <c r="V545" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W545" t="n">
+        <v>25</v>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>5</v>
+      </c>
+      <c r="E546" t="n">
+        <v>25</v>
+      </c>
+      <c r="F546" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G546" t="n">
+        <v>3</v>
+      </c>
+      <c r="H546" t="n">
+        <v>2</v>
+      </c>
+      <c r="I546" t="n">
+        <v>1</v>
+      </c>
+      <c r="J546" t="n">
+        <v>1</v>
+      </c>
+      <c r="K546" t="n">
+        <v>300</v>
+      </c>
+      <c r="L546" t="n">
+        <v>200</v>
+      </c>
+      <c r="M546" t="n">
+        <v>100</v>
+      </c>
+      <c r="N546" t="n">
+        <v>1</v>
+      </c>
+      <c r="O546" t="n">
+        <v>0</v>
+      </c>
+      <c r="P546" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q546" t="n">
+        <v>0</v>
+      </c>
+      <c r="R546" t="n">
+        <v>1</v>
+      </c>
+      <c r="S546" t="n">
+        <v>0</v>
+      </c>
+      <c r="T546" t="n">
+        <v>0</v>
+      </c>
+      <c r="U546" t="n">
+        <v>0</v>
+      </c>
+      <c r="V546" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W546" t="n">
+        <v>25</v>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>5</v>
+      </c>
+      <c r="E547" t="n">
+        <v>184</v>
+      </c>
+      <c r="F547" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="G547" t="n">
+        <v>0</v>
+      </c>
+      <c r="H547" t="n">
+        <v>0</v>
+      </c>
+      <c r="I547" t="n">
+        <v>4</v>
+      </c>
+      <c r="J547" t="n">
+        <v>1</v>
+      </c>
+      <c r="K547" t="n">
+        <v>0</v>
+      </c>
+      <c r="L547" t="n">
+        <v>0</v>
+      </c>
+      <c r="M547" t="n">
+        <v>0</v>
+      </c>
+      <c r="N547" t="n">
+        <v>3</v>
+      </c>
+      <c r="O547" t="n">
+        <v>0</v>
+      </c>
+      <c r="P547" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q547" t="n">
+        <v>0</v>
+      </c>
+      <c r="R547" t="n">
+        <v>1</v>
+      </c>
+      <c r="S547" t="n">
+        <v>0</v>
+      </c>
+      <c r="T547" t="n">
+        <v>1</v>
+      </c>
+      <c r="U547" t="n">
+        <v>1</v>
+      </c>
+      <c r="V547" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W547" t="n">
+        <v>25</v>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SANTOS SPENCER | W. NIANG</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>5</v>
+      </c>
+      <c r="E548" t="n">
+        <v>16</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G548" t="n">
+        <v>0</v>
+      </c>
+      <c r="H548" t="n">
+        <v>2</v>
+      </c>
+      <c r="I548" t="n">
+        <v>0</v>
+      </c>
+      <c r="J548" t="n">
+        <v>1</v>
+      </c>
+      <c r="K548" t="n">
+        <v>0</v>
+      </c>
+      <c r="L548" t="n">
+        <v>200</v>
+      </c>
+      <c r="M548" t="n">
+        <v>0</v>
+      </c>
+      <c r="N548" t="n">
+        <v>0</v>
+      </c>
+      <c r="O548" t="n">
+        <v>0</v>
+      </c>
+      <c r="P548" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q548" t="n">
+        <v>0</v>
+      </c>
+      <c r="R548" t="n">
+        <v>1</v>
+      </c>
+      <c r="S548" t="n">
+        <v>0</v>
+      </c>
+      <c r="T548" t="n">
+        <v>0</v>
+      </c>
+      <c r="U548" t="n">
+        <v>0</v>
+      </c>
+      <c r="V548" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W548" t="n">
+        <v>25</v>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT | B. AREVALO SAENZ | L. OBAJO BELTRAN | S. SERRATO BALLETBO | W. NIANG</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>5</v>
+      </c>
+      <c r="E549" t="n">
+        <v>72</v>
+      </c>
+      <c r="F549" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G549" t="n">
+        <v>0</v>
+      </c>
+      <c r="H549" t="n">
+        <v>2</v>
+      </c>
+      <c r="I549" t="n">
+        <v>2</v>
+      </c>
+      <c r="J549" t="n">
+        <v>2</v>
+      </c>
+      <c r="K549" t="n">
+        <v>0</v>
+      </c>
+      <c r="L549" t="n">
+        <v>100</v>
+      </c>
+      <c r="M549" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N549" t="n">
+        <v>2</v>
+      </c>
+      <c r="O549" t="n">
+        <v>0</v>
+      </c>
+      <c r="P549" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q549" t="n">
+        <v>0</v>
+      </c>
+      <c r="R549" t="n">
+        <v>3</v>
+      </c>
+      <c r="S549" t="n">
+        <v>0</v>
+      </c>
+      <c r="T549" t="n">
+        <v>0</v>
+      </c>
+      <c r="U549" t="n">
+        <v>1</v>
+      </c>
+      <c r="V549" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W549" t="n">
+        <v>25</v>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
+++ b/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X549"/>
+  <dimension ref="A1:X566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46582,6 +46582,1434 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>A. TRAORE | D. CEBOLLA PORCAR | E. VAN DER HEIJDEN | J. LLAMAS PRADO | M. DENG</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>5</v>
+      </c>
+      <c r="E550" t="n">
+        <v>91</v>
+      </c>
+      <c r="F550" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G550" t="n">
+        <v>4</v>
+      </c>
+      <c r="H550" t="n">
+        <v>5</v>
+      </c>
+      <c r="I550" t="n">
+        <v>3</v>
+      </c>
+      <c r="J550" t="n">
+        <v>3</v>
+      </c>
+      <c r="K550" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L550" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="M550" t="n">
+        <v>-33.33</v>
+      </c>
+      <c r="N550" t="n">
+        <v>3</v>
+      </c>
+      <c r="O550" t="n">
+        <v>0</v>
+      </c>
+      <c r="P550" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q550" t="n">
+        <v>0</v>
+      </c>
+      <c r="R550" t="n">
+        <v>3</v>
+      </c>
+      <c r="S550" t="n">
+        <v>0</v>
+      </c>
+      <c r="T550" t="n">
+        <v>2</v>
+      </c>
+      <c r="U550" t="n">
+        <v>2</v>
+      </c>
+      <c r="V550" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W550" t="n">
+        <v>26</v>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>D. CEBOLLA PORCAR | D. HAYMAN | E. VAN DER HEIJDEN | J. LLAMAS PRADO | M. DENG</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>5</v>
+      </c>
+      <c r="E551" t="n">
+        <v>5</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G551" t="n">
+        <v>0</v>
+      </c>
+      <c r="H551" t="n">
+        <v>1</v>
+      </c>
+      <c r="I551" t="n">
+        <v>0</v>
+      </c>
+      <c r="J551" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K551" t="n">
+        <v>0</v>
+      </c>
+      <c r="L551" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="M551" t="n">
+        <v>0</v>
+      </c>
+      <c r="N551" t="n">
+        <v>0</v>
+      </c>
+      <c r="O551" t="n">
+        <v>0</v>
+      </c>
+      <c r="P551" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q551" t="n">
+        <v>0</v>
+      </c>
+      <c r="R551" t="n">
+        <v>0</v>
+      </c>
+      <c r="S551" t="n">
+        <v>4</v>
+      </c>
+      <c r="T551" t="n">
+        <v>0</v>
+      </c>
+      <c r="U551" t="n">
+        <v>0</v>
+      </c>
+      <c r="V551" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W551" t="n">
+        <v>26</v>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>C. JACOBS | J. PARDINA MOLINA | K. TORRES CUEVAS | M. DE PABLO DEL CASTILLO | P. DIENE</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>5</v>
+      </c>
+      <c r="E552" t="n">
+        <v>62</v>
+      </c>
+      <c r="F552" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G552" t="n">
+        <v>5</v>
+      </c>
+      <c r="H552" t="n">
+        <v>2</v>
+      </c>
+      <c r="I552" t="n">
+        <v>3</v>
+      </c>
+      <c r="J552" t="n">
+        <v>1</v>
+      </c>
+      <c r="K552" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L552" t="n">
+        <v>200</v>
+      </c>
+      <c r="M552" t="n">
+        <v>-33.33</v>
+      </c>
+      <c r="N552" t="n">
+        <v>3</v>
+      </c>
+      <c r="O552" t="n">
+        <v>0</v>
+      </c>
+      <c r="P552" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q552" t="n">
+        <v>1</v>
+      </c>
+      <c r="R552" t="n">
+        <v>1</v>
+      </c>
+      <c r="S552" t="n">
+        <v>0</v>
+      </c>
+      <c r="T552" t="n">
+        <v>0</v>
+      </c>
+      <c r="U552" t="n">
+        <v>0</v>
+      </c>
+      <c r="V552" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W552" t="n">
+        <v>26</v>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>C. JACOBS | J. PARDINA MOLINA | K. TORRES CUEVAS | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>5</v>
+      </c>
+      <c r="E553" t="n">
+        <v>1</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G553" t="n">
+        <v>1</v>
+      </c>
+      <c r="H553" t="n">
+        <v>0</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J553" t="n">
+        <v>0</v>
+      </c>
+      <c r="K553" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L553" t="n">
+        <v>0</v>
+      </c>
+      <c r="M553" t="n">
+        <v>0</v>
+      </c>
+      <c r="N553" t="n">
+        <v>0</v>
+      </c>
+      <c r="O553" t="n">
+        <v>2</v>
+      </c>
+      <c r="P553" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q553" t="n">
+        <v>0</v>
+      </c>
+      <c r="R553" t="n">
+        <v>0</v>
+      </c>
+      <c r="S553" t="n">
+        <v>0</v>
+      </c>
+      <c r="T553" t="n">
+        <v>0</v>
+      </c>
+      <c r="U553" t="n">
+        <v>0</v>
+      </c>
+      <c r="V553" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W553" t="n">
+        <v>26</v>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>J. PARDINA MOLINA | K. TORRES CUEVAS | M. DE PABLO DEL CASTILLO | P. DIENE | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>5</v>
+      </c>
+      <c r="E554" t="n">
+        <v>33</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G554" t="n">
+        <v>0</v>
+      </c>
+      <c r="H554" t="n">
+        <v>2</v>
+      </c>
+      <c r="I554" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J554" t="n">
+        <v>2</v>
+      </c>
+      <c r="K554" t="n">
+        <v>0</v>
+      </c>
+      <c r="L554" t="n">
+        <v>100</v>
+      </c>
+      <c r="M554" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N554" t="n">
+        <v>0</v>
+      </c>
+      <c r="O554" t="n">
+        <v>2</v>
+      </c>
+      <c r="P554" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q554" t="n">
+        <v>1</v>
+      </c>
+      <c r="R554" t="n">
+        <v>2</v>
+      </c>
+      <c r="S554" t="n">
+        <v>0</v>
+      </c>
+      <c r="T554" t="n">
+        <v>0</v>
+      </c>
+      <c r="U554" t="n">
+        <v>0</v>
+      </c>
+      <c r="V554" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W554" t="n">
+        <v>26</v>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>A. LAFUENTE SISO | A. MAZAIRA GOMEZ | A. PALAZUELOS PEREZ | E. KALINICENKO | W. LEVEQUE</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>5</v>
+      </c>
+      <c r="E555" t="n">
+        <v>287</v>
+      </c>
+      <c r="F555" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="G555" t="n">
+        <v>10</v>
+      </c>
+      <c r="H555" t="n">
+        <v>5</v>
+      </c>
+      <c r="I555" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="J555" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="K555" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="L555" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="M555" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="N555" t="n">
+        <v>8</v>
+      </c>
+      <c r="O555" t="n">
+        <v>3</v>
+      </c>
+      <c r="P555" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q555" t="n">
+        <v>1</v>
+      </c>
+      <c r="R555" t="n">
+        <v>5</v>
+      </c>
+      <c r="S555" t="n">
+        <v>4</v>
+      </c>
+      <c r="T555" t="n">
+        <v>3</v>
+      </c>
+      <c r="U555" t="n">
+        <v>1</v>
+      </c>
+      <c r="V555" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W555" t="n">
+        <v>26</v>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>A. LAFUENTE SISO | A. MAZAIRA GOMEZ | A. PALAZUELOS PEREZ | M. STRIKKER | W. LEVEQUE</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>5</v>
+      </c>
+      <c r="E556" t="n">
+        <v>1</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G556" t="n">
+        <v>0</v>
+      </c>
+      <c r="H556" t="n">
+        <v>2</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0</v>
+      </c>
+      <c r="J556" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K556" t="n">
+        <v>0</v>
+      </c>
+      <c r="L556" t="n">
+        <v>151.52</v>
+      </c>
+      <c r="M556" t="n">
+        <v>0</v>
+      </c>
+      <c r="N556" t="n">
+        <v>0</v>
+      </c>
+      <c r="O556" t="n">
+        <v>0</v>
+      </c>
+      <c r="P556" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q556" t="n">
+        <v>0</v>
+      </c>
+      <c r="R556" t="n">
+        <v>0</v>
+      </c>
+      <c r="S556" t="n">
+        <v>3</v>
+      </c>
+      <c r="T556" t="n">
+        <v>0</v>
+      </c>
+      <c r="U556" t="n">
+        <v>0</v>
+      </c>
+      <c r="V556" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W556" t="n">
+        <v>26</v>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>F. SIERRA GALA | J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>5</v>
+      </c>
+      <c r="E557" t="n">
+        <v>6</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G557" t="n">
+        <v>2</v>
+      </c>
+      <c r="H557" t="n">
+        <v>6</v>
+      </c>
+      <c r="I557" t="n">
+        <v>1</v>
+      </c>
+      <c r="J557" t="n">
+        <v>2</v>
+      </c>
+      <c r="K557" t="n">
+        <v>200</v>
+      </c>
+      <c r="L557" t="n">
+        <v>300</v>
+      </c>
+      <c r="M557" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N557" t="n">
+        <v>1</v>
+      </c>
+      <c r="O557" t="n">
+        <v>0</v>
+      </c>
+      <c r="P557" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q557" t="n">
+        <v>0</v>
+      </c>
+      <c r="R557" t="n">
+        <v>2</v>
+      </c>
+      <c r="S557" t="n">
+        <v>0</v>
+      </c>
+      <c r="T557" t="n">
+        <v>0</v>
+      </c>
+      <c r="U557" t="n">
+        <v>0</v>
+      </c>
+      <c r="V557" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W557" t="n">
+        <v>26</v>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>F. SIERRA GALA | J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>5</v>
+      </c>
+      <c r="E558" t="n">
+        <v>282</v>
+      </c>
+      <c r="F558" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G558" t="n">
+        <v>5</v>
+      </c>
+      <c r="H558" t="n">
+        <v>4</v>
+      </c>
+      <c r="I558" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="J558" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="K558" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="L558" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="M558" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="N558" t="n">
+        <v>4</v>
+      </c>
+      <c r="O558" t="n">
+        <v>7</v>
+      </c>
+      <c r="P558" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q558" t="n">
+        <v>1</v>
+      </c>
+      <c r="R558" t="n">
+        <v>6</v>
+      </c>
+      <c r="S558" t="n">
+        <v>3</v>
+      </c>
+      <c r="T558" t="n">
+        <v>3</v>
+      </c>
+      <c r="U558" t="n">
+        <v>1</v>
+      </c>
+      <c r="V558" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W558" t="n">
+        <v>26</v>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | G. VERGARA HARBOE | K. FELIZOR | M. TIKHONENKO ANDRIYASHCHENKO</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>5</v>
+      </c>
+      <c r="E559" t="n">
+        <v>14</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G559" t="n">
+        <v>3</v>
+      </c>
+      <c r="H559" t="n">
+        <v>0</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K559" t="n">
+        <v>0</v>
+      </c>
+      <c r="L559" t="n">
+        <v>0</v>
+      </c>
+      <c r="M559" t="n">
+        <v>0</v>
+      </c>
+      <c r="N559" t="n">
+        <v>1</v>
+      </c>
+      <c r="O559" t="n">
+        <v>0</v>
+      </c>
+      <c r="P559" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q559" t="n">
+        <v>1</v>
+      </c>
+      <c r="R559" t="n">
+        <v>1</v>
+      </c>
+      <c r="S559" t="n">
+        <v>2</v>
+      </c>
+      <c r="T559" t="n">
+        <v>0</v>
+      </c>
+      <c r="U559" t="n">
+        <v>1</v>
+      </c>
+      <c r="V559" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W559" t="n">
+        <v>26</v>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | K. FELIZOR</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>5</v>
+      </c>
+      <c r="E560" t="n">
+        <v>28</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G560" t="n">
+        <v>0</v>
+      </c>
+      <c r="H560" t="n">
+        <v>5</v>
+      </c>
+      <c r="I560" t="n">
+        <v>1</v>
+      </c>
+      <c r="J560" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K560" t="n">
+        <v>0</v>
+      </c>
+      <c r="L560" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="M560" t="n">
+        <v>-378.79</v>
+      </c>
+      <c r="N560" t="n">
+        <v>1</v>
+      </c>
+      <c r="O560" t="n">
+        <v>0</v>
+      </c>
+      <c r="P560" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q560" t="n">
+        <v>0</v>
+      </c>
+      <c r="R560" t="n">
+        <v>1</v>
+      </c>
+      <c r="S560" t="n">
+        <v>3</v>
+      </c>
+      <c r="T560" t="n">
+        <v>0</v>
+      </c>
+      <c r="U560" t="n">
+        <v>1</v>
+      </c>
+      <c r="V560" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W560" t="n">
+        <v>26</v>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | J. MORENO POZA | J. SANTA BARBARA CARCELEN | K. FELIZOR</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>5</v>
+      </c>
+      <c r="E561" t="n">
+        <v>43</v>
+      </c>
+      <c r="F561" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G561" t="n">
+        <v>2</v>
+      </c>
+      <c r="H561" t="n">
+        <v>0</v>
+      </c>
+      <c r="I561" t="n">
+        <v>2</v>
+      </c>
+      <c r="J561" t="n">
+        <v>1</v>
+      </c>
+      <c r="K561" t="n">
+        <v>100</v>
+      </c>
+      <c r="L561" t="n">
+        <v>0</v>
+      </c>
+      <c r="M561" t="n">
+        <v>100</v>
+      </c>
+      <c r="N561" t="n">
+        <v>2</v>
+      </c>
+      <c r="O561" t="n">
+        <v>0</v>
+      </c>
+      <c r="P561" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q561" t="n">
+        <v>1</v>
+      </c>
+      <c r="R561" t="n">
+        <v>1</v>
+      </c>
+      <c r="S561" t="n">
+        <v>0</v>
+      </c>
+      <c r="T561" t="n">
+        <v>0</v>
+      </c>
+      <c r="U561" t="n">
+        <v>0</v>
+      </c>
+      <c r="V561" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W561" t="n">
+        <v>26</v>
+      </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | J. SANTA BARBARA CARCELEN | K. FELIZOR | M. TIKHONENKO ANDRIYASHCHENKO</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>5</v>
+      </c>
+      <c r="E562" t="n">
+        <v>65</v>
+      </c>
+      <c r="F562" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G562" t="n">
+        <v>3</v>
+      </c>
+      <c r="H562" t="n">
+        <v>3</v>
+      </c>
+      <c r="I562" t="n">
+        <v>1</v>
+      </c>
+      <c r="J562" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K562" t="n">
+        <v>300</v>
+      </c>
+      <c r="L562" t="n">
+        <v>170.45</v>
+      </c>
+      <c r="M562" t="n">
+        <v>129.55</v>
+      </c>
+      <c r="N562" t="n">
+        <v>2</v>
+      </c>
+      <c r="O562" t="n">
+        <v>0</v>
+      </c>
+      <c r="P562" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q562" t="n">
+        <v>1</v>
+      </c>
+      <c r="R562" t="n">
+        <v>0</v>
+      </c>
+      <c r="S562" t="n">
+        <v>4</v>
+      </c>
+      <c r="T562" t="n">
+        <v>0</v>
+      </c>
+      <c r="U562" t="n">
+        <v>0</v>
+      </c>
+      <c r="V562" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W562" t="n">
+        <v>26</v>
+      </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>C. FIELDS | J. SANTA BARBARA CARCELEN | K. FELIZOR | L. FAIAL | M. TIKHONENKO ANDRIYASHCHENKO</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>5</v>
+      </c>
+      <c r="E563" t="n">
+        <v>23</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G563" t="n">
+        <v>1</v>
+      </c>
+      <c r="H563" t="n">
+        <v>2</v>
+      </c>
+      <c r="I563" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J563" t="n">
+        <v>1</v>
+      </c>
+      <c r="K563" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L563" t="n">
+        <v>200</v>
+      </c>
+      <c r="M563" t="n">
+        <v>-86.36</v>
+      </c>
+      <c r="N563" t="n">
+        <v>0</v>
+      </c>
+      <c r="O563" t="n">
+        <v>2</v>
+      </c>
+      <c r="P563" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q563" t="n">
+        <v>0</v>
+      </c>
+      <c r="R563" t="n">
+        <v>1</v>
+      </c>
+      <c r="S563" t="n">
+        <v>0</v>
+      </c>
+      <c r="T563" t="n">
+        <v>0</v>
+      </c>
+      <c r="U563" t="n">
+        <v>0</v>
+      </c>
+      <c r="V563" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W563" t="n">
+        <v>26</v>
+      </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | B. AREVALO SAENZ | I. MONTERO MECA | P. SANTOS SPENCER | W. NIANG</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>5</v>
+      </c>
+      <c r="E564" t="n">
+        <v>43</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G564" t="n">
+        <v>0</v>
+      </c>
+      <c r="H564" t="n">
+        <v>2</v>
+      </c>
+      <c r="I564" t="n">
+        <v>1</v>
+      </c>
+      <c r="J564" t="n">
+        <v>2</v>
+      </c>
+      <c r="K564" t="n">
+        <v>0</v>
+      </c>
+      <c r="L564" t="n">
+        <v>100</v>
+      </c>
+      <c r="M564" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N564" t="n">
+        <v>1</v>
+      </c>
+      <c r="O564" t="n">
+        <v>0</v>
+      </c>
+      <c r="P564" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q564" t="n">
+        <v>0</v>
+      </c>
+      <c r="R564" t="n">
+        <v>2</v>
+      </c>
+      <c r="S564" t="n">
+        <v>0</v>
+      </c>
+      <c r="T564" t="n">
+        <v>1</v>
+      </c>
+      <c r="U564" t="n">
+        <v>1</v>
+      </c>
+      <c r="V564" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W564" t="n">
+        <v>26</v>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>5</v>
+      </c>
+      <c r="E565" t="n">
+        <v>112</v>
+      </c>
+      <c r="F565" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G565" t="n">
+        <v>9</v>
+      </c>
+      <c r="H565" t="n">
+        <v>7</v>
+      </c>
+      <c r="I565" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="J565" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K565" t="n">
+        <v>220.59</v>
+      </c>
+      <c r="L565" t="n">
+        <v>243.06</v>
+      </c>
+      <c r="M565" t="n">
+        <v>-22.47</v>
+      </c>
+      <c r="N565" t="n">
+        <v>3</v>
+      </c>
+      <c r="O565" t="n">
+        <v>7</v>
+      </c>
+      <c r="P565" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q565" t="n">
+        <v>2</v>
+      </c>
+      <c r="R565" t="n">
+        <v>4</v>
+      </c>
+      <c r="S565" t="n">
+        <v>2</v>
+      </c>
+      <c r="T565" t="n">
+        <v>0</v>
+      </c>
+      <c r="U565" t="n">
+        <v>2</v>
+      </c>
+      <c r="V565" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W565" t="n">
+        <v>26</v>
+      </c>
+      <c r="X565" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | B. AREVALO SAENZ | P. SANTOS SPENCER | S. SERRATO BALLETBO | W. NIANG</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>5</v>
+      </c>
+      <c r="E566" t="n">
+        <v>18</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G566" t="n">
+        <v>1</v>
+      </c>
+      <c r="H566" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J566" t="n">
+        <v>0</v>
+      </c>
+      <c r="K566" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L566" t="n">
+        <v>0</v>
+      </c>
+      <c r="M566" t="n">
+        <v>0</v>
+      </c>
+      <c r="N566" t="n">
+        <v>0</v>
+      </c>
+      <c r="O566" t="n">
+        <v>2</v>
+      </c>
+      <c r="P566" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q566" t="n">
+        <v>0</v>
+      </c>
+      <c r="R566" t="n">
+        <v>0</v>
+      </c>
+      <c r="S566" t="n">
+        <v>0</v>
+      </c>
+      <c r="T566" t="n">
+        <v>0</v>
+      </c>
+      <c r="U566" t="n">
+        <v>0</v>
+      </c>
+      <c r="V566" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W566" t="n">
+        <v>26</v>
+      </c>
+      <c r="X566" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
+++ b/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X566"/>
+  <dimension ref="A1:X484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41122,6894 +41122,6 @@
         </is>
       </c>
     </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>A. MORALES ROS | D. ORRIT SERRANO | J. BERGENS | N. OKEKE | R. HAYES</t>
-        </is>
-      </c>
-      <c r="D485" t="n">
-        <v>5</v>
-      </c>
-      <c r="E485" t="n">
-        <v>79</v>
-      </c>
-      <c r="F485" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="G485" t="n">
-        <v>0</v>
-      </c>
-      <c r="H485" t="n">
-        <v>3</v>
-      </c>
-      <c r="I485" t="n">
-        <v>1</v>
-      </c>
-      <c r="J485" t="n">
-        <v>2</v>
-      </c>
-      <c r="K485" t="n">
-        <v>0</v>
-      </c>
-      <c r="L485" t="n">
-        <v>150</v>
-      </c>
-      <c r="M485" t="n">
-        <v>-150</v>
-      </c>
-      <c r="N485" t="n">
-        <v>0</v>
-      </c>
-      <c r="O485" t="n">
-        <v>0</v>
-      </c>
-      <c r="P485" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q485" t="n">
-        <v>0</v>
-      </c>
-      <c r="R485" t="n">
-        <v>2</v>
-      </c>
-      <c r="S485" t="n">
-        <v>0</v>
-      </c>
-      <c r="T485" t="n">
-        <v>1</v>
-      </c>
-      <c r="U485" t="n">
-        <v>1</v>
-      </c>
-      <c r="V485" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W485" t="n">
-        <v>24</v>
-      </c>
-      <c r="X485" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>A. MORALES ROS | J. BERGENS | J. CERA RODRIGUEZ | N. OKEKE | R. HAYES</t>
-        </is>
-      </c>
-      <c r="D486" t="n">
-        <v>5</v>
-      </c>
-      <c r="E486" t="n">
-        <v>129</v>
-      </c>
-      <c r="F486" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="G486" t="n">
-        <v>10</v>
-      </c>
-      <c r="H486" t="n">
-        <v>6</v>
-      </c>
-      <c r="I486" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="J486" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="K486" t="n">
-        <v>210.08</v>
-      </c>
-      <c r="L486" t="n">
-        <v>164.84</v>
-      </c>
-      <c r="M486" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="N486" t="n">
-        <v>4</v>
-      </c>
-      <c r="O486" t="n">
-        <v>4</v>
-      </c>
-      <c r="P486" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q486" t="n">
-        <v>1</v>
-      </c>
-      <c r="R486" t="n">
-        <v>1</v>
-      </c>
-      <c r="S486" t="n">
-        <v>6</v>
-      </c>
-      <c r="T486" t="n">
-        <v>1</v>
-      </c>
-      <c r="U486" t="n">
-        <v>1</v>
-      </c>
-      <c r="V486" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W486" t="n">
-        <v>24</v>
-      </c>
-      <c r="X486" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>A. MORALES ROS | J. BERGENS | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES</t>
-        </is>
-      </c>
-      <c r="D487" t="n">
-        <v>5</v>
-      </c>
-      <c r="E487" t="n">
-        <v>22</v>
-      </c>
-      <c r="F487" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="G487" t="n">
-        <v>0</v>
-      </c>
-      <c r="H487" t="n">
-        <v>0</v>
-      </c>
-      <c r="I487" t="n">
-        <v>0</v>
-      </c>
-      <c r="J487" t="n">
-        <v>1</v>
-      </c>
-      <c r="K487" t="n">
-        <v>0</v>
-      </c>
-      <c r="L487" t="n">
-        <v>0</v>
-      </c>
-      <c r="M487" t="n">
-        <v>0</v>
-      </c>
-      <c r="N487" t="n">
-        <v>0</v>
-      </c>
-      <c r="O487" t="n">
-        <v>0</v>
-      </c>
-      <c r="P487" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q487" t="n">
-        <v>0</v>
-      </c>
-      <c r="R487" t="n">
-        <v>0</v>
-      </c>
-      <c r="S487" t="n">
-        <v>0</v>
-      </c>
-      <c r="T487" t="n">
-        <v>1</v>
-      </c>
-      <c r="U487" t="n">
-        <v>0</v>
-      </c>
-      <c r="V487" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W487" t="n">
-        <v>24</v>
-      </c>
-      <c r="X487" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>D. ORRIT SERRANO | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
-        </is>
-      </c>
-      <c r="D488" t="n">
-        <v>5</v>
-      </c>
-      <c r="E488" t="n">
-        <v>10</v>
-      </c>
-      <c r="F488" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G488" t="n">
-        <v>0</v>
-      </c>
-      <c r="H488" t="n">
-        <v>0</v>
-      </c>
-      <c r="I488" t="n">
-        <v>0</v>
-      </c>
-      <c r="J488" t="n">
-        <v>1</v>
-      </c>
-      <c r="K488" t="n">
-        <v>0</v>
-      </c>
-      <c r="L488" t="n">
-        <v>0</v>
-      </c>
-      <c r="M488" t="n">
-        <v>0</v>
-      </c>
-      <c r="N488" t="n">
-        <v>0</v>
-      </c>
-      <c r="O488" t="n">
-        <v>0</v>
-      </c>
-      <c r="P488" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q488" t="n">
-        <v>0</v>
-      </c>
-      <c r="R488" t="n">
-        <v>2</v>
-      </c>
-      <c r="S488" t="n">
-        <v>0</v>
-      </c>
-      <c r="T488" t="n">
-        <v>0</v>
-      </c>
-      <c r="U488" t="n">
-        <v>1</v>
-      </c>
-      <c r="V488" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W488" t="n">
-        <v>24</v>
-      </c>
-      <c r="X488" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>J. BERGENS | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
-        </is>
-      </c>
-      <c r="D489" t="n">
-        <v>5</v>
-      </c>
-      <c r="E489" t="n">
-        <v>332</v>
-      </c>
-      <c r="F489" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="G489" t="n">
-        <v>8</v>
-      </c>
-      <c r="H489" t="n">
-        <v>8</v>
-      </c>
-      <c r="I489" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="J489" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="K489" t="n">
-        <v>90.09</v>
-      </c>
-      <c r="L489" t="n">
-        <v>120.48</v>
-      </c>
-      <c r="M489" t="n">
-        <v>-30.39</v>
-      </c>
-      <c r="N489" t="n">
-        <v>10</v>
-      </c>
-      <c r="O489" t="n">
-        <v>2</v>
-      </c>
-      <c r="P489" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q489" t="n">
-        <v>2</v>
-      </c>
-      <c r="R489" t="n">
-        <v>6</v>
-      </c>
-      <c r="S489" t="n">
-        <v>6</v>
-      </c>
-      <c r="T489" t="n">
-        <v>1</v>
-      </c>
-      <c r="U489" t="n">
-        <v>3</v>
-      </c>
-      <c r="V489" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W489" t="n">
-        <v>24</v>
-      </c>
-      <c r="X489" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
-        </is>
-      </c>
-      <c r="D490" t="n">
-        <v>4</v>
-      </c>
-      <c r="E490" t="n">
-        <v>27</v>
-      </c>
-      <c r="F490" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G490" t="n">
-        <v>1</v>
-      </c>
-      <c r="H490" t="n">
-        <v>0</v>
-      </c>
-      <c r="I490" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J490" t="n">
-        <v>1</v>
-      </c>
-      <c r="K490" t="n">
-        <v>0</v>
-      </c>
-      <c r="L490" t="n">
-        <v>0</v>
-      </c>
-      <c r="M490" t="n">
-        <v>0</v>
-      </c>
-      <c r="N490" t="n">
-        <v>0</v>
-      </c>
-      <c r="O490" t="n">
-        <v>2</v>
-      </c>
-      <c r="P490" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q490" t="n">
-        <v>1</v>
-      </c>
-      <c r="R490" t="n">
-        <v>1</v>
-      </c>
-      <c r="S490" t="n">
-        <v>0</v>
-      </c>
-      <c r="T490" t="n">
-        <v>0</v>
-      </c>
-      <c r="U490" t="n">
-        <v>0</v>
-      </c>
-      <c r="V490" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W490" t="n">
-        <v>24</v>
-      </c>
-      <c r="X490" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>A. BIRD-JELINEK | A. INFANTE GUTIERREZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
-        </is>
-      </c>
-      <c r="D491" t="n">
-        <v>5</v>
-      </c>
-      <c r="E491" t="n">
-        <v>31</v>
-      </c>
-      <c r="F491" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G491" t="n">
-        <v>2</v>
-      </c>
-      <c r="H491" t="n">
-        <v>0</v>
-      </c>
-      <c r="I491" t="n">
-        <v>1</v>
-      </c>
-      <c r="J491" t="n">
-        <v>0</v>
-      </c>
-      <c r="K491" t="n">
-        <v>200</v>
-      </c>
-      <c r="L491" t="n">
-        <v>0</v>
-      </c>
-      <c r="M491" t="n">
-        <v>0</v>
-      </c>
-      <c r="N491" t="n">
-        <v>1</v>
-      </c>
-      <c r="O491" t="n">
-        <v>0</v>
-      </c>
-      <c r="P491" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q491" t="n">
-        <v>0</v>
-      </c>
-      <c r="R491" t="n">
-        <v>0</v>
-      </c>
-      <c r="S491" t="n">
-        <v>0</v>
-      </c>
-      <c r="T491" t="n">
-        <v>0</v>
-      </c>
-      <c r="U491" t="n">
-        <v>0</v>
-      </c>
-      <c r="V491" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W491" t="n">
-        <v>24</v>
-      </c>
-      <c r="X491" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>A. BIRD-JELINEK | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | S. SERRATO BALLETBO</t>
-        </is>
-      </c>
-      <c r="D492" t="n">
-        <v>5</v>
-      </c>
-      <c r="E492" t="n">
-        <v>27</v>
-      </c>
-      <c r="F492" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G492" t="n">
-        <v>0</v>
-      </c>
-      <c r="H492" t="n">
-        <v>2</v>
-      </c>
-      <c r="I492" t="n">
-        <v>1</v>
-      </c>
-      <c r="J492" t="n">
-        <v>1</v>
-      </c>
-      <c r="K492" t="n">
-        <v>0</v>
-      </c>
-      <c r="L492" t="n">
-        <v>200</v>
-      </c>
-      <c r="M492" t="n">
-        <v>-200</v>
-      </c>
-      <c r="N492" t="n">
-        <v>1</v>
-      </c>
-      <c r="O492" t="n">
-        <v>0</v>
-      </c>
-      <c r="P492" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q492" t="n">
-        <v>0</v>
-      </c>
-      <c r="R492" t="n">
-        <v>1</v>
-      </c>
-      <c r="S492" t="n">
-        <v>0</v>
-      </c>
-      <c r="T492" t="n">
-        <v>0</v>
-      </c>
-      <c r="U492" t="n">
-        <v>0</v>
-      </c>
-      <c r="V492" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W492" t="n">
-        <v>24</v>
-      </c>
-      <c r="X492" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>A. BIRD-JELINEK | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
-        </is>
-      </c>
-      <c r="D493" t="n">
-        <v>5</v>
-      </c>
-      <c r="E493" t="n">
-        <v>50</v>
-      </c>
-      <c r="F493" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G493" t="n">
-        <v>0</v>
-      </c>
-      <c r="H493" t="n">
-        <v>2</v>
-      </c>
-      <c r="I493" t="n">
-        <v>0</v>
-      </c>
-      <c r="J493" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K493" t="n">
-        <v>0</v>
-      </c>
-      <c r="L493" t="n">
-        <v>106.38</v>
-      </c>
-      <c r="M493" t="n">
-        <v>0</v>
-      </c>
-      <c r="N493" t="n">
-        <v>1</v>
-      </c>
-      <c r="O493" t="n">
-        <v>0</v>
-      </c>
-      <c r="P493" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q493" t="n">
-        <v>1</v>
-      </c>
-      <c r="R493" t="n">
-        <v>1</v>
-      </c>
-      <c r="S493" t="n">
-        <v>2</v>
-      </c>
-      <c r="T493" t="n">
-        <v>0</v>
-      </c>
-      <c r="U493" t="n">
-        <v>0</v>
-      </c>
-      <c r="V493" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W493" t="n">
-        <v>24</v>
-      </c>
-      <c r="X493" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | L. OBAJO BELTRAN | P. SALL</t>
-        </is>
-      </c>
-      <c r="D494" t="n">
-        <v>5</v>
-      </c>
-      <c r="E494" t="n">
-        <v>85</v>
-      </c>
-      <c r="F494" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G494" t="n">
-        <v>3</v>
-      </c>
-      <c r="H494" t="n">
-        <v>4</v>
-      </c>
-      <c r="I494" t="n">
-        <v>2</v>
-      </c>
-      <c r="J494" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K494" t="n">
-        <v>150</v>
-      </c>
-      <c r="L494" t="n">
-        <v>212.77</v>
-      </c>
-      <c r="M494" t="n">
-        <v>-62.77</v>
-      </c>
-      <c r="N494" t="n">
-        <v>1</v>
-      </c>
-      <c r="O494" t="n">
-        <v>0</v>
-      </c>
-      <c r="P494" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q494" t="n">
-        <v>0</v>
-      </c>
-      <c r="R494" t="n">
-        <v>1</v>
-      </c>
-      <c r="S494" t="n">
-        <v>2</v>
-      </c>
-      <c r="T494" t="n">
-        <v>0</v>
-      </c>
-      <c r="U494" t="n">
-        <v>0</v>
-      </c>
-      <c r="V494" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W494" t="n">
-        <v>24</v>
-      </c>
-      <c r="X494" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER</t>
-        </is>
-      </c>
-      <c r="D495" t="n">
-        <v>5</v>
-      </c>
-      <c r="E495" t="n">
-        <v>123</v>
-      </c>
-      <c r="F495" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G495" t="n">
-        <v>6</v>
-      </c>
-      <c r="H495" t="n">
-        <v>6</v>
-      </c>
-      <c r="I495" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="J495" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="K495" t="n">
-        <v>164.84</v>
-      </c>
-      <c r="L495" t="n">
-        <v>154.64</v>
-      </c>
-      <c r="M495" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="N495" t="n">
-        <v>2</v>
-      </c>
-      <c r="O495" t="n">
-        <v>6</v>
-      </c>
-      <c r="P495" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q495" t="n">
-        <v>2</v>
-      </c>
-      <c r="R495" t="n">
-        <v>3</v>
-      </c>
-      <c r="S495" t="n">
-        <v>2</v>
-      </c>
-      <c r="T495" t="n">
-        <v>1</v>
-      </c>
-      <c r="U495" t="n">
-        <v>1</v>
-      </c>
-      <c r="V495" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W495" t="n">
-        <v>24</v>
-      </c>
-      <c r="X495" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
-        </is>
-      </c>
-      <c r="D496" t="n">
-        <v>5</v>
-      </c>
-      <c r="E496" t="n">
-        <v>91</v>
-      </c>
-      <c r="F496" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G496" t="n">
-        <v>4</v>
-      </c>
-      <c r="H496" t="n">
-        <v>3</v>
-      </c>
-      <c r="I496" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J496" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K496" t="n">
-        <v>144.93</v>
-      </c>
-      <c r="L496" t="n">
-        <v>159.57</v>
-      </c>
-      <c r="M496" t="n">
-        <v>-14.65</v>
-      </c>
-      <c r="N496" t="n">
-        <v>2</v>
-      </c>
-      <c r="O496" t="n">
-        <v>4</v>
-      </c>
-      <c r="P496" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q496" t="n">
-        <v>1</v>
-      </c>
-      <c r="R496" t="n">
-        <v>2</v>
-      </c>
-      <c r="S496" t="n">
-        <v>2</v>
-      </c>
-      <c r="T496" t="n">
-        <v>0</v>
-      </c>
-      <c r="U496" t="n">
-        <v>1</v>
-      </c>
-      <c r="V496" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W496" t="n">
-        <v>24</v>
-      </c>
-      <c r="X496" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
-        </is>
-      </c>
-      <c r="D497" t="n">
-        <v>5</v>
-      </c>
-      <c r="E497" t="n">
-        <v>10</v>
-      </c>
-      <c r="F497" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G497" t="n">
-        <v>0</v>
-      </c>
-      <c r="H497" t="n">
-        <v>0</v>
-      </c>
-      <c r="I497" t="n">
-        <v>1</v>
-      </c>
-      <c r="J497" t="n">
-        <v>0</v>
-      </c>
-      <c r="K497" t="n">
-        <v>0</v>
-      </c>
-      <c r="L497" t="n">
-        <v>0</v>
-      </c>
-      <c r="M497" t="n">
-        <v>0</v>
-      </c>
-      <c r="N497" t="n">
-        <v>2</v>
-      </c>
-      <c r="O497" t="n">
-        <v>0</v>
-      </c>
-      <c r="P497" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q497" t="n">
-        <v>1</v>
-      </c>
-      <c r="R497" t="n">
-        <v>0</v>
-      </c>
-      <c r="S497" t="n">
-        <v>0</v>
-      </c>
-      <c r="T497" t="n">
-        <v>0</v>
-      </c>
-      <c r="U497" t="n">
-        <v>0</v>
-      </c>
-      <c r="V497" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W497" t="n">
-        <v>24</v>
-      </c>
-      <c r="X497" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
-        </is>
-      </c>
-      <c r="D498" t="n">
-        <v>5</v>
-      </c>
-      <c r="E498" t="n">
-        <v>182</v>
-      </c>
-      <c r="F498" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="G498" t="n">
-        <v>2</v>
-      </c>
-      <c r="H498" t="n">
-        <v>2</v>
-      </c>
-      <c r="I498" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="J498" t="n">
-        <v>4</v>
-      </c>
-      <c r="K498" t="n">
-        <v>51.55</v>
-      </c>
-      <c r="L498" t="n">
-        <v>50</v>
-      </c>
-      <c r="M498" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="N498" t="n">
-        <v>2</v>
-      </c>
-      <c r="O498" t="n">
-        <v>2</v>
-      </c>
-      <c r="P498" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q498" t="n">
-        <v>1</v>
-      </c>
-      <c r="R498" t="n">
-        <v>6</v>
-      </c>
-      <c r="S498" t="n">
-        <v>0</v>
-      </c>
-      <c r="T498" t="n">
-        <v>0</v>
-      </c>
-      <c r="U498" t="n">
-        <v>2</v>
-      </c>
-      <c r="V498" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W498" t="n">
-        <v>24</v>
-      </c>
-      <c r="X498" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>A. CALVO TORRES | C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | J. LACUNZA ABECIA</t>
-        </is>
-      </c>
-      <c r="D499" t="n">
-        <v>5</v>
-      </c>
-      <c r="E499" t="n">
-        <v>9</v>
-      </c>
-      <c r="F499" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G499" t="n">
-        <v>0</v>
-      </c>
-      <c r="H499" t="n">
-        <v>2</v>
-      </c>
-      <c r="I499" t="n">
-        <v>0</v>
-      </c>
-      <c r="J499" t="n">
-        <v>1</v>
-      </c>
-      <c r="K499" t="n">
-        <v>0</v>
-      </c>
-      <c r="L499" t="n">
-        <v>200</v>
-      </c>
-      <c r="M499" t="n">
-        <v>0</v>
-      </c>
-      <c r="N499" t="n">
-        <v>0</v>
-      </c>
-      <c r="O499" t="n">
-        <v>0</v>
-      </c>
-      <c r="P499" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q499" t="n">
-        <v>0</v>
-      </c>
-      <c r="R499" t="n">
-        <v>1</v>
-      </c>
-      <c r="S499" t="n">
-        <v>0</v>
-      </c>
-      <c r="T499" t="n">
-        <v>0</v>
-      </c>
-      <c r="U499" t="n">
-        <v>0</v>
-      </c>
-      <c r="V499" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W499" t="n">
-        <v>24</v>
-      </c>
-      <c r="X499" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>A. CALVO TORRES | C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | P. YARNOZ LUMBRERAS</t>
-        </is>
-      </c>
-      <c r="D500" t="n">
-        <v>5</v>
-      </c>
-      <c r="E500" t="n">
-        <v>33</v>
-      </c>
-      <c r="F500" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G500" t="n">
-        <v>3</v>
-      </c>
-      <c r="H500" t="n">
-        <v>0</v>
-      </c>
-      <c r="I500" t="n">
-        <v>2</v>
-      </c>
-      <c r="J500" t="n">
-        <v>0</v>
-      </c>
-      <c r="K500" t="n">
-        <v>150</v>
-      </c>
-      <c r="L500" t="n">
-        <v>0</v>
-      </c>
-      <c r="M500" t="n">
-        <v>0</v>
-      </c>
-      <c r="N500" t="n">
-        <v>2</v>
-      </c>
-      <c r="O500" t="n">
-        <v>0</v>
-      </c>
-      <c r="P500" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q500" t="n">
-        <v>0</v>
-      </c>
-      <c r="R500" t="n">
-        <v>0</v>
-      </c>
-      <c r="S500" t="n">
-        <v>0</v>
-      </c>
-      <c r="T500" t="n">
-        <v>0</v>
-      </c>
-      <c r="U500" t="n">
-        <v>0</v>
-      </c>
-      <c r="V500" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W500" t="n">
-        <v>24</v>
-      </c>
-      <c r="X500" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | J. LACUNZA ABECIA | P. YARNOZ LUMBRERAS</t>
-        </is>
-      </c>
-      <c r="D501" t="n">
-        <v>5</v>
-      </c>
-      <c r="E501" t="n">
-        <v>248</v>
-      </c>
-      <c r="F501" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="G501" t="n">
-        <v>13</v>
-      </c>
-      <c r="H501" t="n">
-        <v>14</v>
-      </c>
-      <c r="I501" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="J501" t="n">
-        <v>8</v>
-      </c>
-      <c r="K501" t="n">
-        <v>195.78</v>
-      </c>
-      <c r="L501" t="n">
-        <v>175</v>
-      </c>
-      <c r="M501" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="N501" t="n">
-        <v>7</v>
-      </c>
-      <c r="O501" t="n">
-        <v>6</v>
-      </c>
-      <c r="P501" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q501" t="n">
-        <v>3</v>
-      </c>
-      <c r="R501" t="n">
-        <v>9</v>
-      </c>
-      <c r="S501" t="n">
-        <v>0</v>
-      </c>
-      <c r="T501" t="n">
-        <v>0</v>
-      </c>
-      <c r="U501" t="n">
-        <v>1</v>
-      </c>
-      <c r="V501" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W501" t="n">
-        <v>24</v>
-      </c>
-      <c r="X501" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. BARROS GARCIA</t>
-        </is>
-      </c>
-      <c r="D502" t="n">
-        <v>5</v>
-      </c>
-      <c r="E502" t="n">
-        <v>9</v>
-      </c>
-      <c r="F502" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G502" t="n">
-        <v>2</v>
-      </c>
-      <c r="H502" t="n">
-        <v>0</v>
-      </c>
-      <c r="I502" t="n">
-        <v>1</v>
-      </c>
-      <c r="J502" t="n">
-        <v>0</v>
-      </c>
-      <c r="K502" t="n">
-        <v>200</v>
-      </c>
-      <c r="L502" t="n">
-        <v>0</v>
-      </c>
-      <c r="M502" t="n">
-        <v>0</v>
-      </c>
-      <c r="N502" t="n">
-        <v>1</v>
-      </c>
-      <c r="O502" t="n">
-        <v>0</v>
-      </c>
-      <c r="P502" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q502" t="n">
-        <v>0</v>
-      </c>
-      <c r="R502" t="n">
-        <v>0</v>
-      </c>
-      <c r="S502" t="n">
-        <v>0</v>
-      </c>
-      <c r="T502" t="n">
-        <v>0</v>
-      </c>
-      <c r="U502" t="n">
-        <v>0</v>
-      </c>
-      <c r="V502" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W502" t="n">
-        <v>24</v>
-      </c>
-      <c r="X502" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | T. PIERRE PHILIPPE</t>
-        </is>
-      </c>
-      <c r="D503" t="n">
-        <v>5</v>
-      </c>
-      <c r="E503" t="n">
-        <v>124</v>
-      </c>
-      <c r="F503" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="G503" t="n">
-        <v>7</v>
-      </c>
-      <c r="H503" t="n">
-        <v>5</v>
-      </c>
-      <c r="I503" t="n">
-        <v>4</v>
-      </c>
-      <c r="J503" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K503" t="n">
-        <v>175</v>
-      </c>
-      <c r="L503" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="M503" t="n">
-        <v>-52.27</v>
-      </c>
-      <c r="N503" t="n">
-        <v>5</v>
-      </c>
-      <c r="O503" t="n">
-        <v>0</v>
-      </c>
-      <c r="P503" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q503" t="n">
-        <v>1</v>
-      </c>
-      <c r="R503" t="n">
-        <v>2</v>
-      </c>
-      <c r="S503" t="n">
-        <v>5</v>
-      </c>
-      <c r="T503" t="n">
-        <v>0</v>
-      </c>
-      <c r="U503" t="n">
-        <v>2</v>
-      </c>
-      <c r="V503" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W503" t="n">
-        <v>24</v>
-      </c>
-      <c r="X503" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | J. MENENDEZ GARCIA | M. OKAFOR AUGUSTIN | T. PIERRE PHILIPPE</t>
-        </is>
-      </c>
-      <c r="D504" t="n">
-        <v>5</v>
-      </c>
-      <c r="E504" t="n">
-        <v>24</v>
-      </c>
-      <c r="F504" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G504" t="n">
-        <v>0</v>
-      </c>
-      <c r="H504" t="n">
-        <v>3</v>
-      </c>
-      <c r="I504" t="n">
-        <v>0</v>
-      </c>
-      <c r="J504" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="K504" t="n">
-        <v>0</v>
-      </c>
-      <c r="L504" t="n">
-        <v>208.33</v>
-      </c>
-      <c r="M504" t="n">
-        <v>0</v>
-      </c>
-      <c r="N504" t="n">
-        <v>0</v>
-      </c>
-      <c r="O504" t="n">
-        <v>0</v>
-      </c>
-      <c r="P504" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q504" t="n">
-        <v>0</v>
-      </c>
-      <c r="R504" t="n">
-        <v>1</v>
-      </c>
-      <c r="S504" t="n">
-        <v>1</v>
-      </c>
-      <c r="T504" t="n">
-        <v>0</v>
-      </c>
-      <c r="U504" t="n">
-        <v>0</v>
-      </c>
-      <c r="V504" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W504" t="n">
-        <v>24</v>
-      </c>
-      <c r="X504" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>D. RAMÍREZ SÁNCHEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. BARROS GARCIA | T. PIERRE PHILIPPE</t>
-        </is>
-      </c>
-      <c r="D505" t="n">
-        <v>5</v>
-      </c>
-      <c r="E505" t="n">
-        <v>24</v>
-      </c>
-      <c r="F505" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G505" t="n">
-        <v>0</v>
-      </c>
-      <c r="H505" t="n">
-        <v>0</v>
-      </c>
-      <c r="I505" t="n">
-        <v>0</v>
-      </c>
-      <c r="J505" t="n">
-        <v>1</v>
-      </c>
-      <c r="K505" t="n">
-        <v>0</v>
-      </c>
-      <c r="L505" t="n">
-        <v>0</v>
-      </c>
-      <c r="M505" t="n">
-        <v>0</v>
-      </c>
-      <c r="N505" t="n">
-        <v>0</v>
-      </c>
-      <c r="O505" t="n">
-        <v>0</v>
-      </c>
-      <c r="P505" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q505" t="n">
-        <v>0</v>
-      </c>
-      <c r="R505" t="n">
-        <v>1</v>
-      </c>
-      <c r="S505" t="n">
-        <v>0</v>
-      </c>
-      <c r="T505" t="n">
-        <v>0</v>
-      </c>
-      <c r="U505" t="n">
-        <v>0</v>
-      </c>
-      <c r="V505" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W505" t="n">
-        <v>24</v>
-      </c>
-      <c r="X505" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>D. RAMÍREZ SÁNCHEZ | I. DUKE TOUSSAINT | S. BARROS GARCIA | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
-        </is>
-      </c>
-      <c r="D506" t="n">
-        <v>5</v>
-      </c>
-      <c r="E506" t="n">
-        <v>11</v>
-      </c>
-      <c r="F506" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G506" t="n">
-        <v>2</v>
-      </c>
-      <c r="H506" t="n">
-        <v>2</v>
-      </c>
-      <c r="I506" t="n">
-        <v>1</v>
-      </c>
-      <c r="J506" t="n">
-        <v>1</v>
-      </c>
-      <c r="K506" t="n">
-        <v>200</v>
-      </c>
-      <c r="L506" t="n">
-        <v>200</v>
-      </c>
-      <c r="M506" t="n">
-        <v>0</v>
-      </c>
-      <c r="N506" t="n">
-        <v>1</v>
-      </c>
-      <c r="O506" t="n">
-        <v>0</v>
-      </c>
-      <c r="P506" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q506" t="n">
-        <v>0</v>
-      </c>
-      <c r="R506" t="n">
-        <v>1</v>
-      </c>
-      <c r="S506" t="n">
-        <v>0</v>
-      </c>
-      <c r="T506" t="n">
-        <v>0</v>
-      </c>
-      <c r="U506" t="n">
-        <v>0</v>
-      </c>
-      <c r="V506" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W506" t="n">
-        <v>24</v>
-      </c>
-      <c r="X506" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
-        </is>
-      </c>
-      <c r="D507" t="n">
-        <v>5</v>
-      </c>
-      <c r="E507" t="n">
-        <v>9</v>
-      </c>
-      <c r="F507" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G507" t="n">
-        <v>0</v>
-      </c>
-      <c r="H507" t="n">
-        <v>3</v>
-      </c>
-      <c r="I507" t="n">
-        <v>0</v>
-      </c>
-      <c r="J507" t="n">
-        <v>1</v>
-      </c>
-      <c r="K507" t="n">
-        <v>0</v>
-      </c>
-      <c r="L507" t="n">
-        <v>300</v>
-      </c>
-      <c r="M507" t="n">
-        <v>0</v>
-      </c>
-      <c r="N507" t="n">
-        <v>0</v>
-      </c>
-      <c r="O507" t="n">
-        <v>0</v>
-      </c>
-      <c r="P507" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q507" t="n">
-        <v>0</v>
-      </c>
-      <c r="R507" t="n">
-        <v>1</v>
-      </c>
-      <c r="S507" t="n">
-        <v>0</v>
-      </c>
-      <c r="T507" t="n">
-        <v>0</v>
-      </c>
-      <c r="U507" t="n">
-        <v>0</v>
-      </c>
-      <c r="V507" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W507" t="n">
-        <v>24</v>
-      </c>
-      <c r="X507" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>G. ARCOS GONZALEZ | J. MENENDEZ GARCIA | M. OKAFOR AUGUSTIN | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
-        </is>
-      </c>
-      <c r="D508" t="n">
-        <v>5</v>
-      </c>
-      <c r="E508" t="n">
-        <v>89</v>
-      </c>
-      <c r="F508" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="G508" t="n">
-        <v>5</v>
-      </c>
-      <c r="H508" t="n">
-        <v>3</v>
-      </c>
-      <c r="I508" t="n">
-        <v>3</v>
-      </c>
-      <c r="J508" t="n">
-        <v>2</v>
-      </c>
-      <c r="K508" t="n">
-        <v>166.67</v>
-      </c>
-      <c r="L508" t="n">
-        <v>150</v>
-      </c>
-      <c r="M508" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="N508" t="n">
-        <v>3</v>
-      </c>
-      <c r="O508" t="n">
-        <v>0</v>
-      </c>
-      <c r="P508" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q508" t="n">
-        <v>0</v>
-      </c>
-      <c r="R508" t="n">
-        <v>3</v>
-      </c>
-      <c r="S508" t="n">
-        <v>0</v>
-      </c>
-      <c r="T508" t="n">
-        <v>0</v>
-      </c>
-      <c r="U508" t="n">
-        <v>1</v>
-      </c>
-      <c r="V508" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W508" t="n">
-        <v>24</v>
-      </c>
-      <c r="X508" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. KOCIC | V. MORENO MARTIN</t>
-        </is>
-      </c>
-      <c r="D509" t="n">
-        <v>5</v>
-      </c>
-      <c r="E509" t="n">
-        <v>84</v>
-      </c>
-      <c r="F509" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G509" t="n">
-        <v>2</v>
-      </c>
-      <c r="H509" t="n">
-        <v>2</v>
-      </c>
-      <c r="I509" t="n">
-        <v>1</v>
-      </c>
-      <c r="J509" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K509" t="n">
-        <v>200</v>
-      </c>
-      <c r="L509" t="n">
-        <v>69.44</v>
-      </c>
-      <c r="M509" t="n">
-        <v>130.56</v>
-      </c>
-      <c r="N509" t="n">
-        <v>2</v>
-      </c>
-      <c r="O509" t="n">
-        <v>0</v>
-      </c>
-      <c r="P509" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q509" t="n">
-        <v>1</v>
-      </c>
-      <c r="R509" t="n">
-        <v>2</v>
-      </c>
-      <c r="S509" t="n">
-        <v>2</v>
-      </c>
-      <c r="T509" t="n">
-        <v>0</v>
-      </c>
-      <c r="U509" t="n">
-        <v>0</v>
-      </c>
-      <c r="V509" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W509" t="n">
-        <v>24</v>
-      </c>
-      <c r="X509" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
-        </is>
-      </c>
-      <c r="D510" t="n">
-        <v>5</v>
-      </c>
-      <c r="E510" t="n">
-        <v>3</v>
-      </c>
-      <c r="F510" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G510" t="n">
-        <v>0</v>
-      </c>
-      <c r="H510" t="n">
-        <v>1</v>
-      </c>
-      <c r="I510" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J510" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K510" t="n">
-        <v>0</v>
-      </c>
-      <c r="L510" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="M510" t="n">
-        <v>0</v>
-      </c>
-      <c r="N510" t="n">
-        <v>0</v>
-      </c>
-      <c r="O510" t="n">
-        <v>0</v>
-      </c>
-      <c r="P510" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q510" t="n">
-        <v>1</v>
-      </c>
-      <c r="R510" t="n">
-        <v>1</v>
-      </c>
-      <c r="S510" t="n">
-        <v>2</v>
-      </c>
-      <c r="T510" t="n">
-        <v>0</v>
-      </c>
-      <c r="U510" t="n">
-        <v>1</v>
-      </c>
-      <c r="V510" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W510" t="n">
-        <v>24</v>
-      </c>
-      <c r="X510" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. KOCIC | V. MORENO MARTIN | V. STEVANIC</t>
-        </is>
-      </c>
-      <c r="D511" t="n">
-        <v>5</v>
-      </c>
-      <c r="E511" t="n">
-        <v>40</v>
-      </c>
-      <c r="F511" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G511" t="n">
-        <v>4</v>
-      </c>
-      <c r="H511" t="n">
-        <v>0</v>
-      </c>
-      <c r="I511" t="n">
-        <v>2</v>
-      </c>
-      <c r="J511" t="n">
-        <v>1</v>
-      </c>
-      <c r="K511" t="n">
-        <v>200</v>
-      </c>
-      <c r="L511" t="n">
-        <v>0</v>
-      </c>
-      <c r="M511" t="n">
-        <v>200</v>
-      </c>
-      <c r="N511" t="n">
-        <v>2</v>
-      </c>
-      <c r="O511" t="n">
-        <v>0</v>
-      </c>
-      <c r="P511" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q511" t="n">
-        <v>0</v>
-      </c>
-      <c r="R511" t="n">
-        <v>1</v>
-      </c>
-      <c r="S511" t="n">
-        <v>0</v>
-      </c>
-      <c r="T511" t="n">
-        <v>0</v>
-      </c>
-      <c r="U511" t="n">
-        <v>0</v>
-      </c>
-      <c r="V511" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W511" t="n">
-        <v>24</v>
-      </c>
-      <c r="X511" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>C. JACOBS | E. A NONGO BERTHOLD | H. ARBOSA ROLDAN | J. PARDINA MOLINA | R. UKAWUBA</t>
-        </is>
-      </c>
-      <c r="D512" t="n">
-        <v>5</v>
-      </c>
-      <c r="E512" t="n">
-        <v>3</v>
-      </c>
-      <c r="F512" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G512" t="n">
-        <v>1</v>
-      </c>
-      <c r="H512" t="n">
-        <v>0</v>
-      </c>
-      <c r="I512" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J512" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K512" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="L512" t="n">
-        <v>0</v>
-      </c>
-      <c r="M512" t="n">
-        <v>0</v>
-      </c>
-      <c r="N512" t="n">
-        <v>1</v>
-      </c>
-      <c r="O512" t="n">
-        <v>2</v>
-      </c>
-      <c r="P512" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q512" t="n">
-        <v>1</v>
-      </c>
-      <c r="R512" t="n">
-        <v>0</v>
-      </c>
-      <c r="S512" t="n">
-        <v>0</v>
-      </c>
-      <c r="T512" t="n">
-        <v>0</v>
-      </c>
-      <c r="U512" t="n">
-        <v>1</v>
-      </c>
-      <c r="V512" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W512" t="n">
-        <v>24</v>
-      </c>
-      <c r="X512" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>C. JACOBS | E. A NONGO BERTHOLD | H. ARBOSA ROLDAN | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
-        </is>
-      </c>
-      <c r="D513" t="n">
-        <v>5</v>
-      </c>
-      <c r="E513" t="n">
-        <v>19</v>
-      </c>
-      <c r="F513" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G513" t="n">
-        <v>0</v>
-      </c>
-      <c r="H513" t="n">
-        <v>2</v>
-      </c>
-      <c r="I513" t="n">
-        <v>0</v>
-      </c>
-      <c r="J513" t="n">
-        <v>1</v>
-      </c>
-      <c r="K513" t="n">
-        <v>0</v>
-      </c>
-      <c r="L513" t="n">
-        <v>200</v>
-      </c>
-      <c r="M513" t="n">
-        <v>0</v>
-      </c>
-      <c r="N513" t="n">
-        <v>0</v>
-      </c>
-      <c r="O513" t="n">
-        <v>0</v>
-      </c>
-      <c r="P513" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q513" t="n">
-        <v>0</v>
-      </c>
-      <c r="R513" t="n">
-        <v>1</v>
-      </c>
-      <c r="S513" t="n">
-        <v>0</v>
-      </c>
-      <c r="T513" t="n">
-        <v>0</v>
-      </c>
-      <c r="U513" t="n">
-        <v>0</v>
-      </c>
-      <c r="V513" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W513" t="n">
-        <v>24</v>
-      </c>
-      <c r="X513" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>C. JACOBS | H. ARBOSA ROLDAN | J. PARDINA MOLINA | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
-        </is>
-      </c>
-      <c r="D514" t="n">
-        <v>5</v>
-      </c>
-      <c r="E514" t="n">
-        <v>34</v>
-      </c>
-      <c r="F514" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G514" t="n">
-        <v>0</v>
-      </c>
-      <c r="H514" t="n">
-        <v>0</v>
-      </c>
-      <c r="I514" t="n">
-        <v>1</v>
-      </c>
-      <c r="J514" t="n">
-        <v>0</v>
-      </c>
-      <c r="K514" t="n">
-        <v>0</v>
-      </c>
-      <c r="L514" t="n">
-        <v>0</v>
-      </c>
-      <c r="M514" t="n">
-        <v>0</v>
-      </c>
-      <c r="N514" t="n">
-        <v>1</v>
-      </c>
-      <c r="O514" t="n">
-        <v>0</v>
-      </c>
-      <c r="P514" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q514" t="n">
-        <v>0</v>
-      </c>
-      <c r="R514" t="n">
-        <v>1</v>
-      </c>
-      <c r="S514" t="n">
-        <v>0</v>
-      </c>
-      <c r="T514" t="n">
-        <v>0</v>
-      </c>
-      <c r="U514" t="n">
-        <v>1</v>
-      </c>
-      <c r="V514" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W514" t="n">
-        <v>24</v>
-      </c>
-      <c r="X514" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>C. JACOBS | H. ARBOSA ROLDAN | K. TORRES CUEVAS | P. DIENE | R. UKAWUBA</t>
-        </is>
-      </c>
-      <c r="D515" t="n">
-        <v>5</v>
-      </c>
-      <c r="E515" t="n">
-        <v>50</v>
-      </c>
-      <c r="F515" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G515" t="n">
-        <v>2</v>
-      </c>
-      <c r="H515" t="n">
-        <v>2</v>
-      </c>
-      <c r="I515" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J515" t="n">
-        <v>1</v>
-      </c>
-      <c r="K515" t="n">
-        <v>106.38</v>
-      </c>
-      <c r="L515" t="n">
-        <v>200</v>
-      </c>
-      <c r="M515" t="n">
-        <v>-93.62</v>
-      </c>
-      <c r="N515" t="n">
-        <v>1</v>
-      </c>
-      <c r="O515" t="n">
-        <v>2</v>
-      </c>
-      <c r="P515" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q515" t="n">
-        <v>0</v>
-      </c>
-      <c r="R515" t="n">
-        <v>1</v>
-      </c>
-      <c r="S515" t="n">
-        <v>0</v>
-      </c>
-      <c r="T515" t="n">
-        <v>0</v>
-      </c>
-      <c r="U515" t="n">
-        <v>0</v>
-      </c>
-      <c r="V515" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W515" t="n">
-        <v>24</v>
-      </c>
-      <c r="X515" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>C. JACOBS | H. ARBOSA ROLDAN | M. DE PABLO DEL CASTILLO | P. DIENE | R. UKAWUBA</t>
-        </is>
-      </c>
-      <c r="D516" t="n">
-        <v>5</v>
-      </c>
-      <c r="E516" t="n">
-        <v>21</v>
-      </c>
-      <c r="F516" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G516" t="n">
-        <v>0</v>
-      </c>
-      <c r="H516" t="n">
-        <v>2</v>
-      </c>
-      <c r="I516" t="n">
-        <v>1</v>
-      </c>
-      <c r="J516" t="n">
-        <v>1</v>
-      </c>
-      <c r="K516" t="n">
-        <v>0</v>
-      </c>
-      <c r="L516" t="n">
-        <v>200</v>
-      </c>
-      <c r="M516" t="n">
-        <v>-200</v>
-      </c>
-      <c r="N516" t="n">
-        <v>1</v>
-      </c>
-      <c r="O516" t="n">
-        <v>0</v>
-      </c>
-      <c r="P516" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q516" t="n">
-        <v>0</v>
-      </c>
-      <c r="R516" t="n">
-        <v>1</v>
-      </c>
-      <c r="S516" t="n">
-        <v>0</v>
-      </c>
-      <c r="T516" t="n">
-        <v>0</v>
-      </c>
-      <c r="U516" t="n">
-        <v>0</v>
-      </c>
-      <c r="V516" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W516" t="n">
-        <v>24</v>
-      </c>
-      <c r="X516" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>2487920</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>C. FIELDS | G. BOAHEN | G. VERGARA HARBOE | J. MARTINEZ MEGIAS | L. FAIAL</t>
-        </is>
-      </c>
-      <c r="D517" t="n">
-        <v>5</v>
-      </c>
-      <c r="E517" t="n">
-        <v>9</v>
-      </c>
-      <c r="F517" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G517" t="n">
-        <v>0</v>
-      </c>
-      <c r="H517" t="n">
-        <v>0</v>
-      </c>
-      <c r="I517" t="n">
-        <v>1</v>
-      </c>
-      <c r="J517" t="n">
-        <v>0</v>
-      </c>
-      <c r="K517" t="n">
-        <v>0</v>
-      </c>
-      <c r="L517" t="n">
-        <v>0</v>
-      </c>
-      <c r="M517" t="n">
-        <v>0</v>
-      </c>
-      <c r="N517" t="n">
-        <v>0</v>
-      </c>
-      <c r="O517" t="n">
-        <v>0</v>
-      </c>
-      <c r="P517" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q517" t="n">
-        <v>0</v>
-      </c>
-      <c r="R517" t="n">
-        <v>0</v>
-      </c>
-      <c r="S517" t="n">
-        <v>0</v>
-      </c>
-      <c r="T517" t="n">
-        <v>0</v>
-      </c>
-      <c r="U517" t="n">
-        <v>0</v>
-      </c>
-      <c r="V517" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W517" t="n">
-        <v>24</v>
-      </c>
-      <c r="X517" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>2487920</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>C. FIELDS | G. BOAHEN | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | L. FAIAL</t>
-        </is>
-      </c>
-      <c r="D518" t="n">
-        <v>5</v>
-      </c>
-      <c r="E518" t="n">
-        <v>120</v>
-      </c>
-      <c r="F518" t="n">
-        <v>2</v>
-      </c>
-      <c r="G518" t="n">
-        <v>4</v>
-      </c>
-      <c r="H518" t="n">
-        <v>6</v>
-      </c>
-      <c r="I518" t="n">
-        <v>3</v>
-      </c>
-      <c r="J518" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K518" t="n">
-        <v>133.33</v>
-      </c>
-      <c r="L518" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="M518" t="n">
-        <v>-93.94</v>
-      </c>
-      <c r="N518" t="n">
-        <v>3</v>
-      </c>
-      <c r="O518" t="n">
-        <v>0</v>
-      </c>
-      <c r="P518" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q518" t="n">
-        <v>0</v>
-      </c>
-      <c r="R518" t="n">
-        <v>2</v>
-      </c>
-      <c r="S518" t="n">
-        <v>6</v>
-      </c>
-      <c r="T518" t="n">
-        <v>0</v>
-      </c>
-      <c r="U518" t="n">
-        <v>2</v>
-      </c>
-      <c r="V518" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W518" t="n">
-        <v>24</v>
-      </c>
-      <c r="X518" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>2487920</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>C. FIELDS | G. VERGARA HARBOE | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | L. FAIAL</t>
-        </is>
-      </c>
-      <c r="D519" t="n">
-        <v>5</v>
-      </c>
-      <c r="E519" t="n">
-        <v>91</v>
-      </c>
-      <c r="F519" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G519" t="n">
-        <v>2</v>
-      </c>
-      <c r="H519" t="n">
-        <v>3</v>
-      </c>
-      <c r="I519" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J519" t="n">
-        <v>3</v>
-      </c>
-      <c r="K519" t="n">
-        <v>106.38</v>
-      </c>
-      <c r="L519" t="n">
-        <v>100</v>
-      </c>
-      <c r="M519" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="N519" t="n">
-        <v>4</v>
-      </c>
-      <c r="O519" t="n">
-        <v>2</v>
-      </c>
-      <c r="P519" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q519" t="n">
-        <v>3</v>
-      </c>
-      <c r="R519" t="n">
-        <v>2</v>
-      </c>
-      <c r="S519" t="n">
-        <v>0</v>
-      </c>
-      <c r="T519" t="n">
-        <v>1</v>
-      </c>
-      <c r="U519" t="n">
-        <v>0</v>
-      </c>
-      <c r="V519" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W519" t="n">
-        <v>24</v>
-      </c>
-      <c r="X519" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>2487920</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>I. HANEY | I. ORDOÑEZ OCHOA | J. GARCIA-ABRIL GUERRERO | M. OCHI | P. ISERN MAZA</t>
-        </is>
-      </c>
-      <c r="D520" t="n">
-        <v>5</v>
-      </c>
-      <c r="E520" t="n">
-        <v>65</v>
-      </c>
-      <c r="F520" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G520" t="n">
-        <v>3</v>
-      </c>
-      <c r="H520" t="n">
-        <v>0</v>
-      </c>
-      <c r="I520" t="n">
-        <v>2</v>
-      </c>
-      <c r="J520" t="n">
-        <v>2</v>
-      </c>
-      <c r="K520" t="n">
-        <v>150</v>
-      </c>
-      <c r="L520" t="n">
-        <v>0</v>
-      </c>
-      <c r="M520" t="n">
-        <v>150</v>
-      </c>
-      <c r="N520" t="n">
-        <v>1</v>
-      </c>
-      <c r="O520" t="n">
-        <v>0</v>
-      </c>
-      <c r="P520" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q520" t="n">
-        <v>0</v>
-      </c>
-      <c r="R520" t="n">
-        <v>3</v>
-      </c>
-      <c r="S520" t="n">
-        <v>0</v>
-      </c>
-      <c r="T520" t="n">
-        <v>0</v>
-      </c>
-      <c r="U520" t="n">
-        <v>1</v>
-      </c>
-      <c r="V520" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W520" t="n">
-        <v>24</v>
-      </c>
-      <c r="X520" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>2487920</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>I. HANEY | I. ORDOÑEZ OCHOA | J. GARCIA-ABRIL GUERRERO | M. OCHI | P. MARIN FONTAN</t>
-        </is>
-      </c>
-      <c r="D521" t="n">
-        <v>5</v>
-      </c>
-      <c r="E521" t="n">
-        <v>146</v>
-      </c>
-      <c r="F521" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="G521" t="n">
-        <v>6</v>
-      </c>
-      <c r="H521" t="n">
-        <v>6</v>
-      </c>
-      <c r="I521" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="J521" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K521" t="n">
-        <v>164.84</v>
-      </c>
-      <c r="L521" t="n">
-        <v>208.33</v>
-      </c>
-      <c r="M521" t="n">
-        <v>-43.5</v>
-      </c>
-      <c r="N521" t="n">
-        <v>3</v>
-      </c>
-      <c r="O521" t="n">
-        <v>6</v>
-      </c>
-      <c r="P521" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q521" t="n">
-        <v>2</v>
-      </c>
-      <c r="R521" t="n">
-        <v>4</v>
-      </c>
-      <c r="S521" t="n">
-        <v>2</v>
-      </c>
-      <c r="T521" t="n">
-        <v>0</v>
-      </c>
-      <c r="U521" t="n">
-        <v>2</v>
-      </c>
-      <c r="V521" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W521" t="n">
-        <v>24</v>
-      </c>
-      <c r="X521" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>2487920</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>I. HANEY | I. ORDOÑEZ OCHOA | M. OCHI | P. ISERN MAZA | P. MARIN FONTAN</t>
-        </is>
-      </c>
-      <c r="D522" t="n">
-        <v>5</v>
-      </c>
-      <c r="E522" t="n">
-        <v>9</v>
-      </c>
-      <c r="F522" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G522" t="n">
-        <v>0</v>
-      </c>
-      <c r="H522" t="n">
-        <v>0</v>
-      </c>
-      <c r="I522" t="n">
-        <v>0</v>
-      </c>
-      <c r="J522" t="n">
-        <v>1</v>
-      </c>
-      <c r="K522" t="n">
-        <v>0</v>
-      </c>
-      <c r="L522" t="n">
-        <v>0</v>
-      </c>
-      <c r="M522" t="n">
-        <v>0</v>
-      </c>
-      <c r="N522" t="n">
-        <v>0</v>
-      </c>
-      <c r="O522" t="n">
-        <v>0</v>
-      </c>
-      <c r="P522" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q522" t="n">
-        <v>0</v>
-      </c>
-      <c r="R522" t="n">
-        <v>0</v>
-      </c>
-      <c r="S522" t="n">
-        <v>0</v>
-      </c>
-      <c r="T522" t="n">
-        <v>1</v>
-      </c>
-      <c r="U522" t="n">
-        <v>0</v>
-      </c>
-      <c r="V522" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W522" t="n">
-        <v>24</v>
-      </c>
-      <c r="X522" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>I. AIZPITARTE ARANZA | J. CEBOLLA HERRERA | M. OLAIZOLA GARIN | N. WILLIAMS | T. SAGNA</t>
-        </is>
-      </c>
-      <c r="D523" t="n">
-        <v>5</v>
-      </c>
-      <c r="E523" t="n">
-        <v>33</v>
-      </c>
-      <c r="F523" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G523" t="n">
-        <v>0</v>
-      </c>
-      <c r="H523" t="n">
-        <v>5</v>
-      </c>
-      <c r="I523" t="n">
-        <v>1</v>
-      </c>
-      <c r="J523" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K523" t="n">
-        <v>0</v>
-      </c>
-      <c r="L523" t="n">
-        <v>568.1799999999999</v>
-      </c>
-      <c r="M523" t="n">
-        <v>-568.1799999999999</v>
-      </c>
-      <c r="N523" t="n">
-        <v>1</v>
-      </c>
-      <c r="O523" t="n">
-        <v>0</v>
-      </c>
-      <c r="P523" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q523" t="n">
-        <v>0</v>
-      </c>
-      <c r="R523" t="n">
-        <v>1</v>
-      </c>
-      <c r="S523" t="n">
-        <v>2</v>
-      </c>
-      <c r="T523" t="n">
-        <v>0</v>
-      </c>
-      <c r="U523" t="n">
-        <v>1</v>
-      </c>
-      <c r="V523" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W523" t="n">
-        <v>24</v>
-      </c>
-      <c r="X523" t="inlineStr">
-        <is>
-          <t>BIELE ISB vs INSOLAC CAJA 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>I. AIZPITARTE ARANZA | M. NIANG NDONGO | N. WILLIAMS | O. INDA HERNANDEZ | T. SAGNA</t>
-        </is>
-      </c>
-      <c r="D524" t="n">
-        <v>5</v>
-      </c>
-      <c r="E524" t="n">
-        <v>228</v>
-      </c>
-      <c r="F524" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G524" t="n">
-        <v>11</v>
-      </c>
-      <c r="H524" t="n">
-        <v>5</v>
-      </c>
-      <c r="I524" t="n">
-        <v>4</v>
-      </c>
-      <c r="J524" t="n">
-        <v>4</v>
-      </c>
-      <c r="K524" t="n">
-        <v>275</v>
-      </c>
-      <c r="L524" t="n">
-        <v>125</v>
-      </c>
-      <c r="M524" t="n">
-        <v>150</v>
-      </c>
-      <c r="N524" t="n">
-        <v>6</v>
-      </c>
-      <c r="O524" t="n">
-        <v>0</v>
-      </c>
-      <c r="P524" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q524" t="n">
-        <v>2</v>
-      </c>
-      <c r="R524" t="n">
-        <v>5</v>
-      </c>
-      <c r="S524" t="n">
-        <v>0</v>
-      </c>
-      <c r="T524" t="n">
-        <v>0</v>
-      </c>
-      <c r="U524" t="n">
-        <v>1</v>
-      </c>
-      <c r="V524" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W524" t="n">
-        <v>24</v>
-      </c>
-      <c r="X524" t="inlineStr">
-        <is>
-          <t>BIELE ISB vs INSOLAC CAJA 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>I. MIRANDA GARCIA | M. NIANG NDONGO | N. WILLIAMS | O. INDA HERNANDEZ | T. SAGNA</t>
-        </is>
-      </c>
-      <c r="D525" t="n">
-        <v>5</v>
-      </c>
-      <c r="E525" t="n">
-        <v>9</v>
-      </c>
-      <c r="F525" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G525" t="n">
-        <v>0</v>
-      </c>
-      <c r="H525" t="n">
-        <v>0</v>
-      </c>
-      <c r="I525" t="n">
-        <v>0</v>
-      </c>
-      <c r="J525" t="n">
-        <v>1</v>
-      </c>
-      <c r="K525" t="n">
-        <v>0</v>
-      </c>
-      <c r="L525" t="n">
-        <v>0</v>
-      </c>
-      <c r="M525" t="n">
-        <v>0</v>
-      </c>
-      <c r="N525" t="n">
-        <v>0</v>
-      </c>
-      <c r="O525" t="n">
-        <v>0</v>
-      </c>
-      <c r="P525" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q525" t="n">
-        <v>0</v>
-      </c>
-      <c r="R525" t="n">
-        <v>1</v>
-      </c>
-      <c r="S525" t="n">
-        <v>0</v>
-      </c>
-      <c r="T525" t="n">
-        <v>0</v>
-      </c>
-      <c r="U525" t="n">
-        <v>0</v>
-      </c>
-      <c r="V525" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W525" t="n">
-        <v>24</v>
-      </c>
-      <c r="X525" t="inlineStr">
-        <is>
-          <t>BIELE ISB vs INSOLAC CAJA 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>J. CEBOLLA HERRERA | M. OLAIZOLA GARIN | N. WILLIAMS | O. ARDANZA BERNAOLA | T. SAGNA</t>
-        </is>
-      </c>
-      <c r="D526" t="n">
-        <v>5</v>
-      </c>
-      <c r="E526" t="n">
-        <v>7</v>
-      </c>
-      <c r="F526" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G526" t="n">
-        <v>0</v>
-      </c>
-      <c r="H526" t="n">
-        <v>0</v>
-      </c>
-      <c r="I526" t="n">
-        <v>1</v>
-      </c>
-      <c r="J526" t="n">
-        <v>0</v>
-      </c>
-      <c r="K526" t="n">
-        <v>0</v>
-      </c>
-      <c r="L526" t="n">
-        <v>0</v>
-      </c>
-      <c r="M526" t="n">
-        <v>0</v>
-      </c>
-      <c r="N526" t="n">
-        <v>0</v>
-      </c>
-      <c r="O526" t="n">
-        <v>0</v>
-      </c>
-      <c r="P526" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q526" t="n">
-        <v>0</v>
-      </c>
-      <c r="R526" t="n">
-        <v>1</v>
-      </c>
-      <c r="S526" t="n">
-        <v>0</v>
-      </c>
-      <c r="T526" t="n">
-        <v>0</v>
-      </c>
-      <c r="U526" t="n">
-        <v>1</v>
-      </c>
-      <c r="V526" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W526" t="n">
-        <v>24</v>
-      </c>
-      <c r="X526" t="inlineStr">
-        <is>
-          <t>BIELE ISB vs INSOLAC CAJA 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC</t>
-        </is>
-      </c>
-      <c r="D527" t="n">
-        <v>5</v>
-      </c>
-      <c r="E527" t="n">
-        <v>7</v>
-      </c>
-      <c r="F527" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G527" t="n">
-        <v>0</v>
-      </c>
-      <c r="H527" t="n">
-        <v>0</v>
-      </c>
-      <c r="I527" t="n">
-        <v>0</v>
-      </c>
-      <c r="J527" t="n">
-        <v>1</v>
-      </c>
-      <c r="K527" t="n">
-        <v>0</v>
-      </c>
-      <c r="L527" t="n">
-        <v>0</v>
-      </c>
-      <c r="M527" t="n">
-        <v>0</v>
-      </c>
-      <c r="N527" t="n">
-        <v>1</v>
-      </c>
-      <c r="O527" t="n">
-        <v>0</v>
-      </c>
-      <c r="P527" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q527" t="n">
-        <v>1</v>
-      </c>
-      <c r="R527" t="n">
-        <v>0</v>
-      </c>
-      <c r="S527" t="n">
-        <v>0</v>
-      </c>
-      <c r="T527" t="n">
-        <v>1</v>
-      </c>
-      <c r="U527" t="n">
-        <v>0</v>
-      </c>
-      <c r="V527" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W527" t="n">
-        <v>24</v>
-      </c>
-      <c r="X527" t="inlineStr">
-        <is>
-          <t>BIELE ISB vs INSOLAC CAJA 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ</t>
-        </is>
-      </c>
-      <c r="D528" t="n">
-        <v>5</v>
-      </c>
-      <c r="E528" t="n">
-        <v>33</v>
-      </c>
-      <c r="F528" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G528" t="n">
-        <v>5</v>
-      </c>
-      <c r="H528" t="n">
-        <v>0</v>
-      </c>
-      <c r="I528" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J528" t="n">
-        <v>1</v>
-      </c>
-      <c r="K528" t="n">
-        <v>568.1799999999999</v>
-      </c>
-      <c r="L528" t="n">
-        <v>0</v>
-      </c>
-      <c r="M528" t="n">
-        <v>568.1799999999999</v>
-      </c>
-      <c r="N528" t="n">
-        <v>1</v>
-      </c>
-      <c r="O528" t="n">
-        <v>2</v>
-      </c>
-      <c r="P528" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q528" t="n">
-        <v>1</v>
-      </c>
-      <c r="R528" t="n">
-        <v>1</v>
-      </c>
-      <c r="S528" t="n">
-        <v>0</v>
-      </c>
-      <c r="T528" t="n">
-        <v>0</v>
-      </c>
-      <c r="U528" t="n">
-        <v>0</v>
-      </c>
-      <c r="V528" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W528" t="n">
-        <v>24</v>
-      </c>
-      <c r="X528" t="inlineStr">
-        <is>
-          <t>BIELE ISB vs INSOLAC CAJA 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
-        </is>
-      </c>
-      <c r="D529" t="n">
-        <v>5</v>
-      </c>
-      <c r="E529" t="n">
-        <v>27</v>
-      </c>
-      <c r="F529" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G529" t="n">
-        <v>0</v>
-      </c>
-      <c r="H529" t="n">
-        <v>2</v>
-      </c>
-      <c r="I529" t="n">
-        <v>1</v>
-      </c>
-      <c r="J529" t="n">
-        <v>1</v>
-      </c>
-      <c r="K529" t="n">
-        <v>0</v>
-      </c>
-      <c r="L529" t="n">
-        <v>200</v>
-      </c>
-      <c r="M529" t="n">
-        <v>-200</v>
-      </c>
-      <c r="N529" t="n">
-        <v>1</v>
-      </c>
-      <c r="O529" t="n">
-        <v>0</v>
-      </c>
-      <c r="P529" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q529" t="n">
-        <v>0</v>
-      </c>
-      <c r="R529" t="n">
-        <v>1</v>
-      </c>
-      <c r="S529" t="n">
-        <v>0</v>
-      </c>
-      <c r="T529" t="n">
-        <v>0</v>
-      </c>
-      <c r="U529" t="n">
-        <v>0</v>
-      </c>
-      <c r="V529" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W529" t="n">
-        <v>24</v>
-      </c>
-      <c r="X529" t="inlineStr">
-        <is>
-          <t>BIELE ISB vs INSOLAC CAJA 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
-        </is>
-      </c>
-      <c r="D530" t="n">
-        <v>5</v>
-      </c>
-      <c r="E530" t="n">
-        <v>48</v>
-      </c>
-      <c r="F530" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G530" t="n">
-        <v>0</v>
-      </c>
-      <c r="H530" t="n">
-        <v>0</v>
-      </c>
-      <c r="I530" t="n">
-        <v>1</v>
-      </c>
-      <c r="J530" t="n">
-        <v>0</v>
-      </c>
-      <c r="K530" t="n">
-        <v>0</v>
-      </c>
-      <c r="L530" t="n">
-        <v>0</v>
-      </c>
-      <c r="M530" t="n">
-        <v>0</v>
-      </c>
-      <c r="N530" t="n">
-        <v>1</v>
-      </c>
-      <c r="O530" t="n">
-        <v>0</v>
-      </c>
-      <c r="P530" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q530" t="n">
-        <v>0</v>
-      </c>
-      <c r="R530" t="n">
-        <v>0</v>
-      </c>
-      <c r="S530" t="n">
-        <v>0</v>
-      </c>
-      <c r="T530" t="n">
-        <v>0</v>
-      </c>
-      <c r="U530" t="n">
-        <v>0</v>
-      </c>
-      <c r="V530" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W530" t="n">
-        <v>24</v>
-      </c>
-      <c r="X530" t="inlineStr">
-        <is>
-          <t>BIELE ISB vs INSOLAC CAJA 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
-        </is>
-      </c>
-      <c r="D531" t="n">
-        <v>5</v>
-      </c>
-      <c r="E531" t="n">
-        <v>162</v>
-      </c>
-      <c r="F531" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G531" t="n">
-        <v>5</v>
-      </c>
-      <c r="H531" t="n">
-        <v>9</v>
-      </c>
-      <c r="I531" t="n">
-        <v>3</v>
-      </c>
-      <c r="J531" t="n">
-        <v>3</v>
-      </c>
-      <c r="K531" t="n">
-        <v>166.67</v>
-      </c>
-      <c r="L531" t="n">
-        <v>300</v>
-      </c>
-      <c r="M531" t="n">
-        <v>-133.33</v>
-      </c>
-      <c r="N531" t="n">
-        <v>4</v>
-      </c>
-      <c r="O531" t="n">
-        <v>0</v>
-      </c>
-      <c r="P531" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q531" t="n">
-        <v>1</v>
-      </c>
-      <c r="R531" t="n">
-        <v>5</v>
-      </c>
-      <c r="S531" t="n">
-        <v>0</v>
-      </c>
-      <c r="T531" t="n">
-        <v>0</v>
-      </c>
-      <c r="U531" t="n">
-        <v>2</v>
-      </c>
-      <c r="V531" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W531" t="n">
-        <v>24</v>
-      </c>
-      <c r="X531" t="inlineStr">
-        <is>
-          <t>BIELE ISB vs INSOLAC CAJA 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>2487927</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>A. LAFUENTE SISO | A. PALAZUELOS PEREZ | E. KALINICENKO | W. LEVEQUE</t>
-        </is>
-      </c>
-      <c r="D532" t="n">
-        <v>4</v>
-      </c>
-      <c r="E532" t="n">
-        <v>74</v>
-      </c>
-      <c r="F532" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G532" t="n">
-        <v>2</v>
-      </c>
-      <c r="H532" t="n">
-        <v>1</v>
-      </c>
-      <c r="I532" t="n">
-        <v>2</v>
-      </c>
-      <c r="J532" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K532" t="n">
-        <v>100</v>
-      </c>
-      <c r="L532" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="M532" t="n">
-        <v>-13.64</v>
-      </c>
-      <c r="N532" t="n">
-        <v>2</v>
-      </c>
-      <c r="O532" t="n">
-        <v>0</v>
-      </c>
-      <c r="P532" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q532" t="n">
-        <v>0</v>
-      </c>
-      <c r="R532" t="n">
-        <v>0</v>
-      </c>
-      <c r="S532" t="n">
-        <v>2</v>
-      </c>
-      <c r="T532" t="n">
-        <v>1</v>
-      </c>
-      <c r="U532" t="n">
-        <v>1</v>
-      </c>
-      <c r="V532" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W532" t="n">
-        <v>25</v>
-      </c>
-      <c r="X532" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID vs CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>2487927</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>E. ARQUES LOPEZ | I. HANEY | J. HANNA | M. OCHI | P. ISERN MAZA</t>
-        </is>
-      </c>
-      <c r="D533" t="n">
-        <v>5</v>
-      </c>
-      <c r="E533" t="n">
-        <v>74</v>
-      </c>
-      <c r="F533" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G533" t="n">
-        <v>1</v>
-      </c>
-      <c r="H533" t="n">
-        <v>2</v>
-      </c>
-      <c r="I533" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J533" t="n">
-        <v>2</v>
-      </c>
-      <c r="K533" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="L533" t="n">
-        <v>100</v>
-      </c>
-      <c r="M533" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="N533" t="n">
-        <v>0</v>
-      </c>
-      <c r="O533" t="n">
-        <v>2</v>
-      </c>
-      <c r="P533" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q533" t="n">
-        <v>1</v>
-      </c>
-      <c r="R533" t="n">
-        <v>2</v>
-      </c>
-      <c r="S533" t="n">
-        <v>0</v>
-      </c>
-      <c r="T533" t="n">
-        <v>0</v>
-      </c>
-      <c r="U533" t="n">
-        <v>0</v>
-      </c>
-      <c r="V533" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W533" t="n">
-        <v>25</v>
-      </c>
-      <c r="X533" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID vs CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>2487928</t>
-        </is>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | S. KOCIC | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
-        </is>
-      </c>
-      <c r="D534" t="n">
-        <v>5</v>
-      </c>
-      <c r="E534" t="n">
-        <v>231</v>
-      </c>
-      <c r="F534" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="G534" t="n">
-        <v>6</v>
-      </c>
-      <c r="H534" t="n">
-        <v>5</v>
-      </c>
-      <c r="I534" t="n">
-        <v>9</v>
-      </c>
-      <c r="J534" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="K534" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="L534" t="n">
-        <v>70.62</v>
-      </c>
-      <c r="M534" t="n">
-        <v>-3.95</v>
-      </c>
-      <c r="N534" t="n">
-        <v>7</v>
-      </c>
-      <c r="O534" t="n">
-        <v>0</v>
-      </c>
-      <c r="P534" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q534" t="n">
-        <v>0</v>
-      </c>
-      <c r="R534" t="n">
-        <v>5</v>
-      </c>
-      <c r="S534" t="n">
-        <v>7</v>
-      </c>
-      <c r="T534" t="n">
-        <v>1</v>
-      </c>
-      <c r="U534" t="n">
-        <v>2</v>
-      </c>
-      <c r="V534" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W534" t="n">
-        <v>25</v>
-      </c>
-      <c r="X534" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>2487928</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>J. LAFUENTE VELAZQUEZ | S. KOCIC | S. MENDIOLA DIEZ | T. TEIXEIRA DO VALE DIAS | V. MORENO MARTIN</t>
-        </is>
-      </c>
-      <c r="D535" t="n">
-        <v>5</v>
-      </c>
-      <c r="E535" t="n">
-        <v>14</v>
-      </c>
-      <c r="F535" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G535" t="n">
-        <v>1</v>
-      </c>
-      <c r="H535" t="n">
-        <v>2</v>
-      </c>
-      <c r="I535" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J535" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K535" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="L535" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="M535" t="n">
-        <v>-113.64</v>
-      </c>
-      <c r="N535" t="n">
-        <v>0</v>
-      </c>
-      <c r="O535" t="n">
-        <v>2</v>
-      </c>
-      <c r="P535" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q535" t="n">
-        <v>0</v>
-      </c>
-      <c r="R535" t="n">
-        <v>1</v>
-      </c>
-      <c r="S535" t="n">
-        <v>2</v>
-      </c>
-      <c r="T535" t="n">
-        <v>0</v>
-      </c>
-      <c r="U535" t="n">
-        <v>1</v>
-      </c>
-      <c r="V535" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W535" t="n">
-        <v>25</v>
-      </c>
-      <c r="X535" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>2487928</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>A. RODRIGUEZ AGUILAR | D. ROLLINS | F. BELLO MOURE | P. SANCHEZ INFANTES | S. NDIAYE</t>
-        </is>
-      </c>
-      <c r="D536" t="n">
-        <v>5</v>
-      </c>
-      <c r="E536" t="n">
-        <v>69</v>
-      </c>
-      <c r="F536" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="G536" t="n">
-        <v>2</v>
-      </c>
-      <c r="H536" t="n">
-        <v>0</v>
-      </c>
-      <c r="I536" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J536" t="n">
-        <v>2</v>
-      </c>
-      <c r="K536" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="L536" t="n">
-        <v>0</v>
-      </c>
-      <c r="M536" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="N536" t="n">
-        <v>0</v>
-      </c>
-      <c r="O536" t="n">
-        <v>2</v>
-      </c>
-      <c r="P536" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q536" t="n">
-        <v>0</v>
-      </c>
-      <c r="R536" t="n">
-        <v>1</v>
-      </c>
-      <c r="S536" t="n">
-        <v>0</v>
-      </c>
-      <c r="T536" t="n">
-        <v>1</v>
-      </c>
-      <c r="U536" t="n">
-        <v>0</v>
-      </c>
-      <c r="V536" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W536" t="n">
-        <v>25</v>
-      </c>
-      <c r="X536" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>2487928</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>A. RODRIGUEZ AGUILAR | D. ROLLINS | J. SIENCHE GUEMETA | P. SANCHEZ INFANTES | S. NDIAYE</t>
-        </is>
-      </c>
-      <c r="D537" t="n">
-        <v>5</v>
-      </c>
-      <c r="E537" t="n">
-        <v>23</v>
-      </c>
-      <c r="F537" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G537" t="n">
-        <v>1</v>
-      </c>
-      <c r="H537" t="n">
-        <v>0</v>
-      </c>
-      <c r="I537" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J537" t="n">
-        <v>1</v>
-      </c>
-      <c r="K537" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="L537" t="n">
-        <v>0</v>
-      </c>
-      <c r="M537" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="N537" t="n">
-        <v>0</v>
-      </c>
-      <c r="O537" t="n">
-        <v>2</v>
-      </c>
-      <c r="P537" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q537" t="n">
-        <v>0</v>
-      </c>
-      <c r="R537" t="n">
-        <v>1</v>
-      </c>
-      <c r="S537" t="n">
-        <v>0</v>
-      </c>
-      <c r="T537" t="n">
-        <v>0</v>
-      </c>
-      <c r="U537" t="n">
-        <v>0</v>
-      </c>
-      <c r="V537" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W537" t="n">
-        <v>25</v>
-      </c>
-      <c r="X537" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>2487928</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>A. RODRIGUEZ AGUILAR | F. BELLO MOURE | J. SIENCHE GUEMETA | P. SANCHEZ INFANTES | S. NDIAYE</t>
-        </is>
-      </c>
-      <c r="D538" t="n">
-        <v>5</v>
-      </c>
-      <c r="E538" t="n">
-        <v>14</v>
-      </c>
-      <c r="F538" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G538" t="n">
-        <v>2</v>
-      </c>
-      <c r="H538" t="n">
-        <v>1</v>
-      </c>
-      <c r="I538" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J538" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K538" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="L538" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="M538" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="N538" t="n">
-        <v>1</v>
-      </c>
-      <c r="O538" t="n">
-        <v>2</v>
-      </c>
-      <c r="P538" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q538" t="n">
-        <v>1</v>
-      </c>
-      <c r="R538" t="n">
-        <v>0</v>
-      </c>
-      <c r="S538" t="n">
-        <v>2</v>
-      </c>
-      <c r="T538" t="n">
-        <v>0</v>
-      </c>
-      <c r="U538" t="n">
-        <v>0</v>
-      </c>
-      <c r="V538" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W538" t="n">
-        <v>25</v>
-      </c>
-      <c r="X538" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>2487928</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>D. ROLLINS | J. SIENCHE GUEMETA | K. SCHUTTE | P. SANCHEZ INFANTES | S. NDIAYE</t>
-        </is>
-      </c>
-      <c r="D539" t="n">
-        <v>5</v>
-      </c>
-      <c r="E539" t="n">
-        <v>40</v>
-      </c>
-      <c r="F539" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G539" t="n">
-        <v>0</v>
-      </c>
-      <c r="H539" t="n">
-        <v>3</v>
-      </c>
-      <c r="I539" t="n">
-        <v>2</v>
-      </c>
-      <c r="J539" t="n">
-        <v>2</v>
-      </c>
-      <c r="K539" t="n">
-        <v>0</v>
-      </c>
-      <c r="L539" t="n">
-        <v>150</v>
-      </c>
-      <c r="M539" t="n">
-        <v>-150</v>
-      </c>
-      <c r="N539" t="n">
-        <v>2</v>
-      </c>
-      <c r="O539" t="n">
-        <v>0</v>
-      </c>
-      <c r="P539" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q539" t="n">
-        <v>0</v>
-      </c>
-      <c r="R539" t="n">
-        <v>2</v>
-      </c>
-      <c r="S539" t="n">
-        <v>0</v>
-      </c>
-      <c r="T539" t="n">
-        <v>0</v>
-      </c>
-      <c r="U539" t="n">
-        <v>0</v>
-      </c>
-      <c r="V539" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W539" t="n">
-        <v>25</v>
-      </c>
-      <c r="X539" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>2487928</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>F. BELLO MOURE | J. SIENCHE GUEMETA | K. SCHUTTE | P. SANCHEZ INFANTES | S. NDIAYE</t>
-        </is>
-      </c>
-      <c r="D540" t="n">
-        <v>5</v>
-      </c>
-      <c r="E540" t="n">
-        <v>99</v>
-      </c>
-      <c r="F540" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G540" t="n">
-        <v>2</v>
-      </c>
-      <c r="H540" t="n">
-        <v>3</v>
-      </c>
-      <c r="I540" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J540" t="n">
-        <v>4</v>
-      </c>
-      <c r="K540" t="n">
-        <v>60.24</v>
-      </c>
-      <c r="L540" t="n">
-        <v>75</v>
-      </c>
-      <c r="M540" t="n">
-        <v>-14.76</v>
-      </c>
-      <c r="N540" t="n">
-        <v>3</v>
-      </c>
-      <c r="O540" t="n">
-        <v>3</v>
-      </c>
-      <c r="P540" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q540" t="n">
-        <v>2</v>
-      </c>
-      <c r="R540" t="n">
-        <v>3</v>
-      </c>
-      <c r="S540" t="n">
-        <v>0</v>
-      </c>
-      <c r="T540" t="n">
-        <v>1</v>
-      </c>
-      <c r="U540" t="n">
-        <v>0</v>
-      </c>
-      <c r="V540" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W540" t="n">
-        <v>25</v>
-      </c>
-      <c r="X540" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>A. LATORRE SANCHEZ | G. CLARKE | J. FRANCH DE PABLO | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
-        </is>
-      </c>
-      <c r="D541" t="n">
-        <v>5</v>
-      </c>
-      <c r="E541" t="n">
-        <v>76</v>
-      </c>
-      <c r="F541" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G541" t="n">
-        <v>0</v>
-      </c>
-      <c r="H541" t="n">
-        <v>0</v>
-      </c>
-      <c r="I541" t="n">
-        <v>0</v>
-      </c>
-      <c r="J541" t="n">
-        <v>2</v>
-      </c>
-      <c r="K541" t="n">
-        <v>0</v>
-      </c>
-      <c r="L541" t="n">
-        <v>0</v>
-      </c>
-      <c r="M541" t="n">
-        <v>0</v>
-      </c>
-      <c r="N541" t="n">
-        <v>0</v>
-      </c>
-      <c r="O541" t="n">
-        <v>0</v>
-      </c>
-      <c r="P541" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q541" t="n">
-        <v>0</v>
-      </c>
-      <c r="R541" t="n">
-        <v>1</v>
-      </c>
-      <c r="S541" t="n">
-        <v>0</v>
-      </c>
-      <c r="T541" t="n">
-        <v>1</v>
-      </c>
-      <c r="U541" t="n">
-        <v>0</v>
-      </c>
-      <c r="V541" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W541" t="n">
-        <v>25</v>
-      </c>
-      <c r="X541" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>A. LATORRE SANCHEZ | J. FRANCH DE PABLO | N. DEDOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
-        </is>
-      </c>
-      <c r="D542" t="n">
-        <v>5</v>
-      </c>
-      <c r="E542" t="n">
-        <v>16</v>
-      </c>
-      <c r="F542" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G542" t="n">
-        <v>2</v>
-      </c>
-      <c r="H542" t="n">
-        <v>0</v>
-      </c>
-      <c r="I542" t="n">
-        <v>1</v>
-      </c>
-      <c r="J542" t="n">
-        <v>0</v>
-      </c>
-      <c r="K542" t="n">
-        <v>200</v>
-      </c>
-      <c r="L542" t="n">
-        <v>0</v>
-      </c>
-      <c r="M542" t="n">
-        <v>0</v>
-      </c>
-      <c r="N542" t="n">
-        <v>1</v>
-      </c>
-      <c r="O542" t="n">
-        <v>0</v>
-      </c>
-      <c r="P542" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q542" t="n">
-        <v>0</v>
-      </c>
-      <c r="R542" t="n">
-        <v>0</v>
-      </c>
-      <c r="S542" t="n">
-        <v>0</v>
-      </c>
-      <c r="T542" t="n">
-        <v>0</v>
-      </c>
-      <c r="U542" t="n">
-        <v>0</v>
-      </c>
-      <c r="V542" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W542" t="n">
-        <v>25</v>
-      </c>
-      <c r="X542" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>A. MOODY | G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | W. CABRAL BUERIBERI</t>
-        </is>
-      </c>
-      <c r="D543" t="n">
-        <v>5</v>
-      </c>
-      <c r="E543" t="n">
-        <v>108</v>
-      </c>
-      <c r="F543" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G543" t="n">
-        <v>0</v>
-      </c>
-      <c r="H543" t="n">
-        <v>0</v>
-      </c>
-      <c r="I543" t="n">
-        <v>1</v>
-      </c>
-      <c r="J543" t="n">
-        <v>2</v>
-      </c>
-      <c r="K543" t="n">
-        <v>0</v>
-      </c>
-      <c r="L543" t="n">
-        <v>0</v>
-      </c>
-      <c r="M543" t="n">
-        <v>0</v>
-      </c>
-      <c r="N543" t="n">
-        <v>1</v>
-      </c>
-      <c r="O543" t="n">
-        <v>0</v>
-      </c>
-      <c r="P543" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q543" t="n">
-        <v>1</v>
-      </c>
-      <c r="R543" t="n">
-        <v>2</v>
-      </c>
-      <c r="S543" t="n">
-        <v>0</v>
-      </c>
-      <c r="T543" t="n">
-        <v>0</v>
-      </c>
-      <c r="U543" t="n">
-        <v>0</v>
-      </c>
-      <c r="V543" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W543" t="n">
-        <v>25</v>
-      </c>
-      <c r="X543" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
-        </is>
-      </c>
-      <c r="D544" t="n">
-        <v>5</v>
-      </c>
-      <c r="E544" t="n">
-        <v>72</v>
-      </c>
-      <c r="F544" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G544" t="n">
-        <v>2</v>
-      </c>
-      <c r="H544" t="n">
-        <v>0</v>
-      </c>
-      <c r="I544" t="n">
-        <v>2</v>
-      </c>
-      <c r="J544" t="n">
-        <v>2</v>
-      </c>
-      <c r="K544" t="n">
-        <v>100</v>
-      </c>
-      <c r="L544" t="n">
-        <v>0</v>
-      </c>
-      <c r="M544" t="n">
-        <v>100</v>
-      </c>
-      <c r="N544" t="n">
-        <v>3</v>
-      </c>
-      <c r="O544" t="n">
-        <v>0</v>
-      </c>
-      <c r="P544" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q544" t="n">
-        <v>1</v>
-      </c>
-      <c r="R544" t="n">
-        <v>2</v>
-      </c>
-      <c r="S544" t="n">
-        <v>0</v>
-      </c>
-      <c r="T544" t="n">
-        <v>0</v>
-      </c>
-      <c r="U544" t="n">
-        <v>0</v>
-      </c>
-      <c r="V544" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W544" t="n">
-        <v>25</v>
-      </c>
-      <c r="X544" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
-        </is>
-      </c>
-      <c r="D545" t="n">
-        <v>5</v>
-      </c>
-      <c r="E545" t="n">
-        <v>25</v>
-      </c>
-      <c r="F545" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G545" t="n">
-        <v>2</v>
-      </c>
-      <c r="H545" t="n">
-        <v>3</v>
-      </c>
-      <c r="I545" t="n">
-        <v>1</v>
-      </c>
-      <c r="J545" t="n">
-        <v>1</v>
-      </c>
-      <c r="K545" t="n">
-        <v>200</v>
-      </c>
-      <c r="L545" t="n">
-        <v>300</v>
-      </c>
-      <c r="M545" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N545" t="n">
-        <v>1</v>
-      </c>
-      <c r="O545" t="n">
-        <v>0</v>
-      </c>
-      <c r="P545" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q545" t="n">
-        <v>0</v>
-      </c>
-      <c r="R545" t="n">
-        <v>1</v>
-      </c>
-      <c r="S545" t="n">
-        <v>0</v>
-      </c>
-      <c r="T545" t="n">
-        <v>0</v>
-      </c>
-      <c r="U545" t="n">
-        <v>0</v>
-      </c>
-      <c r="V545" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W545" t="n">
-        <v>25</v>
-      </c>
-      <c r="X545" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER</t>
-        </is>
-      </c>
-      <c r="D546" t="n">
-        <v>5</v>
-      </c>
-      <c r="E546" t="n">
-        <v>25</v>
-      </c>
-      <c r="F546" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G546" t="n">
-        <v>3</v>
-      </c>
-      <c r="H546" t="n">
-        <v>2</v>
-      </c>
-      <c r="I546" t="n">
-        <v>1</v>
-      </c>
-      <c r="J546" t="n">
-        <v>1</v>
-      </c>
-      <c r="K546" t="n">
-        <v>300</v>
-      </c>
-      <c r="L546" t="n">
-        <v>200</v>
-      </c>
-      <c r="M546" t="n">
-        <v>100</v>
-      </c>
-      <c r="N546" t="n">
-        <v>1</v>
-      </c>
-      <c r="O546" t="n">
-        <v>0</v>
-      </c>
-      <c r="P546" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q546" t="n">
-        <v>0</v>
-      </c>
-      <c r="R546" t="n">
-        <v>1</v>
-      </c>
-      <c r="S546" t="n">
-        <v>0</v>
-      </c>
-      <c r="T546" t="n">
-        <v>0</v>
-      </c>
-      <c r="U546" t="n">
-        <v>0</v>
-      </c>
-      <c r="V546" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W546" t="n">
-        <v>25</v>
-      </c>
-      <c r="X546" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
-        </is>
-      </c>
-      <c r="D547" t="n">
-        <v>5</v>
-      </c>
-      <c r="E547" t="n">
-        <v>184</v>
-      </c>
-      <c r="F547" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="G547" t="n">
-        <v>0</v>
-      </c>
-      <c r="H547" t="n">
-        <v>0</v>
-      </c>
-      <c r="I547" t="n">
-        <v>4</v>
-      </c>
-      <c r="J547" t="n">
-        <v>1</v>
-      </c>
-      <c r="K547" t="n">
-        <v>0</v>
-      </c>
-      <c r="L547" t="n">
-        <v>0</v>
-      </c>
-      <c r="M547" t="n">
-        <v>0</v>
-      </c>
-      <c r="N547" t="n">
-        <v>3</v>
-      </c>
-      <c r="O547" t="n">
-        <v>0</v>
-      </c>
-      <c r="P547" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q547" t="n">
-        <v>0</v>
-      </c>
-      <c r="R547" t="n">
-        <v>1</v>
-      </c>
-      <c r="S547" t="n">
-        <v>0</v>
-      </c>
-      <c r="T547" t="n">
-        <v>1</v>
-      </c>
-      <c r="U547" t="n">
-        <v>1</v>
-      </c>
-      <c r="V547" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W547" t="n">
-        <v>25</v>
-      </c>
-      <c r="X547" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SANTOS SPENCER | W. NIANG</t>
-        </is>
-      </c>
-      <c r="D548" t="n">
-        <v>5</v>
-      </c>
-      <c r="E548" t="n">
-        <v>16</v>
-      </c>
-      <c r="F548" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G548" t="n">
-        <v>0</v>
-      </c>
-      <c r="H548" t="n">
-        <v>2</v>
-      </c>
-      <c r="I548" t="n">
-        <v>0</v>
-      </c>
-      <c r="J548" t="n">
-        <v>1</v>
-      </c>
-      <c r="K548" t="n">
-        <v>0</v>
-      </c>
-      <c r="L548" t="n">
-        <v>200</v>
-      </c>
-      <c r="M548" t="n">
-        <v>0</v>
-      </c>
-      <c r="N548" t="n">
-        <v>0</v>
-      </c>
-      <c r="O548" t="n">
-        <v>0</v>
-      </c>
-      <c r="P548" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q548" t="n">
-        <v>0</v>
-      </c>
-      <c r="R548" t="n">
-        <v>1</v>
-      </c>
-      <c r="S548" t="n">
-        <v>0</v>
-      </c>
-      <c r="T548" t="n">
-        <v>0</v>
-      </c>
-      <c r="U548" t="n">
-        <v>0</v>
-      </c>
-      <c r="V548" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W548" t="n">
-        <v>25</v>
-      </c>
-      <c r="X548" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>A. PLITZUWEIT | B. AREVALO SAENZ | L. OBAJO BELTRAN | S. SERRATO BALLETBO | W. NIANG</t>
-        </is>
-      </c>
-      <c r="D549" t="n">
-        <v>5</v>
-      </c>
-      <c r="E549" t="n">
-        <v>72</v>
-      </c>
-      <c r="F549" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G549" t="n">
-        <v>0</v>
-      </c>
-      <c r="H549" t="n">
-        <v>2</v>
-      </c>
-      <c r="I549" t="n">
-        <v>2</v>
-      </c>
-      <c r="J549" t="n">
-        <v>2</v>
-      </c>
-      <c r="K549" t="n">
-        <v>0</v>
-      </c>
-      <c r="L549" t="n">
-        <v>100</v>
-      </c>
-      <c r="M549" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N549" t="n">
-        <v>2</v>
-      </c>
-      <c r="O549" t="n">
-        <v>0</v>
-      </c>
-      <c r="P549" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q549" t="n">
-        <v>0</v>
-      </c>
-      <c r="R549" t="n">
-        <v>3</v>
-      </c>
-      <c r="S549" t="n">
-        <v>0</v>
-      </c>
-      <c r="T549" t="n">
-        <v>0</v>
-      </c>
-      <c r="U549" t="n">
-        <v>1</v>
-      </c>
-      <c r="V549" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W549" t="n">
-        <v>25</v>
-      </c>
-      <c r="X549" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>2487938</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>A. TRAORE | D. CEBOLLA PORCAR | E. VAN DER HEIJDEN | J. LLAMAS PRADO | M. DENG</t>
-        </is>
-      </c>
-      <c r="D550" t="n">
-        <v>5</v>
-      </c>
-      <c r="E550" t="n">
-        <v>91</v>
-      </c>
-      <c r="F550" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G550" t="n">
-        <v>4</v>
-      </c>
-      <c r="H550" t="n">
-        <v>5</v>
-      </c>
-      <c r="I550" t="n">
-        <v>3</v>
-      </c>
-      <c r="J550" t="n">
-        <v>3</v>
-      </c>
-      <c r="K550" t="n">
-        <v>133.33</v>
-      </c>
-      <c r="L550" t="n">
-        <v>166.67</v>
-      </c>
-      <c r="M550" t="n">
-        <v>-33.33</v>
-      </c>
-      <c r="N550" t="n">
-        <v>3</v>
-      </c>
-      <c r="O550" t="n">
-        <v>0</v>
-      </c>
-      <c r="P550" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q550" t="n">
-        <v>0</v>
-      </c>
-      <c r="R550" t="n">
-        <v>3</v>
-      </c>
-      <c r="S550" t="n">
-        <v>0</v>
-      </c>
-      <c r="T550" t="n">
-        <v>2</v>
-      </c>
-      <c r="U550" t="n">
-        <v>2</v>
-      </c>
-      <c r="V550" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W550" t="n">
-        <v>26</v>
-      </c>
-      <c r="X550" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>2487938</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>D. CEBOLLA PORCAR | D. HAYMAN | E. VAN DER HEIJDEN | J. LLAMAS PRADO | M. DENG</t>
-        </is>
-      </c>
-      <c r="D551" t="n">
-        <v>5</v>
-      </c>
-      <c r="E551" t="n">
-        <v>5</v>
-      </c>
-      <c r="F551" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G551" t="n">
-        <v>0</v>
-      </c>
-      <c r="H551" t="n">
-        <v>1</v>
-      </c>
-      <c r="I551" t="n">
-        <v>0</v>
-      </c>
-      <c r="J551" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="K551" t="n">
-        <v>0</v>
-      </c>
-      <c r="L551" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="M551" t="n">
-        <v>0</v>
-      </c>
-      <c r="N551" t="n">
-        <v>0</v>
-      </c>
-      <c r="O551" t="n">
-        <v>0</v>
-      </c>
-      <c r="P551" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q551" t="n">
-        <v>0</v>
-      </c>
-      <c r="R551" t="n">
-        <v>0</v>
-      </c>
-      <c r="S551" t="n">
-        <v>4</v>
-      </c>
-      <c r="T551" t="n">
-        <v>0</v>
-      </c>
-      <c r="U551" t="n">
-        <v>0</v>
-      </c>
-      <c r="V551" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W551" t="n">
-        <v>26</v>
-      </c>
-      <c r="X551" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>2487938</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>C. JACOBS | J. PARDINA MOLINA | K. TORRES CUEVAS | M. DE PABLO DEL CASTILLO | P. DIENE</t>
-        </is>
-      </c>
-      <c r="D552" t="n">
-        <v>5</v>
-      </c>
-      <c r="E552" t="n">
-        <v>62</v>
-      </c>
-      <c r="F552" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="G552" t="n">
-        <v>5</v>
-      </c>
-      <c r="H552" t="n">
-        <v>2</v>
-      </c>
-      <c r="I552" t="n">
-        <v>3</v>
-      </c>
-      <c r="J552" t="n">
-        <v>1</v>
-      </c>
-      <c r="K552" t="n">
-        <v>166.67</v>
-      </c>
-      <c r="L552" t="n">
-        <v>200</v>
-      </c>
-      <c r="M552" t="n">
-        <v>-33.33</v>
-      </c>
-      <c r="N552" t="n">
-        <v>3</v>
-      </c>
-      <c r="O552" t="n">
-        <v>0</v>
-      </c>
-      <c r="P552" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q552" t="n">
-        <v>1</v>
-      </c>
-      <c r="R552" t="n">
-        <v>1</v>
-      </c>
-      <c r="S552" t="n">
-        <v>0</v>
-      </c>
-      <c r="T552" t="n">
-        <v>0</v>
-      </c>
-      <c r="U552" t="n">
-        <v>0</v>
-      </c>
-      <c r="V552" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W552" t="n">
-        <v>26</v>
-      </c>
-      <c r="X552" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>2487938</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>C. JACOBS | J. PARDINA MOLINA | K. TORRES CUEVAS | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
-        </is>
-      </c>
-      <c r="D553" t="n">
-        <v>5</v>
-      </c>
-      <c r="E553" t="n">
-        <v>1</v>
-      </c>
-      <c r="F553" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G553" t="n">
-        <v>1</v>
-      </c>
-      <c r="H553" t="n">
-        <v>0</v>
-      </c>
-      <c r="I553" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J553" t="n">
-        <v>0</v>
-      </c>
-      <c r="K553" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="L553" t="n">
-        <v>0</v>
-      </c>
-      <c r="M553" t="n">
-        <v>0</v>
-      </c>
-      <c r="N553" t="n">
-        <v>0</v>
-      </c>
-      <c r="O553" t="n">
-        <v>2</v>
-      </c>
-      <c r="P553" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q553" t="n">
-        <v>0</v>
-      </c>
-      <c r="R553" t="n">
-        <v>0</v>
-      </c>
-      <c r="S553" t="n">
-        <v>0</v>
-      </c>
-      <c r="T553" t="n">
-        <v>0</v>
-      </c>
-      <c r="U553" t="n">
-        <v>0</v>
-      </c>
-      <c r="V553" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W553" t="n">
-        <v>26</v>
-      </c>
-      <c r="X553" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>2487938</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>J. PARDINA MOLINA | K. TORRES CUEVAS | M. DE PABLO DEL CASTILLO | P. DIENE | R. UKAWUBA</t>
-        </is>
-      </c>
-      <c r="D554" t="n">
-        <v>5</v>
-      </c>
-      <c r="E554" t="n">
-        <v>33</v>
-      </c>
-      <c r="F554" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G554" t="n">
-        <v>0</v>
-      </c>
-      <c r="H554" t="n">
-        <v>2</v>
-      </c>
-      <c r="I554" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J554" t="n">
-        <v>2</v>
-      </c>
-      <c r="K554" t="n">
-        <v>0</v>
-      </c>
-      <c r="L554" t="n">
-        <v>100</v>
-      </c>
-      <c r="M554" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N554" t="n">
-        <v>0</v>
-      </c>
-      <c r="O554" t="n">
-        <v>2</v>
-      </c>
-      <c r="P554" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q554" t="n">
-        <v>1</v>
-      </c>
-      <c r="R554" t="n">
-        <v>2</v>
-      </c>
-      <c r="S554" t="n">
-        <v>0</v>
-      </c>
-      <c r="T554" t="n">
-        <v>0</v>
-      </c>
-      <c r="U554" t="n">
-        <v>0</v>
-      </c>
-      <c r="V554" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W554" t="n">
-        <v>26</v>
-      </c>
-      <c r="X554" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>2487940</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>A. LAFUENTE SISO | A. MAZAIRA GOMEZ | A. PALAZUELOS PEREZ | E. KALINICENKO | W. LEVEQUE</t>
-        </is>
-      </c>
-      <c r="D555" t="n">
-        <v>5</v>
-      </c>
-      <c r="E555" t="n">
-        <v>287</v>
-      </c>
-      <c r="F555" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="G555" t="n">
-        <v>10</v>
-      </c>
-      <c r="H555" t="n">
-        <v>5</v>
-      </c>
-      <c r="I555" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="J555" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="K555" t="n">
-        <v>88.34</v>
-      </c>
-      <c r="L555" t="n">
-        <v>57.08</v>
-      </c>
-      <c r="M555" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="N555" t="n">
-        <v>8</v>
-      </c>
-      <c r="O555" t="n">
-        <v>3</v>
-      </c>
-      <c r="P555" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q555" t="n">
-        <v>1</v>
-      </c>
-      <c r="R555" t="n">
-        <v>5</v>
-      </c>
-      <c r="S555" t="n">
-        <v>4</v>
-      </c>
-      <c r="T555" t="n">
-        <v>3</v>
-      </c>
-      <c r="U555" t="n">
-        <v>1</v>
-      </c>
-      <c r="V555" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W555" t="n">
-        <v>26</v>
-      </c>
-      <c r="X555" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>2487940</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>A. LAFUENTE SISO | A. MAZAIRA GOMEZ | A. PALAZUELOS PEREZ | M. STRIKKER | W. LEVEQUE</t>
-        </is>
-      </c>
-      <c r="D556" t="n">
-        <v>5</v>
-      </c>
-      <c r="E556" t="n">
-        <v>1</v>
-      </c>
-      <c r="F556" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G556" t="n">
-        <v>0</v>
-      </c>
-      <c r="H556" t="n">
-        <v>2</v>
-      </c>
-      <c r="I556" t="n">
-        <v>0</v>
-      </c>
-      <c r="J556" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K556" t="n">
-        <v>0</v>
-      </c>
-      <c r="L556" t="n">
-        <v>151.52</v>
-      </c>
-      <c r="M556" t="n">
-        <v>0</v>
-      </c>
-      <c r="N556" t="n">
-        <v>0</v>
-      </c>
-      <c r="O556" t="n">
-        <v>0</v>
-      </c>
-      <c r="P556" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q556" t="n">
-        <v>0</v>
-      </c>
-      <c r="R556" t="n">
-        <v>0</v>
-      </c>
-      <c r="S556" t="n">
-        <v>3</v>
-      </c>
-      <c r="T556" t="n">
-        <v>0</v>
-      </c>
-      <c r="U556" t="n">
-        <v>0</v>
-      </c>
-      <c r="V556" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W556" t="n">
-        <v>26</v>
-      </c>
-      <c r="X556" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>2487940</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>F. SIERRA GALA | J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | V. MORENO MARTIN</t>
-        </is>
-      </c>
-      <c r="D557" t="n">
-        <v>5</v>
-      </c>
-      <c r="E557" t="n">
-        <v>6</v>
-      </c>
-      <c r="F557" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G557" t="n">
-        <v>2</v>
-      </c>
-      <c r="H557" t="n">
-        <v>6</v>
-      </c>
-      <c r="I557" t="n">
-        <v>1</v>
-      </c>
-      <c r="J557" t="n">
-        <v>2</v>
-      </c>
-      <c r="K557" t="n">
-        <v>200</v>
-      </c>
-      <c r="L557" t="n">
-        <v>300</v>
-      </c>
-      <c r="M557" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N557" t="n">
-        <v>1</v>
-      </c>
-      <c r="O557" t="n">
-        <v>0</v>
-      </c>
-      <c r="P557" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q557" t="n">
-        <v>0</v>
-      </c>
-      <c r="R557" t="n">
-        <v>2</v>
-      </c>
-      <c r="S557" t="n">
-        <v>0</v>
-      </c>
-      <c r="T557" t="n">
-        <v>0</v>
-      </c>
-      <c r="U557" t="n">
-        <v>0</v>
-      </c>
-      <c r="V557" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W557" t="n">
-        <v>26</v>
-      </c>
-      <c r="X557" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>2487940</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>F. SIERRA GALA | J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
-        </is>
-      </c>
-      <c r="D558" t="n">
-        <v>5</v>
-      </c>
-      <c r="E558" t="n">
-        <v>282</v>
-      </c>
-      <c r="F558" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G558" t="n">
-        <v>5</v>
-      </c>
-      <c r="H558" t="n">
-        <v>4</v>
-      </c>
-      <c r="I558" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="J558" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="K558" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="L558" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="M558" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="N558" t="n">
-        <v>4</v>
-      </c>
-      <c r="O558" t="n">
-        <v>7</v>
-      </c>
-      <c r="P558" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q558" t="n">
-        <v>1</v>
-      </c>
-      <c r="R558" t="n">
-        <v>6</v>
-      </c>
-      <c r="S558" t="n">
-        <v>3</v>
-      </c>
-      <c r="T558" t="n">
-        <v>3</v>
-      </c>
-      <c r="U558" t="n">
-        <v>1</v>
-      </c>
-      <c r="V558" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W558" t="n">
-        <v>26</v>
-      </c>
-      <c r="X558" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>C. FIELDS | G. BOAHEN | G. VERGARA HARBOE | K. FELIZOR | M. TIKHONENKO ANDRIYASHCHENKO</t>
-        </is>
-      </c>
-      <c r="D559" t="n">
-        <v>5</v>
-      </c>
-      <c r="E559" t="n">
-        <v>14</v>
-      </c>
-      <c r="F559" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G559" t="n">
-        <v>3</v>
-      </c>
-      <c r="H559" t="n">
-        <v>0</v>
-      </c>
-      <c r="I559" t="n">
-        <v>0</v>
-      </c>
-      <c r="J559" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K559" t="n">
-        <v>0</v>
-      </c>
-      <c r="L559" t="n">
-        <v>0</v>
-      </c>
-      <c r="M559" t="n">
-        <v>0</v>
-      </c>
-      <c r="N559" t="n">
-        <v>1</v>
-      </c>
-      <c r="O559" t="n">
-        <v>0</v>
-      </c>
-      <c r="P559" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q559" t="n">
-        <v>1</v>
-      </c>
-      <c r="R559" t="n">
-        <v>1</v>
-      </c>
-      <c r="S559" t="n">
-        <v>2</v>
-      </c>
-      <c r="T559" t="n">
-        <v>0</v>
-      </c>
-      <c r="U559" t="n">
-        <v>1</v>
-      </c>
-      <c r="V559" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W559" t="n">
-        <v>26</v>
-      </c>
-      <c r="X559" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>C. FIELDS | G. BOAHEN | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | K. FELIZOR</t>
-        </is>
-      </c>
-      <c r="D560" t="n">
-        <v>5</v>
-      </c>
-      <c r="E560" t="n">
-        <v>28</v>
-      </c>
-      <c r="F560" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G560" t="n">
-        <v>0</v>
-      </c>
-      <c r="H560" t="n">
-        <v>5</v>
-      </c>
-      <c r="I560" t="n">
-        <v>1</v>
-      </c>
-      <c r="J560" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K560" t="n">
-        <v>0</v>
-      </c>
-      <c r="L560" t="n">
-        <v>378.79</v>
-      </c>
-      <c r="M560" t="n">
-        <v>-378.79</v>
-      </c>
-      <c r="N560" t="n">
-        <v>1</v>
-      </c>
-      <c r="O560" t="n">
-        <v>0</v>
-      </c>
-      <c r="P560" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q560" t="n">
-        <v>0</v>
-      </c>
-      <c r="R560" t="n">
-        <v>1</v>
-      </c>
-      <c r="S560" t="n">
-        <v>3</v>
-      </c>
-      <c r="T560" t="n">
-        <v>0</v>
-      </c>
-      <c r="U560" t="n">
-        <v>1</v>
-      </c>
-      <c r="V560" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W560" t="n">
-        <v>26</v>
-      </c>
-      <c r="X560" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>C. FIELDS | G. BOAHEN | J. MORENO POZA | J. SANTA BARBARA CARCELEN | K. FELIZOR</t>
-        </is>
-      </c>
-      <c r="D561" t="n">
-        <v>5</v>
-      </c>
-      <c r="E561" t="n">
-        <v>43</v>
-      </c>
-      <c r="F561" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G561" t="n">
-        <v>2</v>
-      </c>
-      <c r="H561" t="n">
-        <v>0</v>
-      </c>
-      <c r="I561" t="n">
-        <v>2</v>
-      </c>
-      <c r="J561" t="n">
-        <v>1</v>
-      </c>
-      <c r="K561" t="n">
-        <v>100</v>
-      </c>
-      <c r="L561" t="n">
-        <v>0</v>
-      </c>
-      <c r="M561" t="n">
-        <v>100</v>
-      </c>
-      <c r="N561" t="n">
-        <v>2</v>
-      </c>
-      <c r="O561" t="n">
-        <v>0</v>
-      </c>
-      <c r="P561" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q561" t="n">
-        <v>1</v>
-      </c>
-      <c r="R561" t="n">
-        <v>1</v>
-      </c>
-      <c r="S561" t="n">
-        <v>0</v>
-      </c>
-      <c r="T561" t="n">
-        <v>0</v>
-      </c>
-      <c r="U561" t="n">
-        <v>0</v>
-      </c>
-      <c r="V561" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W561" t="n">
-        <v>26</v>
-      </c>
-      <c r="X561" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>C. FIELDS | G. BOAHEN | J. SANTA BARBARA CARCELEN | K. FELIZOR | M. TIKHONENKO ANDRIYASHCHENKO</t>
-        </is>
-      </c>
-      <c r="D562" t="n">
-        <v>5</v>
-      </c>
-      <c r="E562" t="n">
-        <v>65</v>
-      </c>
-      <c r="F562" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G562" t="n">
-        <v>3</v>
-      </c>
-      <c r="H562" t="n">
-        <v>3</v>
-      </c>
-      <c r="I562" t="n">
-        <v>1</v>
-      </c>
-      <c r="J562" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="K562" t="n">
-        <v>300</v>
-      </c>
-      <c r="L562" t="n">
-        <v>170.45</v>
-      </c>
-      <c r="M562" t="n">
-        <v>129.55</v>
-      </c>
-      <c r="N562" t="n">
-        <v>2</v>
-      </c>
-      <c r="O562" t="n">
-        <v>0</v>
-      </c>
-      <c r="P562" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q562" t="n">
-        <v>1</v>
-      </c>
-      <c r="R562" t="n">
-        <v>0</v>
-      </c>
-      <c r="S562" t="n">
-        <v>4</v>
-      </c>
-      <c r="T562" t="n">
-        <v>0</v>
-      </c>
-      <c r="U562" t="n">
-        <v>0</v>
-      </c>
-      <c r="V562" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W562" t="n">
-        <v>26</v>
-      </c>
-      <c r="X562" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>C. FIELDS | J. SANTA BARBARA CARCELEN | K. FELIZOR | L. FAIAL | M. TIKHONENKO ANDRIYASHCHENKO</t>
-        </is>
-      </c>
-      <c r="D563" t="n">
-        <v>5</v>
-      </c>
-      <c r="E563" t="n">
-        <v>23</v>
-      </c>
-      <c r="F563" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G563" t="n">
-        <v>1</v>
-      </c>
-      <c r="H563" t="n">
-        <v>2</v>
-      </c>
-      <c r="I563" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J563" t="n">
-        <v>1</v>
-      </c>
-      <c r="K563" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="L563" t="n">
-        <v>200</v>
-      </c>
-      <c r="M563" t="n">
-        <v>-86.36</v>
-      </c>
-      <c r="N563" t="n">
-        <v>0</v>
-      </c>
-      <c r="O563" t="n">
-        <v>2</v>
-      </c>
-      <c r="P563" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q563" t="n">
-        <v>0</v>
-      </c>
-      <c r="R563" t="n">
-        <v>1</v>
-      </c>
-      <c r="S563" t="n">
-        <v>0</v>
-      </c>
-      <c r="T563" t="n">
-        <v>0</v>
-      </c>
-      <c r="U563" t="n">
-        <v>0</v>
-      </c>
-      <c r="V563" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W563" t="n">
-        <v>26</v>
-      </c>
-      <c r="X563" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>A. INFANTE GUTIERREZ | B. AREVALO SAENZ | I. MONTERO MECA | P. SANTOS SPENCER | W. NIANG</t>
-        </is>
-      </c>
-      <c r="D564" t="n">
-        <v>5</v>
-      </c>
-      <c r="E564" t="n">
-        <v>43</v>
-      </c>
-      <c r="F564" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G564" t="n">
-        <v>0</v>
-      </c>
-      <c r="H564" t="n">
-        <v>2</v>
-      </c>
-      <c r="I564" t="n">
-        <v>1</v>
-      </c>
-      <c r="J564" t="n">
-        <v>2</v>
-      </c>
-      <c r="K564" t="n">
-        <v>0</v>
-      </c>
-      <c r="L564" t="n">
-        <v>100</v>
-      </c>
-      <c r="M564" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N564" t="n">
-        <v>1</v>
-      </c>
-      <c r="O564" t="n">
-        <v>0</v>
-      </c>
-      <c r="P564" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q564" t="n">
-        <v>0</v>
-      </c>
-      <c r="R564" t="n">
-        <v>2</v>
-      </c>
-      <c r="S564" t="n">
-        <v>0</v>
-      </c>
-      <c r="T564" t="n">
-        <v>1</v>
-      </c>
-      <c r="U564" t="n">
-        <v>1</v>
-      </c>
-      <c r="V564" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W564" t="n">
-        <v>26</v>
-      </c>
-      <c r="X564" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>A. INFANTE GUTIERREZ | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
-        </is>
-      </c>
-      <c r="D565" t="n">
-        <v>5</v>
-      </c>
-      <c r="E565" t="n">
-        <v>112</v>
-      </c>
-      <c r="F565" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G565" t="n">
-        <v>9</v>
-      </c>
-      <c r="H565" t="n">
-        <v>7</v>
-      </c>
-      <c r="I565" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="J565" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K565" t="n">
-        <v>220.59</v>
-      </c>
-      <c r="L565" t="n">
-        <v>243.06</v>
-      </c>
-      <c r="M565" t="n">
-        <v>-22.47</v>
-      </c>
-      <c r="N565" t="n">
-        <v>3</v>
-      </c>
-      <c r="O565" t="n">
-        <v>7</v>
-      </c>
-      <c r="P565" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q565" t="n">
-        <v>2</v>
-      </c>
-      <c r="R565" t="n">
-        <v>4</v>
-      </c>
-      <c r="S565" t="n">
-        <v>2</v>
-      </c>
-      <c r="T565" t="n">
-        <v>0</v>
-      </c>
-      <c r="U565" t="n">
-        <v>2</v>
-      </c>
-      <c r="V565" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W565" t="n">
-        <v>26</v>
-      </c>
-      <c r="X565" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>A. INFANTE GUTIERREZ | B. AREVALO SAENZ | P. SANTOS SPENCER | S. SERRATO BALLETBO | W. NIANG</t>
-        </is>
-      </c>
-      <c r="D566" t="n">
-        <v>5</v>
-      </c>
-      <c r="E566" t="n">
-        <v>18</v>
-      </c>
-      <c r="F566" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G566" t="n">
-        <v>1</v>
-      </c>
-      <c r="H566" t="n">
-        <v>0</v>
-      </c>
-      <c r="I566" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J566" t="n">
-        <v>0</v>
-      </c>
-      <c r="K566" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="L566" t="n">
-        <v>0</v>
-      </c>
-      <c r="M566" t="n">
-        <v>0</v>
-      </c>
-      <c r="N566" t="n">
-        <v>0</v>
-      </c>
-      <c r="O566" t="n">
-        <v>2</v>
-      </c>
-      <c r="P566" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q566" t="n">
-        <v>0</v>
-      </c>
-      <c r="R566" t="n">
-        <v>0</v>
-      </c>
-      <c r="S566" t="n">
-        <v>0</v>
-      </c>
-      <c r="T566" t="n">
-        <v>0</v>
-      </c>
-      <c r="U566" t="n">
-        <v>0</v>
-      </c>
-      <c r="V566" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="W566" t="n">
-        <v>26</v>
-      </c>
-      <c r="X566" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
+++ b/data/2FEB_25_26/clutch_lineups_25_26_2FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X484"/>
+  <dimension ref="A1:X566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41122,6 +41122,6894 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS | D. ORRIT SERRANO | J. BERGENS | N. OKEKE | R. HAYES</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>5</v>
+      </c>
+      <c r="E485" t="n">
+        <v>79</v>
+      </c>
+      <c r="F485" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G485" t="n">
+        <v>0</v>
+      </c>
+      <c r="H485" t="n">
+        <v>3</v>
+      </c>
+      <c r="I485" t="n">
+        <v>1</v>
+      </c>
+      <c r="J485" t="n">
+        <v>2</v>
+      </c>
+      <c r="K485" t="n">
+        <v>0</v>
+      </c>
+      <c r="L485" t="n">
+        <v>150</v>
+      </c>
+      <c r="M485" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N485" t="n">
+        <v>0</v>
+      </c>
+      <c r="O485" t="n">
+        <v>0</v>
+      </c>
+      <c r="P485" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>0</v>
+      </c>
+      <c r="R485" t="n">
+        <v>2</v>
+      </c>
+      <c r="S485" t="n">
+        <v>0</v>
+      </c>
+      <c r="T485" t="n">
+        <v>1</v>
+      </c>
+      <c r="U485" t="n">
+        <v>1</v>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W485" t="n">
+        <v>24</v>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS | J. BERGENS | J. CERA RODRIGUEZ | N. OKEKE | R. HAYES</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>5</v>
+      </c>
+      <c r="E486" t="n">
+        <v>129</v>
+      </c>
+      <c r="F486" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G486" t="n">
+        <v>10</v>
+      </c>
+      <c r="H486" t="n">
+        <v>6</v>
+      </c>
+      <c r="I486" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J486" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="K486" t="n">
+        <v>210.08</v>
+      </c>
+      <c r="L486" t="n">
+        <v>164.84</v>
+      </c>
+      <c r="M486" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="N486" t="n">
+        <v>4</v>
+      </c>
+      <c r="O486" t="n">
+        <v>4</v>
+      </c>
+      <c r="P486" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>1</v>
+      </c>
+      <c r="R486" t="n">
+        <v>1</v>
+      </c>
+      <c r="S486" t="n">
+        <v>6</v>
+      </c>
+      <c r="T486" t="n">
+        <v>1</v>
+      </c>
+      <c r="U486" t="n">
+        <v>1</v>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W486" t="n">
+        <v>24</v>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS | J. BERGENS | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>5</v>
+      </c>
+      <c r="E487" t="n">
+        <v>22</v>
+      </c>
+      <c r="F487" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G487" t="n">
+        <v>0</v>
+      </c>
+      <c r="H487" t="n">
+        <v>0</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0</v>
+      </c>
+      <c r="J487" t="n">
+        <v>1</v>
+      </c>
+      <c r="K487" t="n">
+        <v>0</v>
+      </c>
+      <c r="L487" t="n">
+        <v>0</v>
+      </c>
+      <c r="M487" t="n">
+        <v>0</v>
+      </c>
+      <c r="N487" t="n">
+        <v>0</v>
+      </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
+      <c r="P487" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>0</v>
+      </c>
+      <c r="R487" t="n">
+        <v>0</v>
+      </c>
+      <c r="S487" t="n">
+        <v>0</v>
+      </c>
+      <c r="T487" t="n">
+        <v>1</v>
+      </c>
+      <c r="U487" t="n">
+        <v>0</v>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W487" t="n">
+        <v>24</v>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>D. ORRIT SERRANO | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>5</v>
+      </c>
+      <c r="E488" t="n">
+        <v>10</v>
+      </c>
+      <c r="F488" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G488" t="n">
+        <v>0</v>
+      </c>
+      <c r="H488" t="n">
+        <v>0</v>
+      </c>
+      <c r="I488" t="n">
+        <v>0</v>
+      </c>
+      <c r="J488" t="n">
+        <v>1</v>
+      </c>
+      <c r="K488" t="n">
+        <v>0</v>
+      </c>
+      <c r="L488" t="n">
+        <v>0</v>
+      </c>
+      <c r="M488" t="n">
+        <v>0</v>
+      </c>
+      <c r="N488" t="n">
+        <v>0</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="P488" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>0</v>
+      </c>
+      <c r="R488" t="n">
+        <v>2</v>
+      </c>
+      <c r="S488" t="n">
+        <v>0</v>
+      </c>
+      <c r="T488" t="n">
+        <v>0</v>
+      </c>
+      <c r="U488" t="n">
+        <v>1</v>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W488" t="n">
+        <v>24</v>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>J. BERGENS | J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>5</v>
+      </c>
+      <c r="E489" t="n">
+        <v>332</v>
+      </c>
+      <c r="F489" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G489" t="n">
+        <v>8</v>
+      </c>
+      <c r="H489" t="n">
+        <v>8</v>
+      </c>
+      <c r="I489" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="J489" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K489" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="L489" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="M489" t="n">
+        <v>-30.39</v>
+      </c>
+      <c r="N489" t="n">
+        <v>10</v>
+      </c>
+      <c r="O489" t="n">
+        <v>2</v>
+      </c>
+      <c r="P489" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>2</v>
+      </c>
+      <c r="R489" t="n">
+        <v>6</v>
+      </c>
+      <c r="S489" t="n">
+        <v>6</v>
+      </c>
+      <c r="T489" t="n">
+        <v>1</v>
+      </c>
+      <c r="U489" t="n">
+        <v>3</v>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W489" t="n">
+        <v>24</v>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>J. CERA RODRIGUEZ | R. BLAK MOLLER | R. HAYES | S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>4</v>
+      </c>
+      <c r="E490" t="n">
+        <v>27</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G490" t="n">
+        <v>1</v>
+      </c>
+      <c r="H490" t="n">
+        <v>0</v>
+      </c>
+      <c r="I490" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J490" t="n">
+        <v>1</v>
+      </c>
+      <c r="K490" t="n">
+        <v>0</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" t="n">
+        <v>0</v>
+      </c>
+      <c r="N490" t="n">
+        <v>0</v>
+      </c>
+      <c r="O490" t="n">
+        <v>2</v>
+      </c>
+      <c r="P490" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>1</v>
+      </c>
+      <c r="R490" t="n">
+        <v>1</v>
+      </c>
+      <c r="S490" t="n">
+        <v>0</v>
+      </c>
+      <c r="T490" t="n">
+        <v>0</v>
+      </c>
+      <c r="U490" t="n">
+        <v>0</v>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W490" t="n">
+        <v>24</v>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK | A. INFANTE GUTIERREZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>5</v>
+      </c>
+      <c r="E491" t="n">
+        <v>31</v>
+      </c>
+      <c r="F491" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G491" t="n">
+        <v>2</v>
+      </c>
+      <c r="H491" t="n">
+        <v>0</v>
+      </c>
+      <c r="I491" t="n">
+        <v>1</v>
+      </c>
+      <c r="J491" t="n">
+        <v>0</v>
+      </c>
+      <c r="K491" t="n">
+        <v>200</v>
+      </c>
+      <c r="L491" t="n">
+        <v>0</v>
+      </c>
+      <c r="M491" t="n">
+        <v>0</v>
+      </c>
+      <c r="N491" t="n">
+        <v>1</v>
+      </c>
+      <c r="O491" t="n">
+        <v>0</v>
+      </c>
+      <c r="P491" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>0</v>
+      </c>
+      <c r="R491" t="n">
+        <v>0</v>
+      </c>
+      <c r="S491" t="n">
+        <v>0</v>
+      </c>
+      <c r="T491" t="n">
+        <v>0</v>
+      </c>
+      <c r="U491" t="n">
+        <v>0</v>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W491" t="n">
+        <v>24</v>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>5</v>
+      </c>
+      <c r="E492" t="n">
+        <v>27</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G492" t="n">
+        <v>0</v>
+      </c>
+      <c r="H492" t="n">
+        <v>2</v>
+      </c>
+      <c r="I492" t="n">
+        <v>1</v>
+      </c>
+      <c r="J492" t="n">
+        <v>1</v>
+      </c>
+      <c r="K492" t="n">
+        <v>0</v>
+      </c>
+      <c r="L492" t="n">
+        <v>200</v>
+      </c>
+      <c r="M492" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N492" t="n">
+        <v>1</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
+      <c r="P492" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>0</v>
+      </c>
+      <c r="R492" t="n">
+        <v>1</v>
+      </c>
+      <c r="S492" t="n">
+        <v>0</v>
+      </c>
+      <c r="T492" t="n">
+        <v>0</v>
+      </c>
+      <c r="U492" t="n">
+        <v>0</v>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W492" t="n">
+        <v>24</v>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>5</v>
+      </c>
+      <c r="E493" t="n">
+        <v>50</v>
+      </c>
+      <c r="F493" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G493" t="n">
+        <v>0</v>
+      </c>
+      <c r="H493" t="n">
+        <v>2</v>
+      </c>
+      <c r="I493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J493" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0</v>
+      </c>
+      <c r="L493" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M493" t="n">
+        <v>0</v>
+      </c>
+      <c r="N493" t="n">
+        <v>1</v>
+      </c>
+      <c r="O493" t="n">
+        <v>0</v>
+      </c>
+      <c r="P493" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>1</v>
+      </c>
+      <c r="R493" t="n">
+        <v>1</v>
+      </c>
+      <c r="S493" t="n">
+        <v>2</v>
+      </c>
+      <c r="T493" t="n">
+        <v>0</v>
+      </c>
+      <c r="U493" t="n">
+        <v>0</v>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W493" t="n">
+        <v>24</v>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | L. OBAJO BELTRAN | P. SALL</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>5</v>
+      </c>
+      <c r="E494" t="n">
+        <v>85</v>
+      </c>
+      <c r="F494" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G494" t="n">
+        <v>3</v>
+      </c>
+      <c r="H494" t="n">
+        <v>4</v>
+      </c>
+      <c r="I494" t="n">
+        <v>2</v>
+      </c>
+      <c r="J494" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K494" t="n">
+        <v>150</v>
+      </c>
+      <c r="L494" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="M494" t="n">
+        <v>-62.77</v>
+      </c>
+      <c r="N494" t="n">
+        <v>1</v>
+      </c>
+      <c r="O494" t="n">
+        <v>0</v>
+      </c>
+      <c r="P494" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>0</v>
+      </c>
+      <c r="R494" t="n">
+        <v>1</v>
+      </c>
+      <c r="S494" t="n">
+        <v>2</v>
+      </c>
+      <c r="T494" t="n">
+        <v>0</v>
+      </c>
+      <c r="U494" t="n">
+        <v>0</v>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W494" t="n">
+        <v>24</v>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>5</v>
+      </c>
+      <c r="E495" t="n">
+        <v>123</v>
+      </c>
+      <c r="F495" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G495" t="n">
+        <v>6</v>
+      </c>
+      <c r="H495" t="n">
+        <v>6</v>
+      </c>
+      <c r="I495" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J495" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K495" t="n">
+        <v>164.84</v>
+      </c>
+      <c r="L495" t="n">
+        <v>154.64</v>
+      </c>
+      <c r="M495" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N495" t="n">
+        <v>2</v>
+      </c>
+      <c r="O495" t="n">
+        <v>6</v>
+      </c>
+      <c r="P495" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>2</v>
+      </c>
+      <c r="R495" t="n">
+        <v>3</v>
+      </c>
+      <c r="S495" t="n">
+        <v>2</v>
+      </c>
+      <c r="T495" t="n">
+        <v>1</v>
+      </c>
+      <c r="U495" t="n">
+        <v>1</v>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W495" t="n">
+        <v>24</v>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>5</v>
+      </c>
+      <c r="E496" t="n">
+        <v>91</v>
+      </c>
+      <c r="F496" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G496" t="n">
+        <v>4</v>
+      </c>
+      <c r="H496" t="n">
+        <v>3</v>
+      </c>
+      <c r="I496" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J496" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K496" t="n">
+        <v>144.93</v>
+      </c>
+      <c r="L496" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="M496" t="n">
+        <v>-14.65</v>
+      </c>
+      <c r="N496" t="n">
+        <v>2</v>
+      </c>
+      <c r="O496" t="n">
+        <v>4</v>
+      </c>
+      <c r="P496" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>1</v>
+      </c>
+      <c r="R496" t="n">
+        <v>2</v>
+      </c>
+      <c r="S496" t="n">
+        <v>2</v>
+      </c>
+      <c r="T496" t="n">
+        <v>0</v>
+      </c>
+      <c r="U496" t="n">
+        <v>1</v>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W496" t="n">
+        <v>24</v>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>5</v>
+      </c>
+      <c r="E497" t="n">
+        <v>10</v>
+      </c>
+      <c r="F497" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G497" t="n">
+        <v>0</v>
+      </c>
+      <c r="H497" t="n">
+        <v>0</v>
+      </c>
+      <c r="I497" t="n">
+        <v>1</v>
+      </c>
+      <c r="J497" t="n">
+        <v>0</v>
+      </c>
+      <c r="K497" t="n">
+        <v>0</v>
+      </c>
+      <c r="L497" t="n">
+        <v>0</v>
+      </c>
+      <c r="M497" t="n">
+        <v>0</v>
+      </c>
+      <c r="N497" t="n">
+        <v>2</v>
+      </c>
+      <c r="O497" t="n">
+        <v>0</v>
+      </c>
+      <c r="P497" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>1</v>
+      </c>
+      <c r="R497" t="n">
+        <v>0</v>
+      </c>
+      <c r="S497" t="n">
+        <v>0</v>
+      </c>
+      <c r="T497" t="n">
+        <v>0</v>
+      </c>
+      <c r="U497" t="n">
+        <v>0</v>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W497" t="n">
+        <v>24</v>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>5</v>
+      </c>
+      <c r="E498" t="n">
+        <v>182</v>
+      </c>
+      <c r="F498" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G498" t="n">
+        <v>2</v>
+      </c>
+      <c r="H498" t="n">
+        <v>2</v>
+      </c>
+      <c r="I498" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J498" t="n">
+        <v>4</v>
+      </c>
+      <c r="K498" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="L498" t="n">
+        <v>50</v>
+      </c>
+      <c r="M498" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N498" t="n">
+        <v>2</v>
+      </c>
+      <c r="O498" t="n">
+        <v>2</v>
+      </c>
+      <c r="P498" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>1</v>
+      </c>
+      <c r="R498" t="n">
+        <v>6</v>
+      </c>
+      <c r="S498" t="n">
+        <v>0</v>
+      </c>
+      <c r="T498" t="n">
+        <v>0</v>
+      </c>
+      <c r="U498" t="n">
+        <v>2</v>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W498" t="n">
+        <v>24</v>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>A. CALVO TORRES | C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | J. LACUNZA ABECIA</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>5</v>
+      </c>
+      <c r="E499" t="n">
+        <v>9</v>
+      </c>
+      <c r="F499" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G499" t="n">
+        <v>0</v>
+      </c>
+      <c r="H499" t="n">
+        <v>2</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0</v>
+      </c>
+      <c r="J499" t="n">
+        <v>1</v>
+      </c>
+      <c r="K499" t="n">
+        <v>0</v>
+      </c>
+      <c r="L499" t="n">
+        <v>200</v>
+      </c>
+      <c r="M499" t="n">
+        <v>0</v>
+      </c>
+      <c r="N499" t="n">
+        <v>0</v>
+      </c>
+      <c r="O499" t="n">
+        <v>0</v>
+      </c>
+      <c r="P499" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>0</v>
+      </c>
+      <c r="R499" t="n">
+        <v>1</v>
+      </c>
+      <c r="S499" t="n">
+        <v>0</v>
+      </c>
+      <c r="T499" t="n">
+        <v>0</v>
+      </c>
+      <c r="U499" t="n">
+        <v>0</v>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W499" t="n">
+        <v>24</v>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>A. CALVO TORRES | C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | P. YARNOZ LUMBRERAS</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>5</v>
+      </c>
+      <c r="E500" t="n">
+        <v>33</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G500" t="n">
+        <v>3</v>
+      </c>
+      <c r="H500" t="n">
+        <v>0</v>
+      </c>
+      <c r="I500" t="n">
+        <v>2</v>
+      </c>
+      <c r="J500" t="n">
+        <v>0</v>
+      </c>
+      <c r="K500" t="n">
+        <v>150</v>
+      </c>
+      <c r="L500" t="n">
+        <v>0</v>
+      </c>
+      <c r="M500" t="n">
+        <v>0</v>
+      </c>
+      <c r="N500" t="n">
+        <v>2</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
+      <c r="P500" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>0</v>
+      </c>
+      <c r="R500" t="n">
+        <v>0</v>
+      </c>
+      <c r="S500" t="n">
+        <v>0</v>
+      </c>
+      <c r="T500" t="n">
+        <v>0</v>
+      </c>
+      <c r="U500" t="n">
+        <v>0</v>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W500" t="n">
+        <v>24</v>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>C. NKALOULOU MILANDOU | F. SANTANA ROSALES | J. KNOTEK | J. LACUNZA ABECIA | P. YARNOZ LUMBRERAS</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>5</v>
+      </c>
+      <c r="E501" t="n">
+        <v>248</v>
+      </c>
+      <c r="F501" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="G501" t="n">
+        <v>13</v>
+      </c>
+      <c r="H501" t="n">
+        <v>14</v>
+      </c>
+      <c r="I501" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="J501" t="n">
+        <v>8</v>
+      </c>
+      <c r="K501" t="n">
+        <v>195.78</v>
+      </c>
+      <c r="L501" t="n">
+        <v>175</v>
+      </c>
+      <c r="M501" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="N501" t="n">
+        <v>7</v>
+      </c>
+      <c r="O501" t="n">
+        <v>6</v>
+      </c>
+      <c r="P501" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>3</v>
+      </c>
+      <c r="R501" t="n">
+        <v>9</v>
+      </c>
+      <c r="S501" t="n">
+        <v>0</v>
+      </c>
+      <c r="T501" t="n">
+        <v>0</v>
+      </c>
+      <c r="U501" t="n">
+        <v>1</v>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W501" t="n">
+        <v>24</v>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. BARROS GARCIA</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>5</v>
+      </c>
+      <c r="E502" t="n">
+        <v>9</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G502" t="n">
+        <v>2</v>
+      </c>
+      <c r="H502" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" t="n">
+        <v>1</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0</v>
+      </c>
+      <c r="K502" t="n">
+        <v>200</v>
+      </c>
+      <c r="L502" t="n">
+        <v>0</v>
+      </c>
+      <c r="M502" t="n">
+        <v>0</v>
+      </c>
+      <c r="N502" t="n">
+        <v>1</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>0</v>
+      </c>
+      <c r="R502" t="n">
+        <v>0</v>
+      </c>
+      <c r="S502" t="n">
+        <v>0</v>
+      </c>
+      <c r="T502" t="n">
+        <v>0</v>
+      </c>
+      <c r="U502" t="n">
+        <v>0</v>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W502" t="n">
+        <v>24</v>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>5</v>
+      </c>
+      <c r="E503" t="n">
+        <v>124</v>
+      </c>
+      <c r="F503" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G503" t="n">
+        <v>7</v>
+      </c>
+      <c r="H503" t="n">
+        <v>5</v>
+      </c>
+      <c r="I503" t="n">
+        <v>4</v>
+      </c>
+      <c r="J503" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K503" t="n">
+        <v>175</v>
+      </c>
+      <c r="L503" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M503" t="n">
+        <v>-52.27</v>
+      </c>
+      <c r="N503" t="n">
+        <v>5</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
+      <c r="P503" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>1</v>
+      </c>
+      <c r="R503" t="n">
+        <v>2</v>
+      </c>
+      <c r="S503" t="n">
+        <v>5</v>
+      </c>
+      <c r="T503" t="n">
+        <v>0</v>
+      </c>
+      <c r="U503" t="n">
+        <v>2</v>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W503" t="n">
+        <v>24</v>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | G. ARCOS GONZALEZ | J. MENENDEZ GARCIA | M. OKAFOR AUGUSTIN | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>5</v>
+      </c>
+      <c r="E504" t="n">
+        <v>24</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G504" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" t="n">
+        <v>3</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K504" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M504" t="n">
+        <v>0</v>
+      </c>
+      <c r="N504" t="n">
+        <v>0</v>
+      </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>0</v>
+      </c>
+      <c r="R504" t="n">
+        <v>1</v>
+      </c>
+      <c r="S504" t="n">
+        <v>1</v>
+      </c>
+      <c r="T504" t="n">
+        <v>0</v>
+      </c>
+      <c r="U504" t="n">
+        <v>0</v>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W504" t="n">
+        <v>24</v>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. BARROS GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>5</v>
+      </c>
+      <c r="E505" t="n">
+        <v>24</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G505" t="n">
+        <v>0</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>1</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" t="n">
+        <v>0</v>
+      </c>
+      <c r="M505" t="n">
+        <v>0</v>
+      </c>
+      <c r="N505" t="n">
+        <v>0</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>0</v>
+      </c>
+      <c r="R505" t="n">
+        <v>1</v>
+      </c>
+      <c r="S505" t="n">
+        <v>0</v>
+      </c>
+      <c r="T505" t="n">
+        <v>0</v>
+      </c>
+      <c r="U505" t="n">
+        <v>0</v>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W505" t="n">
+        <v>24</v>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ | I. DUKE TOUSSAINT | S. BARROS GARCIA | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>5</v>
+      </c>
+      <c r="E506" t="n">
+        <v>11</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G506" t="n">
+        <v>2</v>
+      </c>
+      <c r="H506" t="n">
+        <v>2</v>
+      </c>
+      <c r="I506" t="n">
+        <v>1</v>
+      </c>
+      <c r="J506" t="n">
+        <v>1</v>
+      </c>
+      <c r="K506" t="n">
+        <v>200</v>
+      </c>
+      <c r="L506" t="n">
+        <v>200</v>
+      </c>
+      <c r="M506" t="n">
+        <v>0</v>
+      </c>
+      <c r="N506" t="n">
+        <v>1</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
+      <c r="P506" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>0</v>
+      </c>
+      <c r="R506" t="n">
+        <v>1</v>
+      </c>
+      <c r="S506" t="n">
+        <v>0</v>
+      </c>
+      <c r="T506" t="n">
+        <v>0</v>
+      </c>
+      <c r="U506" t="n">
+        <v>0</v>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W506" t="n">
+        <v>24</v>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>G. ARCOS GONZALEZ | I. DUKE TOUSSAINT | J. MENENDEZ GARCIA | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>5</v>
+      </c>
+      <c r="E507" t="n">
+        <v>9</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0</v>
+      </c>
+      <c r="H507" t="n">
+        <v>3</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="n">
+        <v>1</v>
+      </c>
+      <c r="K507" t="n">
+        <v>0</v>
+      </c>
+      <c r="L507" t="n">
+        <v>300</v>
+      </c>
+      <c r="M507" t="n">
+        <v>0</v>
+      </c>
+      <c r="N507" t="n">
+        <v>0</v>
+      </c>
+      <c r="O507" t="n">
+        <v>0</v>
+      </c>
+      <c r="P507" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>0</v>
+      </c>
+      <c r="R507" t="n">
+        <v>1</v>
+      </c>
+      <c r="S507" t="n">
+        <v>0</v>
+      </c>
+      <c r="T507" t="n">
+        <v>0</v>
+      </c>
+      <c r="U507" t="n">
+        <v>0</v>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W507" t="n">
+        <v>24</v>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>G. ARCOS GONZALEZ | J. MENENDEZ GARCIA | M. OKAFOR AUGUSTIN | S. FRANCO GARCIA | T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>5</v>
+      </c>
+      <c r="E508" t="n">
+        <v>89</v>
+      </c>
+      <c r="F508" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G508" t="n">
+        <v>5</v>
+      </c>
+      <c r="H508" t="n">
+        <v>3</v>
+      </c>
+      <c r="I508" t="n">
+        <v>3</v>
+      </c>
+      <c r="J508" t="n">
+        <v>2</v>
+      </c>
+      <c r="K508" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L508" t="n">
+        <v>150</v>
+      </c>
+      <c r="M508" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="N508" t="n">
+        <v>3</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>0</v>
+      </c>
+      <c r="R508" t="n">
+        <v>3</v>
+      </c>
+      <c r="S508" t="n">
+        <v>0</v>
+      </c>
+      <c r="T508" t="n">
+        <v>0</v>
+      </c>
+      <c r="U508" t="n">
+        <v>1</v>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W508" t="n">
+        <v>24</v>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. KOCIC | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>5</v>
+      </c>
+      <c r="E509" t="n">
+        <v>84</v>
+      </c>
+      <c r="F509" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G509" t="n">
+        <v>2</v>
+      </c>
+      <c r="H509" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" t="n">
+        <v>1</v>
+      </c>
+      <c r="J509" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K509" t="n">
+        <v>200</v>
+      </c>
+      <c r="L509" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M509" t="n">
+        <v>130.56</v>
+      </c>
+      <c r="N509" t="n">
+        <v>2</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0</v>
+      </c>
+      <c r="P509" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>1</v>
+      </c>
+      <c r="R509" t="n">
+        <v>2</v>
+      </c>
+      <c r="S509" t="n">
+        <v>2</v>
+      </c>
+      <c r="T509" t="n">
+        <v>0</v>
+      </c>
+      <c r="U509" t="n">
+        <v>0</v>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W509" t="n">
+        <v>24</v>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>5</v>
+      </c>
+      <c r="E510" t="n">
+        <v>3</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0</v>
+      </c>
+      <c r="H510" t="n">
+        <v>1</v>
+      </c>
+      <c r="I510" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J510" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M510" t="n">
+        <v>0</v>
+      </c>
+      <c r="N510" t="n">
+        <v>0</v>
+      </c>
+      <c r="O510" t="n">
+        <v>0</v>
+      </c>
+      <c r="P510" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>1</v>
+      </c>
+      <c r="R510" t="n">
+        <v>1</v>
+      </c>
+      <c r="S510" t="n">
+        <v>2</v>
+      </c>
+      <c r="T510" t="n">
+        <v>0</v>
+      </c>
+      <c r="U510" t="n">
+        <v>1</v>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W510" t="n">
+        <v>24</v>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | S. KOCIC | V. MORENO MARTIN | V. STEVANIC</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>5</v>
+      </c>
+      <c r="E511" t="n">
+        <v>40</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G511" t="n">
+        <v>4</v>
+      </c>
+      <c r="H511" t="n">
+        <v>0</v>
+      </c>
+      <c r="I511" t="n">
+        <v>2</v>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="n">
+        <v>200</v>
+      </c>
+      <c r="L511" t="n">
+        <v>0</v>
+      </c>
+      <c r="M511" t="n">
+        <v>200</v>
+      </c>
+      <c r="N511" t="n">
+        <v>2</v>
+      </c>
+      <c r="O511" t="n">
+        <v>0</v>
+      </c>
+      <c r="P511" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>0</v>
+      </c>
+      <c r="R511" t="n">
+        <v>1</v>
+      </c>
+      <c r="S511" t="n">
+        <v>0</v>
+      </c>
+      <c r="T511" t="n">
+        <v>0</v>
+      </c>
+      <c r="U511" t="n">
+        <v>0</v>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W511" t="n">
+        <v>24</v>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>C. JACOBS | E. A NONGO BERTHOLD | H. ARBOSA ROLDAN | J. PARDINA MOLINA | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>5</v>
+      </c>
+      <c r="E512" t="n">
+        <v>3</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G512" t="n">
+        <v>1</v>
+      </c>
+      <c r="H512" t="n">
+        <v>0</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J512" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K512" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L512" t="n">
+        <v>0</v>
+      </c>
+      <c r="M512" t="n">
+        <v>0</v>
+      </c>
+      <c r="N512" t="n">
+        <v>1</v>
+      </c>
+      <c r="O512" t="n">
+        <v>2</v>
+      </c>
+      <c r="P512" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>1</v>
+      </c>
+      <c r="R512" t="n">
+        <v>0</v>
+      </c>
+      <c r="S512" t="n">
+        <v>0</v>
+      </c>
+      <c r="T512" t="n">
+        <v>0</v>
+      </c>
+      <c r="U512" t="n">
+        <v>1</v>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W512" t="n">
+        <v>24</v>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>C. JACOBS | E. A NONGO BERTHOLD | H. ARBOSA ROLDAN | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>5</v>
+      </c>
+      <c r="E513" t="n">
+        <v>19</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G513" t="n">
+        <v>0</v>
+      </c>
+      <c r="H513" t="n">
+        <v>2</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0</v>
+      </c>
+      <c r="J513" t="n">
+        <v>1</v>
+      </c>
+      <c r="K513" t="n">
+        <v>0</v>
+      </c>
+      <c r="L513" t="n">
+        <v>200</v>
+      </c>
+      <c r="M513" t="n">
+        <v>0</v>
+      </c>
+      <c r="N513" t="n">
+        <v>0</v>
+      </c>
+      <c r="O513" t="n">
+        <v>0</v>
+      </c>
+      <c r="P513" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>0</v>
+      </c>
+      <c r="R513" t="n">
+        <v>1</v>
+      </c>
+      <c r="S513" t="n">
+        <v>0</v>
+      </c>
+      <c r="T513" t="n">
+        <v>0</v>
+      </c>
+      <c r="U513" t="n">
+        <v>0</v>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W513" t="n">
+        <v>24</v>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>C. JACOBS | H. ARBOSA ROLDAN | J. PARDINA MOLINA | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>5</v>
+      </c>
+      <c r="E514" t="n">
+        <v>34</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" t="n">
+        <v>1</v>
+      </c>
+      <c r="J514" t="n">
+        <v>0</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" t="n">
+        <v>0</v>
+      </c>
+      <c r="M514" t="n">
+        <v>0</v>
+      </c>
+      <c r="N514" t="n">
+        <v>1</v>
+      </c>
+      <c r="O514" t="n">
+        <v>0</v>
+      </c>
+      <c r="P514" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>0</v>
+      </c>
+      <c r="R514" t="n">
+        <v>1</v>
+      </c>
+      <c r="S514" t="n">
+        <v>0</v>
+      </c>
+      <c r="T514" t="n">
+        <v>0</v>
+      </c>
+      <c r="U514" t="n">
+        <v>1</v>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W514" t="n">
+        <v>24</v>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>C. JACOBS | H. ARBOSA ROLDAN | K. TORRES CUEVAS | P. DIENE | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>5</v>
+      </c>
+      <c r="E515" t="n">
+        <v>50</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G515" t="n">
+        <v>2</v>
+      </c>
+      <c r="H515" t="n">
+        <v>2</v>
+      </c>
+      <c r="I515" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J515" t="n">
+        <v>1</v>
+      </c>
+      <c r="K515" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L515" t="n">
+        <v>200</v>
+      </c>
+      <c r="M515" t="n">
+        <v>-93.62</v>
+      </c>
+      <c r="N515" t="n">
+        <v>1</v>
+      </c>
+      <c r="O515" t="n">
+        <v>2</v>
+      </c>
+      <c r="P515" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>0</v>
+      </c>
+      <c r="R515" t="n">
+        <v>1</v>
+      </c>
+      <c r="S515" t="n">
+        <v>0</v>
+      </c>
+      <c r="T515" t="n">
+        <v>0</v>
+      </c>
+      <c r="U515" t="n">
+        <v>0</v>
+      </c>
+      <c r="V515" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W515" t="n">
+        <v>24</v>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>C. JACOBS | H. ARBOSA ROLDAN | M. DE PABLO DEL CASTILLO | P. DIENE | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>5</v>
+      </c>
+      <c r="E516" t="n">
+        <v>21</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G516" t="n">
+        <v>0</v>
+      </c>
+      <c r="H516" t="n">
+        <v>2</v>
+      </c>
+      <c r="I516" t="n">
+        <v>1</v>
+      </c>
+      <c r="J516" t="n">
+        <v>1</v>
+      </c>
+      <c r="K516" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" t="n">
+        <v>200</v>
+      </c>
+      <c r="M516" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N516" t="n">
+        <v>1</v>
+      </c>
+      <c r="O516" t="n">
+        <v>0</v>
+      </c>
+      <c r="P516" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>0</v>
+      </c>
+      <c r="R516" t="n">
+        <v>1</v>
+      </c>
+      <c r="S516" t="n">
+        <v>0</v>
+      </c>
+      <c r="T516" t="n">
+        <v>0</v>
+      </c>
+      <c r="U516" t="n">
+        <v>0</v>
+      </c>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W516" t="n">
+        <v>24</v>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | G. VERGARA HARBOE | J. MARTINEZ MEGIAS | L. FAIAL</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>5</v>
+      </c>
+      <c r="E517" t="n">
+        <v>9</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G517" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I517" t="n">
+        <v>1</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0</v>
+      </c>
+      <c r="K517" t="n">
+        <v>0</v>
+      </c>
+      <c r="L517" t="n">
+        <v>0</v>
+      </c>
+      <c r="M517" t="n">
+        <v>0</v>
+      </c>
+      <c r="N517" t="n">
+        <v>0</v>
+      </c>
+      <c r="O517" t="n">
+        <v>0</v>
+      </c>
+      <c r="P517" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>0</v>
+      </c>
+      <c r="R517" t="n">
+        <v>0</v>
+      </c>
+      <c r="S517" t="n">
+        <v>0</v>
+      </c>
+      <c r="T517" t="n">
+        <v>0</v>
+      </c>
+      <c r="U517" t="n">
+        <v>0</v>
+      </c>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W517" t="n">
+        <v>24</v>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | L. FAIAL</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>5</v>
+      </c>
+      <c r="E518" t="n">
+        <v>120</v>
+      </c>
+      <c r="F518" t="n">
+        <v>2</v>
+      </c>
+      <c r="G518" t="n">
+        <v>4</v>
+      </c>
+      <c r="H518" t="n">
+        <v>6</v>
+      </c>
+      <c r="I518" t="n">
+        <v>3</v>
+      </c>
+      <c r="J518" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K518" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L518" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M518" t="n">
+        <v>-93.94</v>
+      </c>
+      <c r="N518" t="n">
+        <v>3</v>
+      </c>
+      <c r="O518" t="n">
+        <v>0</v>
+      </c>
+      <c r="P518" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>0</v>
+      </c>
+      <c r="R518" t="n">
+        <v>2</v>
+      </c>
+      <c r="S518" t="n">
+        <v>6</v>
+      </c>
+      <c r="T518" t="n">
+        <v>0</v>
+      </c>
+      <c r="U518" t="n">
+        <v>2</v>
+      </c>
+      <c r="V518" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W518" t="n">
+        <v>24</v>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. VERGARA HARBOE | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | L. FAIAL</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>5</v>
+      </c>
+      <c r="E519" t="n">
+        <v>91</v>
+      </c>
+      <c r="F519" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G519" t="n">
+        <v>2</v>
+      </c>
+      <c r="H519" t="n">
+        <v>3</v>
+      </c>
+      <c r="I519" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J519" t="n">
+        <v>3</v>
+      </c>
+      <c r="K519" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L519" t="n">
+        <v>100</v>
+      </c>
+      <c r="M519" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="N519" t="n">
+        <v>4</v>
+      </c>
+      <c r="O519" t="n">
+        <v>2</v>
+      </c>
+      <c r="P519" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q519" t="n">
+        <v>3</v>
+      </c>
+      <c r="R519" t="n">
+        <v>2</v>
+      </c>
+      <c r="S519" t="n">
+        <v>0</v>
+      </c>
+      <c r="T519" t="n">
+        <v>1</v>
+      </c>
+      <c r="U519" t="n">
+        <v>0</v>
+      </c>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W519" t="n">
+        <v>24</v>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>I. HANEY | I. ORDOÑEZ OCHOA | J. GARCIA-ABRIL GUERRERO | M. OCHI | P. ISERN MAZA</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>5</v>
+      </c>
+      <c r="E520" t="n">
+        <v>65</v>
+      </c>
+      <c r="F520" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G520" t="n">
+        <v>3</v>
+      </c>
+      <c r="H520" t="n">
+        <v>0</v>
+      </c>
+      <c r="I520" t="n">
+        <v>2</v>
+      </c>
+      <c r="J520" t="n">
+        <v>2</v>
+      </c>
+      <c r="K520" t="n">
+        <v>150</v>
+      </c>
+      <c r="L520" t="n">
+        <v>0</v>
+      </c>
+      <c r="M520" t="n">
+        <v>150</v>
+      </c>
+      <c r="N520" t="n">
+        <v>1</v>
+      </c>
+      <c r="O520" t="n">
+        <v>0</v>
+      </c>
+      <c r="P520" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>0</v>
+      </c>
+      <c r="R520" t="n">
+        <v>3</v>
+      </c>
+      <c r="S520" t="n">
+        <v>0</v>
+      </c>
+      <c r="T520" t="n">
+        <v>0</v>
+      </c>
+      <c r="U520" t="n">
+        <v>1</v>
+      </c>
+      <c r="V520" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W520" t="n">
+        <v>24</v>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>I. HANEY | I. ORDOÑEZ OCHOA | J. GARCIA-ABRIL GUERRERO | M. OCHI | P. MARIN FONTAN</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>5</v>
+      </c>
+      <c r="E521" t="n">
+        <v>146</v>
+      </c>
+      <c r="F521" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G521" t="n">
+        <v>6</v>
+      </c>
+      <c r="H521" t="n">
+        <v>6</v>
+      </c>
+      <c r="I521" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J521" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K521" t="n">
+        <v>164.84</v>
+      </c>
+      <c r="L521" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M521" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="N521" t="n">
+        <v>3</v>
+      </c>
+      <c r="O521" t="n">
+        <v>6</v>
+      </c>
+      <c r="P521" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q521" t="n">
+        <v>2</v>
+      </c>
+      <c r="R521" t="n">
+        <v>4</v>
+      </c>
+      <c r="S521" t="n">
+        <v>2</v>
+      </c>
+      <c r="T521" t="n">
+        <v>0</v>
+      </c>
+      <c r="U521" t="n">
+        <v>2</v>
+      </c>
+      <c r="V521" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W521" t="n">
+        <v>24</v>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>I. HANEY | I. ORDOÑEZ OCHOA | M. OCHI | P. ISERN MAZA | P. MARIN FONTAN</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>5</v>
+      </c>
+      <c r="E522" t="n">
+        <v>9</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" t="n">
+        <v>1</v>
+      </c>
+      <c r="K522" t="n">
+        <v>0</v>
+      </c>
+      <c r="L522" t="n">
+        <v>0</v>
+      </c>
+      <c r="M522" t="n">
+        <v>0</v>
+      </c>
+      <c r="N522" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" t="n">
+        <v>0</v>
+      </c>
+      <c r="P522" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>0</v>
+      </c>
+      <c r="R522" t="n">
+        <v>0</v>
+      </c>
+      <c r="S522" t="n">
+        <v>0</v>
+      </c>
+      <c r="T522" t="n">
+        <v>1</v>
+      </c>
+      <c r="U522" t="n">
+        <v>0</v>
+      </c>
+      <c r="V522" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W522" t="n">
+        <v>24</v>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>I. AIZPITARTE ARANZA | J. CEBOLLA HERRERA | M. OLAIZOLA GARIN | N. WILLIAMS | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>5</v>
+      </c>
+      <c r="E523" t="n">
+        <v>33</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" t="n">
+        <v>5</v>
+      </c>
+      <c r="I523" t="n">
+        <v>1</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" t="n">
+        <v>568.1799999999999</v>
+      </c>
+      <c r="M523" t="n">
+        <v>-568.1799999999999</v>
+      </c>
+      <c r="N523" t="n">
+        <v>1</v>
+      </c>
+      <c r="O523" t="n">
+        <v>0</v>
+      </c>
+      <c r="P523" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>0</v>
+      </c>
+      <c r="R523" t="n">
+        <v>1</v>
+      </c>
+      <c r="S523" t="n">
+        <v>2</v>
+      </c>
+      <c r="T523" t="n">
+        <v>0</v>
+      </c>
+      <c r="U523" t="n">
+        <v>1</v>
+      </c>
+      <c r="V523" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W523" t="n">
+        <v>24</v>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>I. AIZPITARTE ARANZA | M. NIANG NDONGO | N. WILLIAMS | O. INDA HERNANDEZ | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>5</v>
+      </c>
+      <c r="E524" t="n">
+        <v>228</v>
+      </c>
+      <c r="F524" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G524" t="n">
+        <v>11</v>
+      </c>
+      <c r="H524" t="n">
+        <v>5</v>
+      </c>
+      <c r="I524" t="n">
+        <v>4</v>
+      </c>
+      <c r="J524" t="n">
+        <v>4</v>
+      </c>
+      <c r="K524" t="n">
+        <v>275</v>
+      </c>
+      <c r="L524" t="n">
+        <v>125</v>
+      </c>
+      <c r="M524" t="n">
+        <v>150</v>
+      </c>
+      <c r="N524" t="n">
+        <v>6</v>
+      </c>
+      <c r="O524" t="n">
+        <v>0</v>
+      </c>
+      <c r="P524" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>2</v>
+      </c>
+      <c r="R524" t="n">
+        <v>5</v>
+      </c>
+      <c r="S524" t="n">
+        <v>0</v>
+      </c>
+      <c r="T524" t="n">
+        <v>0</v>
+      </c>
+      <c r="U524" t="n">
+        <v>1</v>
+      </c>
+      <c r="V524" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W524" t="n">
+        <v>24</v>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>I. MIRANDA GARCIA | M. NIANG NDONGO | N. WILLIAMS | O. INDA HERNANDEZ | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>5</v>
+      </c>
+      <c r="E525" t="n">
+        <v>9</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G525" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" t="n">
+        <v>0</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" t="n">
+        <v>1</v>
+      </c>
+      <c r="K525" t="n">
+        <v>0</v>
+      </c>
+      <c r="L525" t="n">
+        <v>0</v>
+      </c>
+      <c r="M525" t="n">
+        <v>0</v>
+      </c>
+      <c r="N525" t="n">
+        <v>0</v>
+      </c>
+      <c r="O525" t="n">
+        <v>0</v>
+      </c>
+      <c r="P525" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>0</v>
+      </c>
+      <c r="R525" t="n">
+        <v>1</v>
+      </c>
+      <c r="S525" t="n">
+        <v>0</v>
+      </c>
+      <c r="T525" t="n">
+        <v>0</v>
+      </c>
+      <c r="U525" t="n">
+        <v>0</v>
+      </c>
+      <c r="V525" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W525" t="n">
+        <v>24</v>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>J. CEBOLLA HERRERA | M. OLAIZOLA GARIN | N. WILLIAMS | O. ARDANZA BERNAOLA | T. SAGNA</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>5</v>
+      </c>
+      <c r="E526" t="n">
+        <v>7</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G526" t="n">
+        <v>0</v>
+      </c>
+      <c r="H526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" t="n">
+        <v>1</v>
+      </c>
+      <c r="J526" t="n">
+        <v>0</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" t="n">
+        <v>0</v>
+      </c>
+      <c r="M526" t="n">
+        <v>0</v>
+      </c>
+      <c r="N526" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" t="n">
+        <v>0</v>
+      </c>
+      <c r="P526" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q526" t="n">
+        <v>0</v>
+      </c>
+      <c r="R526" t="n">
+        <v>1</v>
+      </c>
+      <c r="S526" t="n">
+        <v>0</v>
+      </c>
+      <c r="T526" t="n">
+        <v>0</v>
+      </c>
+      <c r="U526" t="n">
+        <v>1</v>
+      </c>
+      <c r="V526" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W526" t="n">
+        <v>24</v>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>5</v>
+      </c>
+      <c r="E527" t="n">
+        <v>7</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G527" t="n">
+        <v>0</v>
+      </c>
+      <c r="H527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="n">
+        <v>1</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0</v>
+      </c>
+      <c r="L527" t="n">
+        <v>0</v>
+      </c>
+      <c r="M527" t="n">
+        <v>0</v>
+      </c>
+      <c r="N527" t="n">
+        <v>1</v>
+      </c>
+      <c r="O527" t="n">
+        <v>0</v>
+      </c>
+      <c r="P527" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q527" t="n">
+        <v>1</v>
+      </c>
+      <c r="R527" t="n">
+        <v>0</v>
+      </c>
+      <c r="S527" t="n">
+        <v>0</v>
+      </c>
+      <c r="T527" t="n">
+        <v>1</v>
+      </c>
+      <c r="U527" t="n">
+        <v>0</v>
+      </c>
+      <c r="V527" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W527" t="n">
+        <v>24</v>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>5</v>
+      </c>
+      <c r="E528" t="n">
+        <v>33</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G528" t="n">
+        <v>5</v>
+      </c>
+      <c r="H528" t="n">
+        <v>0</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J528" t="n">
+        <v>1</v>
+      </c>
+      <c r="K528" t="n">
+        <v>568.1799999999999</v>
+      </c>
+      <c r="L528" t="n">
+        <v>0</v>
+      </c>
+      <c r="M528" t="n">
+        <v>568.1799999999999</v>
+      </c>
+      <c r="N528" t="n">
+        <v>1</v>
+      </c>
+      <c r="O528" t="n">
+        <v>2</v>
+      </c>
+      <c r="P528" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q528" t="n">
+        <v>1</v>
+      </c>
+      <c r="R528" t="n">
+        <v>1</v>
+      </c>
+      <c r="S528" t="n">
+        <v>0</v>
+      </c>
+      <c r="T528" t="n">
+        <v>0</v>
+      </c>
+      <c r="U528" t="n">
+        <v>0</v>
+      </c>
+      <c r="V528" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W528" t="n">
+        <v>24</v>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | A. MOODY | G. CLARKE | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>5</v>
+      </c>
+      <c r="E529" t="n">
+        <v>27</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G529" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" t="n">
+        <v>2</v>
+      </c>
+      <c r="I529" t="n">
+        <v>1</v>
+      </c>
+      <c r="J529" t="n">
+        <v>1</v>
+      </c>
+      <c r="K529" t="n">
+        <v>0</v>
+      </c>
+      <c r="L529" t="n">
+        <v>200</v>
+      </c>
+      <c r="M529" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N529" t="n">
+        <v>1</v>
+      </c>
+      <c r="O529" t="n">
+        <v>0</v>
+      </c>
+      <c r="P529" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q529" t="n">
+        <v>0</v>
+      </c>
+      <c r="R529" t="n">
+        <v>1</v>
+      </c>
+      <c r="S529" t="n">
+        <v>0</v>
+      </c>
+      <c r="T529" t="n">
+        <v>0</v>
+      </c>
+      <c r="U529" t="n">
+        <v>0</v>
+      </c>
+      <c r="V529" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W529" t="n">
+        <v>24</v>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>5</v>
+      </c>
+      <c r="E530" t="n">
+        <v>48</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G530" t="n">
+        <v>0</v>
+      </c>
+      <c r="H530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" t="n">
+        <v>1</v>
+      </c>
+      <c r="J530" t="n">
+        <v>0</v>
+      </c>
+      <c r="K530" t="n">
+        <v>0</v>
+      </c>
+      <c r="L530" t="n">
+        <v>0</v>
+      </c>
+      <c r="M530" t="n">
+        <v>0</v>
+      </c>
+      <c r="N530" t="n">
+        <v>1</v>
+      </c>
+      <c r="O530" t="n">
+        <v>0</v>
+      </c>
+      <c r="P530" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q530" t="n">
+        <v>0</v>
+      </c>
+      <c r="R530" t="n">
+        <v>0</v>
+      </c>
+      <c r="S530" t="n">
+        <v>0</v>
+      </c>
+      <c r="T530" t="n">
+        <v>0</v>
+      </c>
+      <c r="U530" t="n">
+        <v>0</v>
+      </c>
+      <c r="V530" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W530" t="n">
+        <v>24</v>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>5</v>
+      </c>
+      <c r="E531" t="n">
+        <v>162</v>
+      </c>
+      <c r="F531" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G531" t="n">
+        <v>5</v>
+      </c>
+      <c r="H531" t="n">
+        <v>9</v>
+      </c>
+      <c r="I531" t="n">
+        <v>3</v>
+      </c>
+      <c r="J531" t="n">
+        <v>3</v>
+      </c>
+      <c r="K531" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L531" t="n">
+        <v>300</v>
+      </c>
+      <c r="M531" t="n">
+        <v>-133.33</v>
+      </c>
+      <c r="N531" t="n">
+        <v>4</v>
+      </c>
+      <c r="O531" t="n">
+        <v>0</v>
+      </c>
+      <c r="P531" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q531" t="n">
+        <v>1</v>
+      </c>
+      <c r="R531" t="n">
+        <v>5</v>
+      </c>
+      <c r="S531" t="n">
+        <v>0</v>
+      </c>
+      <c r="T531" t="n">
+        <v>0</v>
+      </c>
+      <c r="U531" t="n">
+        <v>2</v>
+      </c>
+      <c r="V531" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W531" t="n">
+        <v>24</v>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2487927</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>A. LAFUENTE SISO | A. PALAZUELOS PEREZ | E. KALINICENKO | W. LEVEQUE</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>4</v>
+      </c>
+      <c r="E532" t="n">
+        <v>74</v>
+      </c>
+      <c r="F532" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G532" t="n">
+        <v>2</v>
+      </c>
+      <c r="H532" t="n">
+        <v>1</v>
+      </c>
+      <c r="I532" t="n">
+        <v>2</v>
+      </c>
+      <c r="J532" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K532" t="n">
+        <v>100</v>
+      </c>
+      <c r="L532" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M532" t="n">
+        <v>-13.64</v>
+      </c>
+      <c r="N532" t="n">
+        <v>2</v>
+      </c>
+      <c r="O532" t="n">
+        <v>0</v>
+      </c>
+      <c r="P532" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q532" t="n">
+        <v>0</v>
+      </c>
+      <c r="R532" t="n">
+        <v>0</v>
+      </c>
+      <c r="S532" t="n">
+        <v>2</v>
+      </c>
+      <c r="T532" t="n">
+        <v>1</v>
+      </c>
+      <c r="U532" t="n">
+        <v>1</v>
+      </c>
+      <c r="V532" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W532" t="n">
+        <v>25</v>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2487927</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>E. ARQUES LOPEZ | I. HANEY | J. HANNA | M. OCHI | P. ISERN MAZA</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>5</v>
+      </c>
+      <c r="E533" t="n">
+        <v>74</v>
+      </c>
+      <c r="F533" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G533" t="n">
+        <v>1</v>
+      </c>
+      <c r="H533" t="n">
+        <v>2</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J533" t="n">
+        <v>2</v>
+      </c>
+      <c r="K533" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L533" t="n">
+        <v>100</v>
+      </c>
+      <c r="M533" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="N533" t="n">
+        <v>0</v>
+      </c>
+      <c r="O533" t="n">
+        <v>2</v>
+      </c>
+      <c r="P533" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q533" t="n">
+        <v>1</v>
+      </c>
+      <c r="R533" t="n">
+        <v>2</v>
+      </c>
+      <c r="S533" t="n">
+        <v>0</v>
+      </c>
+      <c r="T533" t="n">
+        <v>0</v>
+      </c>
+      <c r="U533" t="n">
+        <v>0</v>
+      </c>
+      <c r="V533" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W533" t="n">
+        <v>25</v>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | S. KOCIC | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>5</v>
+      </c>
+      <c r="E534" t="n">
+        <v>231</v>
+      </c>
+      <c r="F534" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G534" t="n">
+        <v>6</v>
+      </c>
+      <c r="H534" t="n">
+        <v>5</v>
+      </c>
+      <c r="I534" t="n">
+        <v>9</v>
+      </c>
+      <c r="J534" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="K534" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="L534" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="M534" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="N534" t="n">
+        <v>7</v>
+      </c>
+      <c r="O534" t="n">
+        <v>0</v>
+      </c>
+      <c r="P534" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q534" t="n">
+        <v>0</v>
+      </c>
+      <c r="R534" t="n">
+        <v>5</v>
+      </c>
+      <c r="S534" t="n">
+        <v>7</v>
+      </c>
+      <c r="T534" t="n">
+        <v>1</v>
+      </c>
+      <c r="U534" t="n">
+        <v>2</v>
+      </c>
+      <c r="V534" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W534" t="n">
+        <v>25</v>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ | S. KOCIC | S. MENDIOLA DIEZ | T. TEIXEIRA DO VALE DIAS | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>5</v>
+      </c>
+      <c r="E535" t="n">
+        <v>14</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G535" t="n">
+        <v>1</v>
+      </c>
+      <c r="H535" t="n">
+        <v>2</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J535" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K535" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L535" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M535" t="n">
+        <v>-113.64</v>
+      </c>
+      <c r="N535" t="n">
+        <v>0</v>
+      </c>
+      <c r="O535" t="n">
+        <v>2</v>
+      </c>
+      <c r="P535" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>0</v>
+      </c>
+      <c r="R535" t="n">
+        <v>1</v>
+      </c>
+      <c r="S535" t="n">
+        <v>2</v>
+      </c>
+      <c r="T535" t="n">
+        <v>0</v>
+      </c>
+      <c r="U535" t="n">
+        <v>1</v>
+      </c>
+      <c r="V535" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W535" t="n">
+        <v>25</v>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>A. RODRIGUEZ AGUILAR | D. ROLLINS | F. BELLO MOURE | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>5</v>
+      </c>
+      <c r="E536" t="n">
+        <v>69</v>
+      </c>
+      <c r="F536" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G536" t="n">
+        <v>2</v>
+      </c>
+      <c r="H536" t="n">
+        <v>0</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J536" t="n">
+        <v>2</v>
+      </c>
+      <c r="K536" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L536" t="n">
+        <v>0</v>
+      </c>
+      <c r="M536" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="N536" t="n">
+        <v>0</v>
+      </c>
+      <c r="O536" t="n">
+        <v>2</v>
+      </c>
+      <c r="P536" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q536" t="n">
+        <v>0</v>
+      </c>
+      <c r="R536" t="n">
+        <v>1</v>
+      </c>
+      <c r="S536" t="n">
+        <v>0</v>
+      </c>
+      <c r="T536" t="n">
+        <v>1</v>
+      </c>
+      <c r="U536" t="n">
+        <v>0</v>
+      </c>
+      <c r="V536" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W536" t="n">
+        <v>25</v>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>A. RODRIGUEZ AGUILAR | D. ROLLINS | J. SIENCHE GUEMETA | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>5</v>
+      </c>
+      <c r="E537" t="n">
+        <v>23</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G537" t="n">
+        <v>1</v>
+      </c>
+      <c r="H537" t="n">
+        <v>0</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J537" t="n">
+        <v>1</v>
+      </c>
+      <c r="K537" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L537" t="n">
+        <v>0</v>
+      </c>
+      <c r="M537" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N537" t="n">
+        <v>0</v>
+      </c>
+      <c r="O537" t="n">
+        <v>2</v>
+      </c>
+      <c r="P537" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>0</v>
+      </c>
+      <c r="R537" t="n">
+        <v>1</v>
+      </c>
+      <c r="S537" t="n">
+        <v>0</v>
+      </c>
+      <c r="T537" t="n">
+        <v>0</v>
+      </c>
+      <c r="U537" t="n">
+        <v>0</v>
+      </c>
+      <c r="V537" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W537" t="n">
+        <v>25</v>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>A. RODRIGUEZ AGUILAR | F. BELLO MOURE | J. SIENCHE GUEMETA | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>5</v>
+      </c>
+      <c r="E538" t="n">
+        <v>14</v>
+      </c>
+      <c r="F538" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G538" t="n">
+        <v>2</v>
+      </c>
+      <c r="H538" t="n">
+        <v>1</v>
+      </c>
+      <c r="I538" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J538" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K538" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L538" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M538" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N538" t="n">
+        <v>1</v>
+      </c>
+      <c r="O538" t="n">
+        <v>2</v>
+      </c>
+      <c r="P538" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q538" t="n">
+        <v>1</v>
+      </c>
+      <c r="R538" t="n">
+        <v>0</v>
+      </c>
+      <c r="S538" t="n">
+        <v>2</v>
+      </c>
+      <c r="T538" t="n">
+        <v>0</v>
+      </c>
+      <c r="U538" t="n">
+        <v>0</v>
+      </c>
+      <c r="V538" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W538" t="n">
+        <v>25</v>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>D. ROLLINS | J. SIENCHE GUEMETA | K. SCHUTTE | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>5</v>
+      </c>
+      <c r="E539" t="n">
+        <v>40</v>
+      </c>
+      <c r="F539" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G539" t="n">
+        <v>0</v>
+      </c>
+      <c r="H539" t="n">
+        <v>3</v>
+      </c>
+      <c r="I539" t="n">
+        <v>2</v>
+      </c>
+      <c r="J539" t="n">
+        <v>2</v>
+      </c>
+      <c r="K539" t="n">
+        <v>0</v>
+      </c>
+      <c r="L539" t="n">
+        <v>150</v>
+      </c>
+      <c r="M539" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N539" t="n">
+        <v>2</v>
+      </c>
+      <c r="O539" t="n">
+        <v>0</v>
+      </c>
+      <c r="P539" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q539" t="n">
+        <v>0</v>
+      </c>
+      <c r="R539" t="n">
+        <v>2</v>
+      </c>
+      <c r="S539" t="n">
+        <v>0</v>
+      </c>
+      <c r="T539" t="n">
+        <v>0</v>
+      </c>
+      <c r="U539" t="n">
+        <v>0</v>
+      </c>
+      <c r="V539" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W539" t="n">
+        <v>25</v>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>F. BELLO MOURE | J. SIENCHE GUEMETA | K. SCHUTTE | P. SANCHEZ INFANTES | S. NDIAYE</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>5</v>
+      </c>
+      <c r="E540" t="n">
+        <v>99</v>
+      </c>
+      <c r="F540" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G540" t="n">
+        <v>2</v>
+      </c>
+      <c r="H540" t="n">
+        <v>3</v>
+      </c>
+      <c r="I540" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J540" t="n">
+        <v>4</v>
+      </c>
+      <c r="K540" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="L540" t="n">
+        <v>75</v>
+      </c>
+      <c r="M540" t="n">
+        <v>-14.76</v>
+      </c>
+      <c r="N540" t="n">
+        <v>3</v>
+      </c>
+      <c r="O540" t="n">
+        <v>3</v>
+      </c>
+      <c r="P540" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q540" t="n">
+        <v>2</v>
+      </c>
+      <c r="R540" t="n">
+        <v>3</v>
+      </c>
+      <c r="S540" t="n">
+        <v>0</v>
+      </c>
+      <c r="T540" t="n">
+        <v>1</v>
+      </c>
+      <c r="U540" t="n">
+        <v>0</v>
+      </c>
+      <c r="V540" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W540" t="n">
+        <v>25</v>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET vs COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | G. CLARKE | J. FRANCH DE PABLO | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>5</v>
+      </c>
+      <c r="E541" t="n">
+        <v>76</v>
+      </c>
+      <c r="F541" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G541" t="n">
+        <v>0</v>
+      </c>
+      <c r="H541" t="n">
+        <v>0</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" t="n">
+        <v>2</v>
+      </c>
+      <c r="K541" t="n">
+        <v>0</v>
+      </c>
+      <c r="L541" t="n">
+        <v>0</v>
+      </c>
+      <c r="M541" t="n">
+        <v>0</v>
+      </c>
+      <c r="N541" t="n">
+        <v>0</v>
+      </c>
+      <c r="O541" t="n">
+        <v>0</v>
+      </c>
+      <c r="P541" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>0</v>
+      </c>
+      <c r="R541" t="n">
+        <v>1</v>
+      </c>
+      <c r="S541" t="n">
+        <v>0</v>
+      </c>
+      <c r="T541" t="n">
+        <v>1</v>
+      </c>
+      <c r="U541" t="n">
+        <v>0</v>
+      </c>
+      <c r="V541" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W541" t="n">
+        <v>25</v>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ | J. FRANCH DE PABLO | N. DEDOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>5</v>
+      </c>
+      <c r="E542" t="n">
+        <v>16</v>
+      </c>
+      <c r="F542" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G542" t="n">
+        <v>2</v>
+      </c>
+      <c r="H542" t="n">
+        <v>0</v>
+      </c>
+      <c r="I542" t="n">
+        <v>1</v>
+      </c>
+      <c r="J542" t="n">
+        <v>0</v>
+      </c>
+      <c r="K542" t="n">
+        <v>200</v>
+      </c>
+      <c r="L542" t="n">
+        <v>0</v>
+      </c>
+      <c r="M542" t="n">
+        <v>0</v>
+      </c>
+      <c r="N542" t="n">
+        <v>1</v>
+      </c>
+      <c r="O542" t="n">
+        <v>0</v>
+      </c>
+      <c r="P542" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>0</v>
+      </c>
+      <c r="R542" t="n">
+        <v>0</v>
+      </c>
+      <c r="S542" t="n">
+        <v>0</v>
+      </c>
+      <c r="T542" t="n">
+        <v>0</v>
+      </c>
+      <c r="U542" t="n">
+        <v>0</v>
+      </c>
+      <c r="V542" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W542" t="n">
+        <v>25</v>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>A. MOODY | G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>5</v>
+      </c>
+      <c r="E543" t="n">
+        <v>108</v>
+      </c>
+      <c r="F543" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G543" t="n">
+        <v>0</v>
+      </c>
+      <c r="H543" t="n">
+        <v>0</v>
+      </c>
+      <c r="I543" t="n">
+        <v>1</v>
+      </c>
+      <c r="J543" t="n">
+        <v>2</v>
+      </c>
+      <c r="K543" t="n">
+        <v>0</v>
+      </c>
+      <c r="L543" t="n">
+        <v>0</v>
+      </c>
+      <c r="M543" t="n">
+        <v>0</v>
+      </c>
+      <c r="N543" t="n">
+        <v>1</v>
+      </c>
+      <c r="O543" t="n">
+        <v>0</v>
+      </c>
+      <c r="P543" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>1</v>
+      </c>
+      <c r="R543" t="n">
+        <v>2</v>
+      </c>
+      <c r="S543" t="n">
+        <v>0</v>
+      </c>
+      <c r="T543" t="n">
+        <v>0</v>
+      </c>
+      <c r="U543" t="n">
+        <v>0</v>
+      </c>
+      <c r="V543" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W543" t="n">
+        <v>25</v>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>A. MOODY | G. CLARKE | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>5</v>
+      </c>
+      <c r="E544" t="n">
+        <v>72</v>
+      </c>
+      <c r="F544" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G544" t="n">
+        <v>2</v>
+      </c>
+      <c r="H544" t="n">
+        <v>0</v>
+      </c>
+      <c r="I544" t="n">
+        <v>2</v>
+      </c>
+      <c r="J544" t="n">
+        <v>2</v>
+      </c>
+      <c r="K544" t="n">
+        <v>100</v>
+      </c>
+      <c r="L544" t="n">
+        <v>0</v>
+      </c>
+      <c r="M544" t="n">
+        <v>100</v>
+      </c>
+      <c r="N544" t="n">
+        <v>3</v>
+      </c>
+      <c r="O544" t="n">
+        <v>0</v>
+      </c>
+      <c r="P544" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>1</v>
+      </c>
+      <c r="R544" t="n">
+        <v>2</v>
+      </c>
+      <c r="S544" t="n">
+        <v>0</v>
+      </c>
+      <c r="T544" t="n">
+        <v>0</v>
+      </c>
+      <c r="U544" t="n">
+        <v>0</v>
+      </c>
+      <c r="V544" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W544" t="n">
+        <v>25</v>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>G. CLARKE | J. FRANCH DE PABLO | M. JANKOVIC | S. CECILIA PEREZ | W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>5</v>
+      </c>
+      <c r="E545" t="n">
+        <v>25</v>
+      </c>
+      <c r="F545" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G545" t="n">
+        <v>2</v>
+      </c>
+      <c r="H545" t="n">
+        <v>3</v>
+      </c>
+      <c r="I545" t="n">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
+        <v>1</v>
+      </c>
+      <c r="K545" t="n">
+        <v>200</v>
+      </c>
+      <c r="L545" t="n">
+        <v>300</v>
+      </c>
+      <c r="M545" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N545" t="n">
+        <v>1</v>
+      </c>
+      <c r="O545" t="n">
+        <v>0</v>
+      </c>
+      <c r="P545" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>0</v>
+      </c>
+      <c r="R545" t="n">
+        <v>1</v>
+      </c>
+      <c r="S545" t="n">
+        <v>0</v>
+      </c>
+      <c r="T545" t="n">
+        <v>0</v>
+      </c>
+      <c r="U545" t="n">
+        <v>0</v>
+      </c>
+      <c r="V545" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W545" t="n">
+        <v>25</v>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | A. PLITZUWEIT | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>5</v>
+      </c>
+      <c r="E546" t="n">
+        <v>25</v>
+      </c>
+      <c r="F546" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G546" t="n">
+        <v>3</v>
+      </c>
+      <c r="H546" t="n">
+        <v>2</v>
+      </c>
+      <c r="I546" t="n">
+        <v>1</v>
+      </c>
+      <c r="J546" t="n">
+        <v>1</v>
+      </c>
+      <c r="K546" t="n">
+        <v>300</v>
+      </c>
+      <c r="L546" t="n">
+        <v>200</v>
+      </c>
+      <c r="M546" t="n">
+        <v>100</v>
+      </c>
+      <c r="N546" t="n">
+        <v>1</v>
+      </c>
+      <c r="O546" t="n">
+        <v>0</v>
+      </c>
+      <c r="P546" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q546" t="n">
+        <v>0</v>
+      </c>
+      <c r="R546" t="n">
+        <v>1</v>
+      </c>
+      <c r="S546" t="n">
+        <v>0</v>
+      </c>
+      <c r="T546" t="n">
+        <v>0</v>
+      </c>
+      <c r="U546" t="n">
+        <v>0</v>
+      </c>
+      <c r="V546" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W546" t="n">
+        <v>25</v>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SALL | P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>5</v>
+      </c>
+      <c r="E547" t="n">
+        <v>184</v>
+      </c>
+      <c r="F547" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="G547" t="n">
+        <v>0</v>
+      </c>
+      <c r="H547" t="n">
+        <v>0</v>
+      </c>
+      <c r="I547" t="n">
+        <v>4</v>
+      </c>
+      <c r="J547" t="n">
+        <v>1</v>
+      </c>
+      <c r="K547" t="n">
+        <v>0</v>
+      </c>
+      <c r="L547" t="n">
+        <v>0</v>
+      </c>
+      <c r="M547" t="n">
+        <v>0</v>
+      </c>
+      <c r="N547" t="n">
+        <v>3</v>
+      </c>
+      <c r="O547" t="n">
+        <v>0</v>
+      </c>
+      <c r="P547" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q547" t="n">
+        <v>0</v>
+      </c>
+      <c r="R547" t="n">
+        <v>1</v>
+      </c>
+      <c r="S547" t="n">
+        <v>0</v>
+      </c>
+      <c r="T547" t="n">
+        <v>1</v>
+      </c>
+      <c r="U547" t="n">
+        <v>1</v>
+      </c>
+      <c r="V547" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W547" t="n">
+        <v>25</v>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT | B. AREVALO SAENZ | I. MONTERO MECA | P. SANTOS SPENCER | W. NIANG</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>5</v>
+      </c>
+      <c r="E548" t="n">
+        <v>16</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G548" t="n">
+        <v>0</v>
+      </c>
+      <c r="H548" t="n">
+        <v>2</v>
+      </c>
+      <c r="I548" t="n">
+        <v>0</v>
+      </c>
+      <c r="J548" t="n">
+        <v>1</v>
+      </c>
+      <c r="K548" t="n">
+        <v>0</v>
+      </c>
+      <c r="L548" t="n">
+        <v>200</v>
+      </c>
+      <c r="M548" t="n">
+        <v>0</v>
+      </c>
+      <c r="N548" t="n">
+        <v>0</v>
+      </c>
+      <c r="O548" t="n">
+        <v>0</v>
+      </c>
+      <c r="P548" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q548" t="n">
+        <v>0</v>
+      </c>
+      <c r="R548" t="n">
+        <v>1</v>
+      </c>
+      <c r="S548" t="n">
+        <v>0</v>
+      </c>
+      <c r="T548" t="n">
+        <v>0</v>
+      </c>
+      <c r="U548" t="n">
+        <v>0</v>
+      </c>
+      <c r="V548" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W548" t="n">
+        <v>25</v>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT | B. AREVALO SAENZ | L. OBAJO BELTRAN | S. SERRATO BALLETBO | W. NIANG</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>5</v>
+      </c>
+      <c r="E549" t="n">
+        <v>72</v>
+      </c>
+      <c r="F549" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G549" t="n">
+        <v>0</v>
+      </c>
+      <c r="H549" t="n">
+        <v>2</v>
+      </c>
+      <c r="I549" t="n">
+        <v>2</v>
+      </c>
+      <c r="J549" t="n">
+        <v>2</v>
+      </c>
+      <c r="K549" t="n">
+        <v>0</v>
+      </c>
+      <c r="L549" t="n">
+        <v>100</v>
+      </c>
+      <c r="M549" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N549" t="n">
+        <v>2</v>
+      </c>
+      <c r="O549" t="n">
+        <v>0</v>
+      </c>
+      <c r="P549" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q549" t="n">
+        <v>0</v>
+      </c>
+      <c r="R549" t="n">
+        <v>3</v>
+      </c>
+      <c r="S549" t="n">
+        <v>0</v>
+      </c>
+      <c r="T549" t="n">
+        <v>0</v>
+      </c>
+      <c r="U549" t="n">
+        <v>1</v>
+      </c>
+      <c r="V549" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W549" t="n">
+        <v>25</v>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87 vs LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>A. TRAORE | D. CEBOLLA PORCAR | E. VAN DER HEIJDEN | J. LLAMAS PRADO | M. DENG</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>5</v>
+      </c>
+      <c r="E550" t="n">
+        <v>91</v>
+      </c>
+      <c r="F550" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G550" t="n">
+        <v>4</v>
+      </c>
+      <c r="H550" t="n">
+        <v>5</v>
+      </c>
+      <c r="I550" t="n">
+        <v>3</v>
+      </c>
+      <c r="J550" t="n">
+        <v>3</v>
+      </c>
+      <c r="K550" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L550" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="M550" t="n">
+        <v>-33.33</v>
+      </c>
+      <c r="N550" t="n">
+        <v>3</v>
+      </c>
+      <c r="O550" t="n">
+        <v>0</v>
+      </c>
+      <c r="P550" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q550" t="n">
+        <v>0</v>
+      </c>
+      <c r="R550" t="n">
+        <v>3</v>
+      </c>
+      <c r="S550" t="n">
+        <v>0</v>
+      </c>
+      <c r="T550" t="n">
+        <v>2</v>
+      </c>
+      <c r="U550" t="n">
+        <v>2</v>
+      </c>
+      <c r="V550" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W550" t="n">
+        <v>26</v>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>D. CEBOLLA PORCAR | D. HAYMAN | E. VAN DER HEIJDEN | J. LLAMAS PRADO | M. DENG</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>5</v>
+      </c>
+      <c r="E551" t="n">
+        <v>5</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G551" t="n">
+        <v>0</v>
+      </c>
+      <c r="H551" t="n">
+        <v>1</v>
+      </c>
+      <c r="I551" t="n">
+        <v>0</v>
+      </c>
+      <c r="J551" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K551" t="n">
+        <v>0</v>
+      </c>
+      <c r="L551" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="M551" t="n">
+        <v>0</v>
+      </c>
+      <c r="N551" t="n">
+        <v>0</v>
+      </c>
+      <c r="O551" t="n">
+        <v>0</v>
+      </c>
+      <c r="P551" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q551" t="n">
+        <v>0</v>
+      </c>
+      <c r="R551" t="n">
+        <v>0</v>
+      </c>
+      <c r="S551" t="n">
+        <v>4</v>
+      </c>
+      <c r="T551" t="n">
+        <v>0</v>
+      </c>
+      <c r="U551" t="n">
+        <v>0</v>
+      </c>
+      <c r="V551" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W551" t="n">
+        <v>26</v>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>C. JACOBS | J. PARDINA MOLINA | K. TORRES CUEVAS | M. DE PABLO DEL CASTILLO | P. DIENE</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>5</v>
+      </c>
+      <c r="E552" t="n">
+        <v>62</v>
+      </c>
+      <c r="F552" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G552" t="n">
+        <v>5</v>
+      </c>
+      <c r="H552" t="n">
+        <v>2</v>
+      </c>
+      <c r="I552" t="n">
+        <v>3</v>
+      </c>
+      <c r="J552" t="n">
+        <v>1</v>
+      </c>
+      <c r="K552" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L552" t="n">
+        <v>200</v>
+      </c>
+      <c r="M552" t="n">
+        <v>-33.33</v>
+      </c>
+      <c r="N552" t="n">
+        <v>3</v>
+      </c>
+      <c r="O552" t="n">
+        <v>0</v>
+      </c>
+      <c r="P552" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q552" t="n">
+        <v>1</v>
+      </c>
+      <c r="R552" t="n">
+        <v>1</v>
+      </c>
+      <c r="S552" t="n">
+        <v>0</v>
+      </c>
+      <c r="T552" t="n">
+        <v>0</v>
+      </c>
+      <c r="U552" t="n">
+        <v>0</v>
+      </c>
+      <c r="V552" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W552" t="n">
+        <v>26</v>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>C. JACOBS | J. PARDINA MOLINA | K. TORRES CUEVAS | M. DE PABLO DEL CASTILLO | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>5</v>
+      </c>
+      <c r="E553" t="n">
+        <v>1</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G553" t="n">
+        <v>1</v>
+      </c>
+      <c r="H553" t="n">
+        <v>0</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J553" t="n">
+        <v>0</v>
+      </c>
+      <c r="K553" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L553" t="n">
+        <v>0</v>
+      </c>
+      <c r="M553" t="n">
+        <v>0</v>
+      </c>
+      <c r="N553" t="n">
+        <v>0</v>
+      </c>
+      <c r="O553" t="n">
+        <v>2</v>
+      </c>
+      <c r="P553" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q553" t="n">
+        <v>0</v>
+      </c>
+      <c r="R553" t="n">
+        <v>0</v>
+      </c>
+      <c r="S553" t="n">
+        <v>0</v>
+      </c>
+      <c r="T553" t="n">
+        <v>0</v>
+      </c>
+      <c r="U553" t="n">
+        <v>0</v>
+      </c>
+      <c r="V553" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W553" t="n">
+        <v>26</v>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>J. PARDINA MOLINA | K. TORRES CUEVAS | M. DE PABLO DEL CASTILLO | P. DIENE | R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>5</v>
+      </c>
+      <c r="E554" t="n">
+        <v>33</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G554" t="n">
+        <v>0</v>
+      </c>
+      <c r="H554" t="n">
+        <v>2</v>
+      </c>
+      <c r="I554" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J554" t="n">
+        <v>2</v>
+      </c>
+      <c r="K554" t="n">
+        <v>0</v>
+      </c>
+      <c r="L554" t="n">
+        <v>100</v>
+      </c>
+      <c r="M554" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N554" t="n">
+        <v>0</v>
+      </c>
+      <c r="O554" t="n">
+        <v>2</v>
+      </c>
+      <c r="P554" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q554" t="n">
+        <v>1</v>
+      </c>
+      <c r="R554" t="n">
+        <v>2</v>
+      </c>
+      <c r="S554" t="n">
+        <v>0</v>
+      </c>
+      <c r="T554" t="n">
+        <v>0</v>
+      </c>
+      <c r="U554" t="n">
+        <v>0</v>
+      </c>
+      <c r="V554" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W554" t="n">
+        <v>26</v>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>A. LAFUENTE SISO | A. MAZAIRA GOMEZ | A. PALAZUELOS PEREZ | E. KALINICENKO | W. LEVEQUE</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>5</v>
+      </c>
+      <c r="E555" t="n">
+        <v>287</v>
+      </c>
+      <c r="F555" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="G555" t="n">
+        <v>10</v>
+      </c>
+      <c r="H555" t="n">
+        <v>5</v>
+      </c>
+      <c r="I555" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="J555" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="K555" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="L555" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="M555" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="N555" t="n">
+        <v>8</v>
+      </c>
+      <c r="O555" t="n">
+        <v>3</v>
+      </c>
+      <c r="P555" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q555" t="n">
+        <v>1</v>
+      </c>
+      <c r="R555" t="n">
+        <v>5</v>
+      </c>
+      <c r="S555" t="n">
+        <v>4</v>
+      </c>
+      <c r="T555" t="n">
+        <v>3</v>
+      </c>
+      <c r="U555" t="n">
+        <v>1</v>
+      </c>
+      <c r="V555" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W555" t="n">
+        <v>26</v>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>A. LAFUENTE SISO | A. MAZAIRA GOMEZ | A. PALAZUELOS PEREZ | M. STRIKKER | W. LEVEQUE</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>5</v>
+      </c>
+      <c r="E556" t="n">
+        <v>1</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G556" t="n">
+        <v>0</v>
+      </c>
+      <c r="H556" t="n">
+        <v>2</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0</v>
+      </c>
+      <c r="J556" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K556" t="n">
+        <v>0</v>
+      </c>
+      <c r="L556" t="n">
+        <v>151.52</v>
+      </c>
+      <c r="M556" t="n">
+        <v>0</v>
+      </c>
+      <c r="N556" t="n">
+        <v>0</v>
+      </c>
+      <c r="O556" t="n">
+        <v>0</v>
+      </c>
+      <c r="P556" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q556" t="n">
+        <v>0</v>
+      </c>
+      <c r="R556" t="n">
+        <v>0</v>
+      </c>
+      <c r="S556" t="n">
+        <v>3</v>
+      </c>
+      <c r="T556" t="n">
+        <v>0</v>
+      </c>
+      <c r="U556" t="n">
+        <v>0</v>
+      </c>
+      <c r="V556" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W556" t="n">
+        <v>26</v>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>F. SIERRA GALA | J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | M. SERRANO ALVAREZ | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>5</v>
+      </c>
+      <c r="E557" t="n">
+        <v>6</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G557" t="n">
+        <v>2</v>
+      </c>
+      <c r="H557" t="n">
+        <v>6</v>
+      </c>
+      <c r="I557" t="n">
+        <v>1</v>
+      </c>
+      <c r="J557" t="n">
+        <v>2</v>
+      </c>
+      <c r="K557" t="n">
+        <v>200</v>
+      </c>
+      <c r="L557" t="n">
+        <v>300</v>
+      </c>
+      <c r="M557" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N557" t="n">
+        <v>1</v>
+      </c>
+      <c r="O557" t="n">
+        <v>0</v>
+      </c>
+      <c r="P557" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q557" t="n">
+        <v>0</v>
+      </c>
+      <c r="R557" t="n">
+        <v>2</v>
+      </c>
+      <c r="S557" t="n">
+        <v>0</v>
+      </c>
+      <c r="T557" t="n">
+        <v>0</v>
+      </c>
+      <c r="U557" t="n">
+        <v>0</v>
+      </c>
+      <c r="V557" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W557" t="n">
+        <v>26</v>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>F. SIERRA GALA | J. LAFUENTE VELAZQUEZ | L. GARCIA MUÑOZ | S. MENDIOLA DIEZ | V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>5</v>
+      </c>
+      <c r="E558" t="n">
+        <v>282</v>
+      </c>
+      <c r="F558" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G558" t="n">
+        <v>5</v>
+      </c>
+      <c r="H558" t="n">
+        <v>4</v>
+      </c>
+      <c r="I558" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="J558" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="K558" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="L558" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="M558" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="N558" t="n">
+        <v>4</v>
+      </c>
+      <c r="O558" t="n">
+        <v>7</v>
+      </c>
+      <c r="P558" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q558" t="n">
+        <v>1</v>
+      </c>
+      <c r="R558" t="n">
+        <v>6</v>
+      </c>
+      <c r="S558" t="n">
+        <v>3</v>
+      </c>
+      <c r="T558" t="n">
+        <v>3</v>
+      </c>
+      <c r="U558" t="n">
+        <v>1</v>
+      </c>
+      <c r="V558" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W558" t="n">
+        <v>26</v>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | G. VERGARA HARBOE | K. FELIZOR | M. TIKHONENKO ANDRIYASHCHENKO</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>5</v>
+      </c>
+      <c r="E559" t="n">
+        <v>14</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G559" t="n">
+        <v>3</v>
+      </c>
+      <c r="H559" t="n">
+        <v>0</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K559" t="n">
+        <v>0</v>
+      </c>
+      <c r="L559" t="n">
+        <v>0</v>
+      </c>
+      <c r="M559" t="n">
+        <v>0</v>
+      </c>
+      <c r="N559" t="n">
+        <v>1</v>
+      </c>
+      <c r="O559" t="n">
+        <v>0</v>
+      </c>
+      <c r="P559" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q559" t="n">
+        <v>1</v>
+      </c>
+      <c r="R559" t="n">
+        <v>1</v>
+      </c>
+      <c r="S559" t="n">
+        <v>2</v>
+      </c>
+      <c r="T559" t="n">
+        <v>0</v>
+      </c>
+      <c r="U559" t="n">
+        <v>1</v>
+      </c>
+      <c r="V559" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W559" t="n">
+        <v>26</v>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | J. MARTINEZ MEGIAS | J. SANTA BARBARA CARCELEN | K. FELIZOR</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>5</v>
+      </c>
+      <c r="E560" t="n">
+        <v>28</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G560" t="n">
+        <v>0</v>
+      </c>
+      <c r="H560" t="n">
+        <v>5</v>
+      </c>
+      <c r="I560" t="n">
+        <v>1</v>
+      </c>
+      <c r="J560" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K560" t="n">
+        <v>0</v>
+      </c>
+      <c r="L560" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="M560" t="n">
+        <v>-378.79</v>
+      </c>
+      <c r="N560" t="n">
+        <v>1</v>
+      </c>
+      <c r="O560" t="n">
+        <v>0</v>
+      </c>
+      <c r="P560" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q560" t="n">
+        <v>0</v>
+      </c>
+      <c r="R560" t="n">
+        <v>1</v>
+      </c>
+      <c r="S560" t="n">
+        <v>3</v>
+      </c>
+      <c r="T560" t="n">
+        <v>0</v>
+      </c>
+      <c r="U560" t="n">
+        <v>1</v>
+      </c>
+      <c r="V560" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W560" t="n">
+        <v>26</v>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | J. MORENO POZA | J. SANTA BARBARA CARCELEN | K. FELIZOR</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>5</v>
+      </c>
+      <c r="E561" t="n">
+        <v>43</v>
+      </c>
+      <c r="F561" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G561" t="n">
+        <v>2</v>
+      </c>
+      <c r="H561" t="n">
+        <v>0</v>
+      </c>
+      <c r="I561" t="n">
+        <v>2</v>
+      </c>
+      <c r="J561" t="n">
+        <v>1</v>
+      </c>
+      <c r="K561" t="n">
+        <v>100</v>
+      </c>
+      <c r="L561" t="n">
+        <v>0</v>
+      </c>
+      <c r="M561" t="n">
+        <v>100</v>
+      </c>
+      <c r="N561" t="n">
+        <v>2</v>
+      </c>
+      <c r="O561" t="n">
+        <v>0</v>
+      </c>
+      <c r="P561" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q561" t="n">
+        <v>1</v>
+      </c>
+      <c r="R561" t="n">
+        <v>1</v>
+      </c>
+      <c r="S561" t="n">
+        <v>0</v>
+      </c>
+      <c r="T561" t="n">
+        <v>0</v>
+      </c>
+      <c r="U561" t="n">
+        <v>0</v>
+      </c>
+      <c r="V561" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W561" t="n">
+        <v>26</v>
+      </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>C. FIELDS | G. BOAHEN | J. SANTA BARBARA CARCELEN | K. FELIZOR | M. TIKHONENKO ANDRIYASHCHENKO</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>5</v>
+      </c>
+      <c r="E562" t="n">
+        <v>65</v>
+      </c>
+      <c r="F562" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G562" t="n">
+        <v>3</v>
+      </c>
+      <c r="H562" t="n">
+        <v>3</v>
+      </c>
+      <c r="I562" t="n">
+        <v>1</v>
+      </c>
+      <c r="J562" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K562" t="n">
+        <v>300</v>
+      </c>
+      <c r="L562" t="n">
+        <v>170.45</v>
+      </c>
+      <c r="M562" t="n">
+        <v>129.55</v>
+      </c>
+      <c r="N562" t="n">
+        <v>2</v>
+      </c>
+      <c r="O562" t="n">
+        <v>0</v>
+      </c>
+      <c r="P562" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q562" t="n">
+        <v>1</v>
+      </c>
+      <c r="R562" t="n">
+        <v>0</v>
+      </c>
+      <c r="S562" t="n">
+        <v>4</v>
+      </c>
+      <c r="T562" t="n">
+        <v>0</v>
+      </c>
+      <c r="U562" t="n">
+        <v>0</v>
+      </c>
+      <c r="V562" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W562" t="n">
+        <v>26</v>
+      </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>C. FIELDS | J. SANTA BARBARA CARCELEN | K. FELIZOR | L. FAIAL | M. TIKHONENKO ANDRIYASHCHENKO</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>5</v>
+      </c>
+      <c r="E563" t="n">
+        <v>23</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G563" t="n">
+        <v>1</v>
+      </c>
+      <c r="H563" t="n">
+        <v>2</v>
+      </c>
+      <c r="I563" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J563" t="n">
+        <v>1</v>
+      </c>
+      <c r="K563" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L563" t="n">
+        <v>200</v>
+      </c>
+      <c r="M563" t="n">
+        <v>-86.36</v>
+      </c>
+      <c r="N563" t="n">
+        <v>0</v>
+      </c>
+      <c r="O563" t="n">
+        <v>2</v>
+      </c>
+      <c r="P563" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q563" t="n">
+        <v>0</v>
+      </c>
+      <c r="R563" t="n">
+        <v>1</v>
+      </c>
+      <c r="S563" t="n">
+        <v>0</v>
+      </c>
+      <c r="T563" t="n">
+        <v>0</v>
+      </c>
+      <c r="U563" t="n">
+        <v>0</v>
+      </c>
+      <c r="V563" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W563" t="n">
+        <v>26</v>
+      </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | B. AREVALO SAENZ | I. MONTERO MECA | P. SANTOS SPENCER | W. NIANG</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>5</v>
+      </c>
+      <c r="E564" t="n">
+        <v>43</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G564" t="n">
+        <v>0</v>
+      </c>
+      <c r="H564" t="n">
+        <v>2</v>
+      </c>
+      <c r="I564" t="n">
+        <v>1</v>
+      </c>
+      <c r="J564" t="n">
+        <v>2</v>
+      </c>
+      <c r="K564" t="n">
+        <v>0</v>
+      </c>
+      <c r="L564" t="n">
+        <v>100</v>
+      </c>
+      <c r="M564" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N564" t="n">
+        <v>1</v>
+      </c>
+      <c r="O564" t="n">
+        <v>0</v>
+      </c>
+      <c r="P564" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q564" t="n">
+        <v>0</v>
+      </c>
+      <c r="R564" t="n">
+        <v>2</v>
+      </c>
+      <c r="S564" t="n">
+        <v>0</v>
+      </c>
+      <c r="T564" t="n">
+        <v>1</v>
+      </c>
+      <c r="U564" t="n">
+        <v>1</v>
+      </c>
+      <c r="V564" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W564" t="n">
+        <v>26</v>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | B. AREVALO SAENZ | P. SALL | P. SANTOS SPENCER | S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>5</v>
+      </c>
+      <c r="E565" t="n">
+        <v>112</v>
+      </c>
+      <c r="F565" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G565" t="n">
+        <v>9</v>
+      </c>
+      <c r="H565" t="n">
+        <v>7</v>
+      </c>
+      <c r="I565" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="J565" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K565" t="n">
+        <v>220.59</v>
+      </c>
+      <c r="L565" t="n">
+        <v>243.06</v>
+      </c>
+      <c r="M565" t="n">
+        <v>-22.47</v>
+      </c>
+      <c r="N565" t="n">
+        <v>3</v>
+      </c>
+      <c r="O565" t="n">
+        <v>7</v>
+      </c>
+      <c r="P565" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q565" t="n">
+        <v>2</v>
+      </c>
+      <c r="R565" t="n">
+        <v>4</v>
+      </c>
+      <c r="S565" t="n">
+        <v>2</v>
+      </c>
+      <c r="T565" t="n">
+        <v>0</v>
+      </c>
+      <c r="U565" t="n">
+        <v>2</v>
+      </c>
+      <c r="V565" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W565" t="n">
+        <v>26</v>
+      </c>
+      <c r="X565" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ | B. AREVALO SAENZ | P. SANTOS SPENCER | S. SERRATO BALLETBO | W. NIANG</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>5</v>
+      </c>
+      <c r="E566" t="n">
+        <v>18</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G566" t="n">
+        <v>1</v>
+      </c>
+      <c r="H566" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J566" t="n">
+        <v>0</v>
+      </c>
+      <c r="K566" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L566" t="n">
+        <v>0</v>
+      </c>
+      <c r="M566" t="n">
+        <v>0</v>
+      </c>
+      <c r="N566" t="n">
+        <v>0</v>
+      </c>
+      <c r="O566" t="n">
+        <v>2</v>
+      </c>
+      <c r="P566" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q566" t="n">
+        <v>0</v>
+      </c>
+      <c r="R566" t="n">
+        <v>0</v>
+      </c>
+      <c r="S566" t="n">
+        <v>0</v>
+      </c>
+      <c r="T566" t="n">
+        <v>0</v>
+      </c>
+      <c r="U566" t="n">
+        <v>0</v>
+      </c>
+      <c r="V566" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="W566" t="n">
+        <v>26</v>
+      </c>
+      <c r="X566" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
